--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>14min</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>06min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2097781</v>
+        <v>2097803</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -902,27 +902,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDÁGIO AVULSO - EQU3D45 </t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270046 NF 155394</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:50:23</t>
+          <t>02/03/2026 07:28:23</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:01:12</t>
+          <t>02/03/2026 07:39:46</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:50:23</t>
+          <t>02/03/2026 07:28:23</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>01h 22min</t>
+          <t>47min</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2097814</v>
+        <v>2097787</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280037 NF- 627240</t>
+          <t>emissão Reckitt SHI2602280004 NF- 627182</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:46:23</t>
+          <t>02/03/2026 07:00:27</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:05</t>
+          <t>02/03/2026 07:24:47</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:46:23</t>
+          <t>02/03/2026 07:00:27</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>19min</t>
+          <t>01h 02min</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2097803</v>
+        <v>2097814</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1022,27 +1022,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270046 NF 155394</t>
+          <t>emissão Reckitt SHI2602280037 NF- 627240</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:23</t>
+          <t>02/03/2026 07:46:23</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:39:46</t>
+          <t>02/03/2026 08:04:05</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:23</t>
+          <t>02/03/2026 07:46:23</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>43min</t>
+          <t>23min</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>54min</t>
+          <t>58min</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2097787</v>
+        <v>2097811</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280004 NF- 627182</t>
+          <t>emissão Reckitt SHI2603020003 NF- 627246</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:27</t>
+          <t>02/03/2026 07:42:23</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:47</t>
+          <t>02/03/2026 07:57:25</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:27</t>
+          <t>02/03/2026 07:42:23</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>58min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>09min</t>
         </is>
       </c>
     </row>
@@ -1248,11 +1248,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2097786</v>
+        <v>2097781</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270032 NF 155379</t>
+          <t xml:space="preserve">PEDÁGIO AVULSO - EQU3D45 </t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:25</t>
+          <t>02/03/2026 06:50:23</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:16:56</t>
+          <t>02/03/2026 07:01:12</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:25</t>
+          <t>02/03/2026 06:50:23</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>01h 06min</t>
+          <t>01h 26min</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>50min</t>
+          <t>54min</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2097811</v>
+        <v>2097818</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2603020003 NF- 627246</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2602280035 NF- 627236</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:23</t>
+          <t>02/03/2026 07:52:23</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:25</t>
+          <t>02/03/2026 08:11:44</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:23</t>
+          <t>02/03/2026 07:52:23</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2097818</v>
+        <v>2097786</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -1442,27 +1442,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2602280035 NF- 627236</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270032 NF 155379</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:52:23</t>
+          <t>02/03/2026 07:00:25</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:11:44</t>
+          <t>02/03/2026 07:16:56</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:52:23</t>
+          <t>02/03/2026 07:00:25</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -1543,41 +1543,41 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2097813</v>
+        <v>2097812</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:25</t>
+          <t>02/03/2026 07:44:23</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:45:04</t>
+          <t>02/03/2026 08:17:52</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:25</t>
+          <t>02/03/2026 07:44:23</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>38min</t>
+          <t>09min</t>
         </is>
       </c>
     </row>
@@ -1603,11 +1603,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2097820</v>
+        <v>2097794</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>RITMO - SEGUROS</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>RES: Emissão CT-e manual- Ritmo</t>
+          <t xml:space="preserve">RES: PEDÁGIO AVULSO - EQU3D45 </t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Adrian Bitencourt</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:25</t>
+          <t>02/03/2026 07:18:26</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:57</t>
+          <t>02/03/2026 07:19:44</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:25</t>
+          <t>02/03/2026 07:18:26</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>06min</t>
+          <t>01h 07min</t>
         </is>
       </c>
     </row>
@@ -1663,11 +1663,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2097828</v>
+        <v>2097810</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1677,27 +1677,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO DE CTE- MFV-5C36------------DEXCO-----------------DT-6100685957</t>
+          <t>ENC: CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:23</t>
+          <t>02/03/2026 07:40:25</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:17</t>
+          <t>02/03/2026 07:42:46</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:23</t>
+          <t>02/03/2026 07:40:25</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>44min</t>
         </is>
       </c>
     </row>
@@ -1723,11 +1723,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2097778</v>
+        <v>2097763</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1737,27 +1737,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: INFORMAÇÕES PARA EMISSÃO DE CTE  </t>
+          <t>RES: EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:23</t>
+          <t>02/03/2026 05:00:26</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:42</t>
+          <t>02/03/2026 07:45:00</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:23</t>
+          <t>02/03/2026 05:00:26</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>25min</t>
+          <t>42min</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2097816</v>
+        <v>2097784</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 06:56:26</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:25</t>
+          <t>02/03/2026 07:24:19</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 06:56:26</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -1843,41 +1843,41 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2097773</v>
+        <v>2097785</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
+          <t>ENC: CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:28:25</t>
+          <t>02/03/2026 06:56:27</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:49:01</t>
+          <t>02/03/2026 06:59:53</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:28:25</t>
+          <t>02/03/2026 06:56:27</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>01h 27min</t>
         </is>
       </c>
     </row>
@@ -1903,41 +1903,41 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2097763</v>
+        <v>2097813</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
+          <t>ENC: CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:26</t>
+          <t>02/03/2026 07:44:25</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:45:00</t>
+          <t>02/03/2026 07:45:04</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:26</t>
+          <t>02/03/2026 07:44:25</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>38min</t>
+          <t>42min</t>
         </is>
       </c>
     </row>
@@ -1963,11 +1963,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2097789</v>
+        <v>2097816</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1977,27 +1977,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270121 NF 155393</t>
+          <t>CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:25</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:57</t>
+          <t>02/03/2026 07:57:25</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:25</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 16min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -2023,11 +2023,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2097785</v>
+        <v>2097792</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2037,27 +2037,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
+          <t>emissão Reckitt SHI2602280019 NF- 627205</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:27</t>
+          <t>02/03/2026 07:10:23</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:59:53</t>
+          <t>02/03/2026 07:11:44</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:27</t>
+          <t>02/03/2026 07:10:23</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 23min</t>
+          <t>01h 15min</t>
         </is>
       </c>
     </row>
@@ -2083,11 +2083,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2097791</v>
+        <v>2097819</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2602280029 NF- 627224</t>
+          <t xml:space="preserve">RES: Placa FPK5D43 Desagregado </t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>leonardo Pedroso Horita</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:25</t>
+          <t>02/03/2026 07:56:23</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:07:30</t>
+          <t>02/03/2026 07:59:53</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:25</t>
+          <t>02/03/2026 07:56:23</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>01h 16min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2097799</v>
+        <v>2097825</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2157,27 +2157,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.557 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:26</t>
+          <t>02/03/2026 08:04:23</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:45</t>
+          <t>02/03/2026 08:05:10</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:26</t>
+          <t>02/03/2026 08:04:23</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>22min</t>
         </is>
       </c>
     </row>
@@ -2203,11 +2203,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2097806</v>
+        <v>2097798</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>ENC: CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:34:23</t>
+          <t>02/03/2026 07:20:25</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:38</t>
+          <t>02/03/2026 07:20:57</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:34:23</t>
+          <t>02/03/2026 07:20:25</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>01h 06min</t>
         </is>
       </c>
     </row>
@@ -2263,41 +2263,41 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2097748</v>
+        <v>2097817</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>RES: 13065319 ALEXANDRE HERMES PEREIRA IAP5D29 GIX4D54</t>
+          <t>ENC: CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:10:25</t>
+          <t>02/03/2026 07:50:24</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:33:33</t>
+          <t>02/03/2026 07:50:47</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:10:25</t>
+          <t>02/03/2026 07:50:24</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>50min</t>
+          <t>36min</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2097795</v>
+        <v>2097807</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:28</t>
+          <t>02/03/2026 07:38:23</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:42</t>
+          <t>02/03/2026 07:50:22</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:28</t>
+          <t>02/03/2026 07:38:23</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -2383,41 +2383,41 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2097784</v>
+        <v>2097748</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: 13065319 ALEXANDRE HERMES PEREIRA IAP5D29 GIX4D54</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:26</t>
+          <t>02/03/2026 04:10:25</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:19</t>
+          <t>02/03/2026 07:33:33</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:26</t>
+          <t>02/03/2026 04:10:25</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>53min</t>
         </is>
       </c>
     </row>
@@ -2443,11 +2443,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2097817</v>
+        <v>2097795</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2457,27 +2457,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:24</t>
+          <t>02/03/2026 07:18:28</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:47</t>
+          <t>02/03/2026 07:26:42</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:24</t>
+          <t>02/03/2026 07:18:28</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>32min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -2503,11 +2503,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2097794</v>
+        <v>2097796</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2517,27 +2517,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: PEDÁGIO AVULSO - EQU3D45 </t>
+          <t>ENC: CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:26</t>
+          <t>02/03/2026 07:18:29</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:19:44</t>
+          <t>02/03/2026 07:19:39</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:26</t>
+          <t>02/03/2026 07:18:29</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>01h 07min</t>
         </is>
       </c>
     </row>
@@ -2563,41 +2563,41 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2097812</v>
+        <v>2097809</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:23</t>
+          <t>02/03/2026 07:40:23</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:52</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:23</t>
+          <t>02/03/2026 07:40:23</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>18min</t>
+          <t>22min</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2097788</v>
+        <v>2097789</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270105 NF 155387</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270121 NF 155393</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2707,17 +2707,17 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:23</t>
+          <t>02/03/2026 07:02:25</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:05:21</t>
+          <t>02/03/2026 07:06:57</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:23</t>
+          <t>02/03/2026 07:02:25</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>01h 20min</t>
         </is>
       </c>
     </row>
@@ -2743,11 +2743,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2097815</v>
+        <v>2097808</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2757,27 +2757,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Favor encerrar o MDFe do veículo: QXI0C85</t>
+          <t>ENC: CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Rodrigues Silva da Anunciação</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:48:23</t>
+          <t>02/03/2026 07:38:25</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:46</t>
+          <t>02/03/2026 07:38:42</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:48:23</t>
+          <t>02/03/2026 07:38:25</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>32min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2097796</v>
+        <v>2097832</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:29</t>
+          <t>02/03/2026 08:08:29</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:19:39</t>
+          <t>02/03/2026 08:09:09</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:29</t>
+          <t>02/03/2026 08:08:29</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>18min</t>
         </is>
       </c>
     </row>
@@ -2863,41 +2863,41 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2097826</v>
+        <v>2097773</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Re: cte 6920</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:25</t>
+          <t>02/03/2026 05:28:25</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:09</t>
+          <t>02/03/2026 07:49:01</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:25</t>
+          <t>02/03/2026 05:28:25</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>18min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -2923,11 +2923,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2097835</v>
+        <v>2097804</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2937,27 +2937,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151038 - Série: 1</t>
+          <t>Favoe encerrar o MDFe do veículo: QXI3I84</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Eduardo Rodrigues Silva da Anunciação</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:26</t>
+          <t>02/03/2026 07:28:25</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:17</t>
+          <t>02/03/2026 07:30:56</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:26</t>
+          <t>02/03/2026 07:28:25</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>56min</t>
         </is>
       </c>
     </row>
@@ -2983,11 +2983,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2097792</v>
+        <v>2097820</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>RITMO - SEGUROS</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2997,27 +2997,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280019 NF- 627205</t>
+          <t>RES: Emissão CT-e manual- Ritmo</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Adrian Bitencourt</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:10:23</t>
+          <t>02/03/2026 07:56:25</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:11:44</t>
+          <t>02/03/2026 08:16:57</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:10:23</t>
+          <t>02/03/2026 07:56:25</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>01h 11min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -3043,11 +3043,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2097808</v>
+        <v>2097788</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3057,27 +3057,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270105 NF 155387</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:25</t>
+          <t>02/03/2026 07:02:23</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:42</t>
+          <t>02/03/2026 07:05:21</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:25</t>
+          <t>02/03/2026 07:02:23</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>01h 22min</t>
         </is>
       </c>
     </row>
@@ -3103,11 +3103,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2097783</v>
+        <v>2097821</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020002 NF- 627244</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:24</t>
+          <t>02/03/2026 07:58:23</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:59:51</t>
+          <t>02/03/2026 08:01:21</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:24</t>
+          <t>02/03/2026 07:58:23</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>01h 23min</t>
+          <t>26min</t>
         </is>
       </c>
     </row>
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2097797</v>
+        <v>2097828</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3177,27 +3177,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO DE CTE- MFV-5C36------------DEXCO-----------------DT-6100685957</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:23</t>
+          <t>02/03/2026 08:06:23</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:44</t>
+          <t>02/03/2026 08:08:17</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:24</t>
+          <t>02/03/2026 08:06:23</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>19min</t>
         </is>
       </c>
     </row>
@@ -3223,11 +3223,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2097807</v>
+        <v>2097790</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3237,27 +3237,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270120 NF 155391</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:23</t>
+          <t>02/03/2026 07:06:24</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:22</t>
+          <t>02/03/2026 07:07:27</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:23</t>
+          <t>02/03/2026 07:06:24</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>01h 19min</t>
         </is>
       </c>
     </row>
@@ -3283,11 +3283,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2097809</v>
+        <v>2097815</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3297,27 +3297,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Favor encerrar o MDFe do veículo: QXI0C85</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Eduardo Rodrigues Silva da Anunciação</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:23</t>
+          <t>02/03/2026 07:48:23</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 07:50:46</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:23</t>
+          <t>02/03/2026 07:48:23</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>36min</t>
         </is>
       </c>
     </row>
@@ -3343,11 +3343,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2097790</v>
+        <v>2097799</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3357,27 +3357,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270120 NF 155391</t>
+          <t>CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:24</t>
+          <t>02/03/2026 07:20:26</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:07:27</t>
+          <t>02/03/2026 07:26:45</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:24</t>
+          <t>02/03/2026 07:20:26</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>01h 16min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -3403,11 +3403,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2097800</v>
+        <v>2097806</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3417,27 +3417,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:28</t>
+          <t>02/03/2026 07:34:23</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:59</t>
+          <t>02/03/2026 07:38:38</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:28</t>
+          <t>02/03/2026 07:34:23</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>01h 02min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -3463,11 +3463,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2097804</v>
+        <v>2097826</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Favoe encerrar o MDFe do veículo: QXI3I84</t>
+          <t>Re: cte 6920</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Rodrigues Silva da Anunciação</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:25</t>
+          <t>02/03/2026 08:04:25</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:30:56</t>
+          <t>02/03/2026 08:05:09</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:25</t>
+          <t>02/03/2026 08:04:25</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>52min</t>
+          <t>22min</t>
         </is>
       </c>
     </row>
@@ -3523,11 +3523,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2097819</v>
+        <v>2097837</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3537,27 +3537,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Placa FPK5D43 Desagregado </t>
+          <t>ENC: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>leonardo Pedroso Horita</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:23</t>
+          <t>02/03/2026 08:15:25</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:59:53</t>
+          <t>02/03/2026 08:16:40</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:23</t>
+          <t>02/03/2026 08:15:25</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>23min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -3583,11 +3583,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2097821</v>
+        <v>2097822</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3597,27 +3597,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020002 NF- 627244</t>
+          <t>RES: cte 6920</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Victor Oliveira Lamy</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:23</t>
+          <t>02/03/2026 07:58:25</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:01:21</t>
+          <t>02/03/2026 07:58:36</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:23</t>
+          <t>02/03/2026 07:58:25</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>22min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -3643,41 +3643,41 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2097782</v>
+        <v>2097778</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve">RES: INFORMAÇÕES PARA EMISSÃO DE CTE  </t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:23</t>
+          <t>02/03/2026 06:14:23</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:25:37</t>
+          <t>02/03/2026 07:57:42</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:23</t>
+          <t>02/03/2026 06:14:23</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>29min</t>
         </is>
       </c>
     </row>
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2097823</v>
+        <v>2097791</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3717,27 +3717,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2602280029 NF- 627224</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:02:23</t>
+          <t>02/03/2026 07:06:25</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:12</t>
+          <t>02/03/2026 07:07:30</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:02:24</t>
+          <t>02/03/2026 07:06:25</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>01h 19min</t>
         </is>
       </c>
     </row>
@@ -3763,41 +3763,41 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2097755</v>
+        <v>2097800</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
+          <t>ENC: CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:46:23</t>
+          <t>02/03/2026 07:20:28</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:52</t>
+          <t>02/03/2026 07:20:59</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:46:23</t>
+          <t>02/03/2026 07:20:28</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>01h 06min</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2097798</v>
+        <v>2097835</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151038 - Série: 1</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3847,17 +3847,17 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:25</t>
+          <t>02/03/2026 08:14:26</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:57</t>
+          <t>02/03/2026 08:18:17</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:25</t>
+          <t>02/03/2026 08:14:26</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>01h 02min</t>
+          <t>09min</t>
         </is>
       </c>
     </row>
@@ -3883,41 +3883,41 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>2097832</v>
+        <v>2097755</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:29</t>
+          <t>02/03/2026 04:46:23</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:09:09</t>
+          <t>02/03/2026 07:38:52</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:29</t>
+          <t>02/03/2026 04:46:23</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>14min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -3943,11 +3943,11 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>2097810</v>
+        <v>2097797</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3957,27 +3957,27 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:25</t>
+          <t>02/03/2026 07:20:23</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:46</t>
+          <t>02/03/2026 07:26:44</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:25</t>
+          <t>02/03/2026 07:20:24</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>40min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -4003,11 +4003,11 @@
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>2097837</v>
+        <v>2097823</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -4017,27 +4017,27 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:25</t>
+          <t>02/03/2026 08:02:23</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:40</t>
+          <t>02/03/2026 08:08:12</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:25</t>
+          <t>02/03/2026 08:02:24</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>06min</t>
+          <t>19min</t>
         </is>
       </c>
     </row>
@@ -4063,41 +4063,41 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>2097825</v>
+        <v>2097782</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.557 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:23</t>
+          <t>02/03/2026 06:56:23</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:10</t>
+          <t>02/03/2026 07:25:37</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:23</t>
+          <t>02/03/2026 06:56:23</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>18min</t>
+          <t>01h 01min</t>
         </is>
       </c>
     </row>
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>2097822</v>
+        <v>2097783</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -4137,27 +4137,27 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>RES: cte 6920</t>
+          <t>ENC: CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Victor Oliveira Lamy</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:25</t>
+          <t>02/03/2026 06:56:24</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:36</t>
+          <t>02/03/2026 06:59:51</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:25</t>
+          <t>02/03/2026 06:56:24</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>01h 27min</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>2097801</v>
+        <v>2097802</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>RES: REEMBOLSO SEM PARAR - BENS 2025/2026</t>
+          <t>Reembolso_Pedágio_Coca_Fevereiro</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:22:25</t>
+          <t>02/03/2026 07:24:23</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:07:56</t>
+          <t>02/03/2026 08:07:52</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:22:25</t>
+          <t>02/03/2026 07:24:23</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>19min</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2097802</v>
+        <v>2097801</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Reembolso_Pedágio_Coca_Fevereiro</t>
+          <t>RES: REEMBOLSO SEM PARAR - BENS 2025/2026</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:23</t>
+          <t>02/03/2026 07:22:25</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:07:52</t>
+          <t>02/03/2026 08:07:56</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:23</t>
+          <t>02/03/2026 07:22:25</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>19min</t>
         </is>
       </c>
     </row>
@@ -4473,11 +4473,11 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>2097730</v>
+        <v>2097696</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4487,27 +4487,27 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151066 - Série: 1</t>
+          <t>CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:58:24</t>
+          <t>02/03/2026 00:36:23</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:54</t>
+          <t>02/03/2026 00:49:30</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:58:24</t>
+          <t>02/03/2026 00:36:23</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>05h 20min</t>
+          <t>07h 37min</t>
         </is>
       </c>
     </row>
@@ -4533,11 +4533,11 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2097740</v>
+        <v>2097767</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4547,27 +4547,27 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151079 - Série: 1</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:23</t>
+          <t>02/03/2026 05:20:24</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:12</t>
+          <t>02/03/2026 05:22:43</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:23</t>
+          <t>02/03/2026 05:20:24</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>04h 05min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -4593,11 +4593,11 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>2097720</v>
+        <v>2097764</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4607,27 +4607,27 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:25</t>
+          <t>02/03/2026 05:14:23</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:46</t>
+          <t>02/03/2026 05:22:35</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:25</t>
+          <t>02/03/2026 05:14:23</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>06h 16min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -4653,11 +4653,11 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>2097718</v>
+        <v>2097768</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4667,27 +4667,27 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:24</t>
+          <t>02/03/2026 05:24:23</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:58:00</t>
+          <t>02/03/2026 05:44:34</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:24</t>
+          <t>02/03/2026 05:24:23</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>06h 25min</t>
+          <t>02h 42min</t>
         </is>
       </c>
     </row>
@@ -4713,11 +4713,11 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
-        <v>2097737</v>
+        <v>2097733</v>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4727,27 +4727,27 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:25</t>
+          <t>02/03/2026 03:08:25</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:26</t>
+          <t>02/03/2026 03:11:40</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:25</t>
+          <t>02/03/2026 03:08:25</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>04h 21min</t>
+          <t>05h 15min</t>
         </is>
       </c>
     </row>
@@ -4773,11 +4773,11 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>2097729</v>
+        <v>2097724</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4787,27 +4787,27 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:25</t>
+          <t>02/03/2026 02:28:28</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:51:37</t>
+          <t>02/03/2026 02:29:44</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:25</t>
+          <t>02/03/2026 02:28:28</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>05h 31min</t>
+          <t>05h 57min</t>
         </is>
       </c>
     </row>
@@ -4833,11 +4833,11 @@
         </is>
       </c>
       <c r="B84" s="4" t="n">
-        <v>2097742</v>
+        <v>2097705</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4847,27 +4847,27 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo IXR2D00</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:48:23</t>
+          <t>02/03/2026 01:14:26</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:05</t>
+          <t>02/03/2026 01:21:00</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:48:23</t>
+          <t>02/03/2026 01:14:26</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>07h 06min</t>
         </is>
       </c>
     </row>
@@ -4893,11 +4893,11 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
-        <v>2097768</v>
+        <v>2097779</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4907,27 +4907,27 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:23</t>
+          <t>02/03/2026 06:16:23</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:44:34</t>
+          <t>02/03/2026 06:25:20</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:23</t>
+          <t>02/03/2026 06:16:23</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>02h 02min</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>2097772</v>
+        <v>2097715</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:26</t>
+          <t>02/03/2026 01:50:25</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:36:49</t>
+          <t>02/03/2026 01:52:50</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:26</t>
+          <t>02/03/2026 01:50:25</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>06h 34min</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="B87" s="4" t="n">
-        <v>2097715</v>
+        <v>2097750</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -5037,17 +5037,17 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:25</t>
+          <t>02/03/2026 04:18:29</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:50</t>
+          <t>02/03/2026 04:18:44</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:25</t>
+          <t>02/03/2026 04:18:29</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>06h 30min</t>
+          <t>04h 08min</t>
         </is>
       </c>
     </row>
@@ -5073,11 +5073,11 @@
         </is>
       </c>
       <c r="B88" s="4" t="n">
-        <v>2097761</v>
+        <v>2097765</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5087,27 +5087,27 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:23</t>
+          <t>02/03/2026 05:14:27</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:20</t>
+          <t>02/03/2026 05:17:12</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:23</t>
+          <t>02/03/2026 05:14:27</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>03h 03min</t>
+          <t>03h 10min</t>
         </is>
       </c>
     </row>
@@ -5133,11 +5133,11 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>2097724</v>
+        <v>2097726</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -5147,27 +5147,27 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:28</t>
+          <t>02/03/2026 02:32:27</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:29:44</t>
+          <t>02/03/2026 02:35:25</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:28</t>
+          <t>02/03/2026 02:32:27</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>05h 53min</t>
+          <t>05h 52min</t>
         </is>
       </c>
     </row>
@@ -5193,11 +5193,11 @@
         </is>
       </c>
       <c r="B90" s="4" t="n">
-        <v>2097704</v>
+        <v>2097706</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -5207,27 +5207,27 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo BCY3J08</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:25</t>
+          <t>02/03/2026 01:16:23</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:19:15</t>
+          <t>02/03/2026 01:21:04</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:25</t>
+          <t>02/03/2026 01:16:23</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>07h 04min</t>
+          <t>07h 06min</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>2097709</v>
+        <v>2097694</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
+          <t>EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -5277,17 +5277,17 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:30:23</t>
+          <t>02/03/2026 00:26:24</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:31:49</t>
+          <t>02/03/2026 00:34:41</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:30:23</t>
+          <t>02/03/2026 00:26:25</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>06h 51min</t>
+          <t>07h 52min</t>
         </is>
       </c>
     </row>
@@ -5313,11 +5313,11 @@
         </is>
       </c>
       <c r="B92" s="4" t="n">
-        <v>2097756</v>
+        <v>2097720</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -5327,27 +5327,27 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:23</t>
+          <t>02/03/2026 02:00:25</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:56</t>
+          <t>02/03/2026 02:06:46</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:23</t>
+          <t>02/03/2026 02:00:25</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>03h 06min</t>
+          <t>06h 20min</t>
         </is>
       </c>
     </row>
@@ -5373,11 +5373,11 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>2097771</v>
+        <v>2097708</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -5387,27 +5387,27 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:24</t>
+          <t>02/03/2026 01:28:23</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:45:17</t>
+          <t>02/03/2026 01:28:35</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:24</t>
+          <t>02/03/2026 01:28:23</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>02h 38min</t>
+          <t>06h 58min</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>2097752</v>
+        <v>2097711</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:26</t>
+          <t>02/03/2026 01:36:24</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:37:54</t>
+          <t>02/03/2026 01:39:03</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:26</t>
+          <t>02/03/2026 01:36:24</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>06h 48min</t>
         </is>
       </c>
     </row>
@@ -5493,11 +5493,11 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>2097734</v>
+        <v>2097704</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5507,27 +5507,27 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:23</t>
+          <t>02/03/2026 01:14:25</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:17:57</t>
+          <t>02/03/2026 01:19:15</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:23</t>
+          <t>02/03/2026 01:14:25</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>04h 05min</t>
+          <t>07h 08min</t>
         </is>
       </c>
     </row>
@@ -5553,11 +5553,11 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>2097777</v>
+        <v>2097699</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>RES: INFORMAÇÕES PARA EMISSÃO DE CTE - 02/03/2026</t>
+          <t>ENC: CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:06:24</t>
+          <t>02/03/2026 00:54:26</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:59</t>
+          <t>02/03/2026 00:55:36</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:06:24</t>
+          <t>02/03/2026 00:54:26</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>02h 08min</t>
+          <t>07h 31min</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>2097700</v>
+        <v>2097743</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NORDESTE - ASR0C31</t>
+          <t>ENC: CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Gabriel  Molinari de Moraes</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:23</t>
+          <t>02/03/2026 03:50:24</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:19:09</t>
+          <t>02/03/2026 04:02:51</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:23</t>
+          <t>02/03/2026 03:50:24</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>07h 04min</t>
+          <t>04h 24min</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>2097770</v>
+        <v>2097702</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -5697,17 +5697,17 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:26</t>
+          <t>02/03/2026 01:06:26</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:36:41</t>
+          <t>02/03/2026 01:07:57</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:26</t>
+          <t>02/03/2026 01:06:26</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>07h 19min</t>
         </is>
       </c>
     </row>
@@ -5733,11 +5733,11 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>2097780</v>
+        <v>2097719</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5747,27 +5747,27 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020005 NF- 627250</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:18:23</t>
+          <t>02/03/2026 02:00:24</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:28:47</t>
+          <t>02/03/2026 02:06:39</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:18:23</t>
+          <t>02/03/2026 02:00:24</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>06h 20min</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5793,11 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>2097698</v>
+        <v>2097749</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5807,27 +5807,27 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:24</t>
+          <t>02/03/2026 04:18:25</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:58:42</t>
+          <t>02/03/2026 04:38:17</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:24</t>
+          <t>02/03/2026 04:18:25</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>07h 24min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -5853,11 +5853,11 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>2097735</v>
+        <v>2097776</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5867,27 +5867,27 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:25</t>
+          <t>02/03/2026 06:02:23</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:13:33</t>
+          <t>02/03/2026 06:13:38</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:25</t>
+          <t>02/03/2026 06:02:23</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>05h 10min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -5913,11 +5913,11 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>2097746</v>
+        <v>2097739</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5927,27 +5927,27 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Aceite de coleta PepsiCo</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:23</t>
+          <t>02/03/2026 03:42:25</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:35</t>
+          <t>02/03/2026 04:02:35</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:23</t>
+          <t>02/03/2026 03:42:25</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>04h 24min</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="B103" s="4" t="n">
-        <v>2097702</v>
+        <v>2097759</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:26</t>
+          <t>02/03/2026 04:52:29</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:07:57</t>
+          <t>02/03/2026 04:55:28</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:26</t>
+          <t>02/03/2026 04:52:29</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>07h 15min</t>
+          <t>03h 31min</t>
         </is>
       </c>
     </row>
@@ -6033,11 +6033,11 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>2097712</v>
+        <v>2097752</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -6047,27 +6047,27 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:23</t>
+          <t>02/03/2026 04:34:26</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:34</t>
+          <t>02/03/2026 04:37:54</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:23</t>
+          <t>02/03/2026 04:34:26</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>06h 31min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>2097727</v>
+        <v>2097730</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151065 - Série: 1</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151066 - Série: 1</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -6117,17 +6117,17 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:42:23</t>
+          <t>02/03/2026 02:58:24</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:45:28</t>
+          <t>02/03/2026 03:02:54</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:42:23</t>
+          <t>02/03/2026 02:58:24</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>05h 38min</t>
+          <t>05h 24min</t>
         </is>
       </c>
     </row>
@@ -6153,11 +6153,11 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>2097710</v>
+        <v>2097772</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6167,27 +6167,27 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:23</t>
+          <t>02/03/2026 05:26:26</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:42</t>
+          <t>02/03/2026 05:36:49</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:23</t>
+          <t>02/03/2026 05:26:26</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>06h 38min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
@@ -6213,11 +6213,11 @@
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>2097769</v>
+        <v>2097735</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6227,27 +6227,27 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
+          <t>ENC: CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:24</t>
+          <t>02/03/2026 03:12:25</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:37:03</t>
+          <t>02/03/2026 03:13:33</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:24</t>
+          <t>02/03/2026 03:12:25</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>05h 13min</t>
         </is>
       </c>
     </row>
@@ -6273,11 +6273,11 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>2097707</v>
+        <v>2097731</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -6287,27 +6287,27 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
+          <t>CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:23</t>
+          <t>02/03/2026 03:02:23</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:40</t>
+          <t>02/03/2026 04:17:34</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:23</t>
+          <t>02/03/2026 03:02:23</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>06h 54min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -6333,11 +6333,11 @@
         </is>
       </c>
       <c r="B109" s="4" t="n">
-        <v>2097744</v>
+        <v>2097762</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -6347,27 +6347,27 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:23</t>
+          <t>02/03/2026 05:00:24</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:11</t>
+          <t>02/03/2026 05:02:47</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:23</t>
+          <t>02/03/2026 05:00:24</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>03h 24min</t>
         </is>
       </c>
     </row>
@@ -6393,11 +6393,11 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>2097758</v>
+        <v>2097769</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -6407,27 +6407,27 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:28</t>
+          <t>02/03/2026 05:24:24</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:17:01</t>
+          <t>02/03/2026 05:37:03</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:28</t>
+          <t>02/03/2026 05:24:24</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>03h 06min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>2097759</v>
+        <v>2097775</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:29</t>
+          <t>02/03/2026 05:50:25</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:55:28</t>
+          <t>02/03/2026 05:50:47</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:29</t>
+          <t>02/03/2026 05:50:25</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>03h 28min</t>
+          <t>02h 36min</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>2097721</v>
+        <v>2097770</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151037 - Série: 1</t>
+          <t>ENC: CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -6537,17 +6537,17 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:23</t>
+          <t>02/03/2026 05:24:26</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:10:16</t>
+          <t>02/03/2026 05:36:41</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:23</t>
+          <t>02/03/2026 05:24:26</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>06h 13min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
@@ -6573,11 +6573,11 @@
         </is>
       </c>
       <c r="B113" s="4" t="n">
-        <v>2097767</v>
+        <v>2097709</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -6587,27 +6587,27 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151079 - Série: 1</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:24</t>
+          <t>02/03/2026 01:30:23</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:22:43</t>
+          <t>02/03/2026 01:31:49</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:24</t>
+          <t>02/03/2026 01:30:23</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>06h 55min</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>2097764</v>
+        <v>2097716</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -6647,27 +6647,27 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:23</t>
+          <t>02/03/2026 01:54:23</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:22:35</t>
+          <t>02/03/2026 01:54:41</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:23</t>
+          <t>02/03/2026 01:54:23</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>06h 32min</t>
         </is>
       </c>
     </row>
@@ -6693,11 +6693,11 @@
         </is>
       </c>
       <c r="B115" s="4" t="n">
-        <v>2097705</v>
+        <v>2097757</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -6707,27 +6707,27 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo IXR2D00</t>
+          <t>ENC: CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:26</t>
+          <t>02/03/2026 04:52:26</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:21:00</t>
+          <t>02/03/2026 04:55:23</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:26</t>
+          <t>02/03/2026 04:52:26</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>07h 02min</t>
+          <t>03h 32min</t>
         </is>
       </c>
     </row>
@@ -6753,11 +6753,11 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>2097747</v>
+        <v>2097734</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6767,27 +6767,27 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:25</t>
+          <t>02/03/2026 03:12:23</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:03:15</t>
+          <t>02/03/2026 04:17:57</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:25</t>
+          <t>02/03/2026 03:12:23</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>04h 20min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B117" s="4" t="n">
-        <v>2097701</v>
+        <v>2097771</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -6827,27 +6827,27 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:25</t>
+          <t>02/03/2026 05:26:24</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:48</t>
+          <t>02/03/2026 05:45:17</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:25</t>
+          <t>02/03/2026 05:26:24</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>06h 58min</t>
+          <t>02h 42min</t>
         </is>
       </c>
     </row>
@@ -6873,11 +6873,11 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>2097714</v>
+        <v>2097700</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -6887,27 +6887,27 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NORDESTE - ASR0C31</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Gabriel  Molinari de Moraes</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:23</t>
+          <t>02/03/2026 01:06:23</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:41</t>
+          <t>02/03/2026 01:19:09</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:23</t>
+          <t>02/03/2026 01:06:23</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>06h 30min</t>
+          <t>07h 08min</t>
         </is>
       </c>
     </row>
@@ -6933,11 +6933,11 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>2097749</v>
+        <v>2097721</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -6947,27 +6947,27 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151037 - Série: 1</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:25</t>
+          <t>02/03/2026 02:06:23</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:17</t>
+          <t>02/03/2026 02:10:16</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:25</t>
+          <t>02/03/2026 02:06:23</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>06h 17min</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>2097711</v>
+        <v>2097727</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151065 - Série: 1</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -7017,17 +7017,17 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:24</t>
+          <t>02/03/2026 02:42:23</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:39:03</t>
+          <t>02/03/2026 02:45:28</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:24</t>
+          <t>02/03/2026 02:42:23</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>06h 44min</t>
+          <t>05h 41min</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="B121" s="4" t="n">
-        <v>2097731</v>
+        <v>2097738</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:23</t>
+          <t>02/03/2026 03:26:23</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:17:34</t>
+          <t>02/03/2026 04:18:05</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:23</t>
+          <t>02/03/2026 03:26:23</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -7113,11 +7113,11 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>2097765</v>
+        <v>2097722</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -7127,27 +7127,27 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo PPH8A77</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:27</t>
+          <t>02/03/2026 02:14:25</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:17:12</t>
+          <t>02/03/2026 02:16:29</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:27</t>
+          <t>02/03/2026 02:14:25</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>03h 06min</t>
+          <t>06h 10min</t>
         </is>
       </c>
     </row>
@@ -7173,11 +7173,11 @@
         </is>
       </c>
       <c r="B123" s="4" t="n">
-        <v>2097751</v>
+        <v>2097729</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -7187,27 +7187,27 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:23</t>
+          <t>02/03/2026 02:50:25</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:43:51</t>
+          <t>02/03/2026 02:51:37</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:23</t>
+          <t>02/03/2026 02:50:25</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>03h 39min</t>
+          <t>05h 35min</t>
         </is>
       </c>
     </row>
@@ -7233,11 +7233,11 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>2097706</v>
+        <v>2097761</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -7247,27 +7247,27 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo BCY3J08</t>
+          <t>CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:16:23</t>
+          <t>02/03/2026 05:00:23</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:21:04</t>
+          <t>02/03/2026 05:20:20</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:16:23</t>
+          <t>02/03/2026 05:00:23</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>07h 02min</t>
+          <t>03h 07min</t>
         </is>
       </c>
     </row>
@@ -7293,11 +7293,11 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
-        <v>2097694</v>
+        <v>2097777</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -7307,27 +7307,27 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
+          <t>RES: INFORMAÇÕES PARA EMISSÃO DE CTE - 02/03/2026</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:26:24</t>
+          <t>02/03/2026 06:06:24</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:34:41</t>
+          <t>02/03/2026 06:14:59</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:26:25</t>
+          <t>02/03/2026 06:06:24</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>07h 48min</t>
+          <t>02h 12min</t>
         </is>
       </c>
     </row>
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>2097750</v>
+        <v>2097774</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -7367,27 +7367,27 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:29</t>
+          <t>02/03/2026 05:50:23</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:44</t>
+          <t>02/03/2026 06:01:20</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:29</t>
+          <t>02/03/2026 05:50:23</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -7413,11 +7413,11 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
-        <v>2097726</v>
+        <v>2097760</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -7427,27 +7427,27 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:27</t>
+          <t>02/03/2026 04:54:23</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:35:25</t>
+          <t>02/03/2026 04:56:27</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:27</t>
+          <t>02/03/2026 04:54:23</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>05h 48min</t>
+          <t>03h 30min</t>
         </is>
       </c>
     </row>
@@ -7473,11 +7473,11 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>2097699</v>
+        <v>2097780</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -7487,27 +7487,27 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020005 NF- 627250</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:26</t>
+          <t>02/03/2026 06:18:23</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:55:36</t>
+          <t>02/03/2026 06:28:47</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:26</t>
+          <t>02/03/2026 06:18:23</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>07h 27min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -7533,11 +7533,11 @@
         </is>
       </c>
       <c r="B129" s="4" t="n">
-        <v>2097722</v>
+        <v>2097745</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -7547,27 +7547,27 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo PPH8A77</t>
+          <t>ENC: CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:14:25</t>
+          <t>02/03/2026 03:58:25</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:16:29</t>
+          <t>02/03/2026 04:03:05</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:14:25</t>
+          <t>02/03/2026 03:58:25</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>06h 07min</t>
+          <t>04h 24min</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>2097741</v>
+        <v>2097754</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -7617,17 +7617,17 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:25</t>
+          <t>02/03/2026 04:36:24</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:44</t>
+          <t>02/03/2026 04:37:59</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:25</t>
+          <t>02/03/2026 04:36:24</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>04h 20min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -7653,11 +7653,11 @@
         </is>
       </c>
       <c r="B131" s="4" t="n">
-        <v>2097697</v>
+        <v>2097695</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -7667,27 +7667,27 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:24</t>
+          <t>02/03/2026 00:30:25</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:43:23</t>
+          <t>02/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:24</t>
+          <t>02/03/2026 00:30:25</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>07h 40min</t>
+          <t>07h 44min</t>
         </is>
       </c>
     </row>
@@ -7713,11 +7713,11 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>2097743</v>
+        <v>2097701</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -7727,27 +7727,27 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:50:24</t>
+          <t>02/03/2026 01:06:25</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:51</t>
+          <t>02/03/2026 01:24:48</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:50:24</t>
+          <t>02/03/2026 01:06:25</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>04h 20min</t>
+          <t>07h 02min</t>
         </is>
       </c>
     </row>
@@ -7773,11 +7773,11 @@
         </is>
       </c>
       <c r="B133" s="4" t="n">
-        <v>2097766</v>
+        <v>2097712</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -7787,27 +7787,27 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151077 - Série: 1</t>
+          <t>CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:23</t>
+          <t>02/03/2026 01:44:23</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:50</t>
+          <t>02/03/2026 01:52:34</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:23</t>
+          <t>02/03/2026 01:44:23</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>03h 06min</t>
+          <t>06h 34min</t>
         </is>
       </c>
     </row>
@@ -7833,11 +7833,11 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>2097695</v>
+        <v>2097713</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -7847,27 +7847,27 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
+          <t>ENC: CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:30:25</t>
+          <t>02/03/2026 01:44:25</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:43:18</t>
+          <t>02/03/2026 01:45:50</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:30:25</t>
+          <t>02/03/2026 01:44:25</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>07h 40min</t>
+          <t>06h 41min</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
-        <v>2097719</v>
+        <v>2097714</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
@@ -7917,17 +7917,17 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:24</t>
+          <t>02/03/2026 01:50:23</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:39</t>
+          <t>02/03/2026 01:52:41</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:24</t>
+          <t>02/03/2026 01:50:23</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>06h 16min</t>
+          <t>06h 34min</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>2097713</v>
+        <v>2097718</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:25</t>
+          <t>02/03/2026 01:56:24</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:45:50</t>
+          <t>02/03/2026 01:58:00</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:25</t>
+          <t>02/03/2026 01:56:24</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>06h 37min</t>
+          <t>06h 29min</t>
         </is>
       </c>
     </row>
@@ -8013,11 +8013,11 @@
         </is>
       </c>
       <c r="B137" s="4" t="n">
-        <v>2097733</v>
+        <v>2097697</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -8027,27 +8027,27 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
+          <t>ENC: CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:08:25</t>
+          <t>02/03/2026 00:36:24</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:11:40</t>
+          <t>02/03/2026 00:43:23</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:08:25</t>
+          <t>02/03/2026 00:36:24</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>05h 11min</t>
+          <t>07h 44min</t>
         </is>
       </c>
     </row>
@@ -8073,11 +8073,11 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>2097779</v>
+        <v>2097710</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -8087,27 +8087,27 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:16:23</t>
+          <t>02/03/2026 01:36:23</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:25:20</t>
+          <t>02/03/2026 01:44:42</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:16:23</t>
+          <t>02/03/2026 01:36:23</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>06h 42min</t>
         </is>
       </c>
     </row>
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="B139" s="4" t="n">
-        <v>2097717</v>
+        <v>2097707</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -8147,27 +8147,27 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:23</t>
+          <t>02/03/2026 01:24:23</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:32</t>
+          <t>02/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:23</t>
+          <t>02/03/2026 01:24:23</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>06h 17min</t>
+          <t>06h 58min</t>
         </is>
       </c>
     </row>
@@ -8193,11 +8193,11 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>2097736</v>
+        <v>2097753</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -8207,27 +8207,27 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo PCQ2I98</t>
+          <t>CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:23</t>
+          <t>02/03/2026 04:36:23</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:06:06</t>
+          <t>02/03/2026 04:43:57</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:23</t>
+          <t>02/03/2026 04:36:23</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>03h 43min</t>
         </is>
       </c>
     </row>
@@ -8253,11 +8253,11 @@
         </is>
       </c>
       <c r="B141" s="4" t="n">
-        <v>2097776</v>
+        <v>2097758</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -8267,27 +8267,27 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:02:23</t>
+          <t>02/03/2026 04:52:28</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:13:38</t>
+          <t>02/03/2026 05:17:01</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:02:23</t>
+          <t>02/03/2026 04:52:28</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>03h 10min</t>
         </is>
       </c>
     </row>
@@ -8313,11 +8313,11 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>2097762</v>
+        <v>2097698</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -8327,27 +8327,27 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:24</t>
+          <t>02/03/2026 00:54:24</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:02:47</t>
+          <t>02/03/2026 00:58:42</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:24</t>
+          <t>02/03/2026 00:54:24</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>03h 20min</t>
+          <t>07h 28min</t>
         </is>
       </c>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="B143" s="4" t="n">
-        <v>2097738</v>
+        <v>2097766</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -8387,27 +8387,27 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151077 - Série: 1</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:26:23</t>
+          <t>02/03/2026 05:16:23</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:05</t>
+          <t>02/03/2026 05:16:50</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:26:23</t>
+          <t>02/03/2026 05:16:23</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>04h 05min</t>
+          <t>03h 10min</t>
         </is>
       </c>
     </row>
@@ -8433,11 +8433,11 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>2097775</v>
+        <v>2097740</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -8447,27 +8447,27 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:25</t>
+          <t>02/03/2026 03:44:23</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:47</t>
+          <t>02/03/2026 04:18:12</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:25</t>
+          <t>02/03/2026 03:44:23</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>02h 32min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -8493,11 +8493,11 @@
         </is>
       </c>
       <c r="B145" s="4" t="n">
-        <v>2097753</v>
+        <v>2097741</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -8507,27 +8507,27 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:23</t>
+          <t>02/03/2026 03:44:25</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:43:57</t>
+          <t>02/03/2026 04:02:44</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:23</t>
+          <t>02/03/2026 03:44:25</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>03h 39min</t>
+          <t>04h 24min</t>
         </is>
       </c>
     </row>
@@ -8553,11 +8553,11 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>2097757</v>
+        <v>2097746</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -8567,27 +8567,27 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:26</t>
+          <t>02/03/2026 04:00:23</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:55:23</t>
+          <t>02/03/2026 04:18:35</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:26</t>
+          <t>02/03/2026 04:00:23</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>03h 28min</t>
+          <t>04h 08min</t>
         </is>
       </c>
     </row>
@@ -8613,11 +8613,11 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
-        <v>2097696</v>
+        <v>2097747</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -8627,27 +8627,27 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:23</t>
+          <t>02/03/2026 04:00:25</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:49:30</t>
+          <t>02/03/2026 04:03:15</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:23</t>
+          <t>02/03/2026 04:00:25</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>07h 34min</t>
+          <t>04h 24min</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>2097708</v>
+        <v>2097717</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -8687,27 +8687,27 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:23</t>
+          <t>02/03/2026 01:56:23</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:35</t>
+          <t>02/03/2026 02:06:32</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:23</t>
+          <t>02/03/2026 01:56:23</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>06h 54min</t>
+          <t>06h 20min</t>
         </is>
       </c>
     </row>
@@ -8733,11 +8733,11 @@
         </is>
       </c>
       <c r="B149" s="4" t="n">
-        <v>2097732</v>
+        <v>2097736</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -8747,27 +8747,27 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo PCQ2I98</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:25</t>
+          <t>02/03/2026 03:24:23</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:11:45</t>
+          <t>02/03/2026 04:06:06</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:25</t>
+          <t>02/03/2026 03:24:23</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>05h 11min</t>
+          <t>04h 21min</t>
         </is>
       </c>
     </row>
@@ -8793,11 +8793,11 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>2097774</v>
+        <v>2097737</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -8807,27 +8807,27 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:23</t>
+          <t>02/03/2026 03:24:25</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:01:20</t>
+          <t>02/03/2026 04:02:26</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:23</t>
+          <t>02/03/2026 03:24:25</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>04h 24min</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="B151" s="4" t="n">
-        <v>2097739</v>
+        <v>2097732</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>ENC: Aceite de coleta PepsiCo</t>
+          <t>ENC: CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -8877,17 +8877,17 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:42:25</t>
+          <t>02/03/2026 03:02:25</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:35</t>
+          <t>02/03/2026 03:11:45</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:42:25</t>
+          <t>02/03/2026 03:02:25</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>04h 20min</t>
+          <t>05h 15min</t>
         </is>
       </c>
     </row>
@@ -8913,11 +8913,11 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>2097760</v>
+        <v>2097742</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -8927,27 +8927,27 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
+          <t>CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:54:23</t>
+          <t>02/03/2026 03:48:23</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:56:27</t>
+          <t>02/03/2026 04:38:05</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:54:23</t>
+          <t>02/03/2026 03:48:23</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>03h 27min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>2097716</v>
+        <v>2097744</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
@@ -8987,27 +8987,27 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:23</t>
+          <t>02/03/2026 03:58:23</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:41</t>
+          <t>02/03/2026 04:38:11</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:23</t>
+          <t>02/03/2026 03:58:23</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>06h 28min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -9033,11 +9033,11 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>2097745</v>
+        <v>2097756</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -9047,27 +9047,27 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:25</t>
+          <t>02/03/2026 04:52:23</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:03:05</t>
+          <t>02/03/2026 05:16:56</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:25</t>
+          <t>02/03/2026 04:52:23</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>04h 20min</t>
+          <t>03h 10min</t>
         </is>
       </c>
     </row>
@@ -9093,11 +9093,11 @@
         </is>
       </c>
       <c r="B155" s="4" t="n">
-        <v>2097754</v>
+        <v>2097751</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -9107,27 +9107,27 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:24</t>
+          <t>02/03/2026 04:34:23</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:37:59</t>
+          <t>02/03/2026 04:43:51</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:24</t>
+          <t>02/03/2026 04:34:23</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>03h 43min</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9325,11 +9325,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2097842</v>
+        <v>2097838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>ANTONIO CARLOS DE PAULA SOARES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9339,28 +9339,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: A51540 - CRT </t>
+          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>Priscila Eredes da Silva Lourenço</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 01 Min</t>
+          <t xml:space="preserve"> 00 Hs 09 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>01min</t>
+          <t>09min</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 03 Min</t>
+          <t xml:space="preserve"> 00 Hs 07 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>03min</t>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -9437,11 +9437,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2097841</v>
+        <v>2097844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9451,23 +9451,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151084 - Série: 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ingrid de Sousa Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:28</t>
+          <t>02/03/2026 08:22:25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:28</t>
+          <t>02/03/2026 08:22:25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -9493,11 +9493,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2097836</v>
+        <v>2097842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9507,28 +9507,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve">RES: A51540 - CRT </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Matheus Braz de Moura</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:23</t>
+          <t>02/03/2026 08:20:23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:23</t>
+          <t>02/03/2026 08:20:23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 06 Min</t>
+          <t xml:space="preserve"> 00 Hs 05 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>06min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -9549,11 +9549,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2097838</v>
+        <v>2097843</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS DE PAULA SOARES</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9563,23 +9563,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
+          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Priscila Eredes da Silva Lourenço</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:20:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:20:25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -9605,11 +9605,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2097843</v>
+        <v>2097841</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9624,23 +9624,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>Ingrid de Sousa Costa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:25</t>
+          <t>02/03/2026 08:18:28</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:25</t>
+          <t>02/03/2026 08:18:28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 01 Min</t>
+          <t xml:space="preserve"> 00 Hs 06 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01min</t>
+          <t>06min</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 11 Min</t>
+          <t xml:space="preserve"> 00 Hs 15 Min</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -9717,11 +9717,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2097834</v>
+        <v>2097836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9731,28 +9731,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT EXTREMA  155402/155401</t>
+          <t>CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabriel Henrique Baptista Santos</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:25</t>
+          <t>02/03/2026 08:15:23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:25</t>
+          <t>02/03/2026 08:15:23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 07 Min</t>
+          <t xml:space="preserve"> 00 Hs 10 Min</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>00min</t>
         </is>
       </c>
     </row>
@@ -9773,11 +9773,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2097839</v>
+        <v>2097834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9787,38 +9787,94 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ENC: Solicitação de coleta: ARGENTINA - PEÇAS - Fatura: 266677</t>
+          <t>EMISSÃO RECKITT EXTREMA  155402/155401</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>Gabriel Henrique Baptista Santos</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:25</t>
+          <t>02/03/2026 08:14:25</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>02/03/2026 08:14:25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 11 Min</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>08min</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2097839</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MERCOSUL - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENC: Solicitação de coleta: ARGENTINA - PEÇAS - Fatura: 266677</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Matheus Braz de Moura</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>02/03/2026 08:18:25</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 03 Min</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:18:25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 07 Min</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>03min</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>06min</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9977,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -9931,42 +9987,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2097725</v>
+        <v>2097723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:25</t>
+          <t>02/03/2026 02:28:25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:25</t>
+          <t>02/03/2026 02:28:25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 05 Hs 49 Min</t>
+          <t xml:space="preserve"> 05 Hs 57 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -9976,11 +10032,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05h 42min</t>
+          <t>05h 48min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -9990,7 +10046,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2097728</v>
+        <v>2097703</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -10004,7 +10060,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -10014,18 +10070,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:23</t>
+          <t>02/03/2026 01:12:23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:23</t>
+          <t>02/03/2026 01:12:23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 05 Hs 31 Min</t>
+          <t xml:space="preserve"> 07 Hs 13 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10035,11 +10091,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>07h 00min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -10049,42 +10105,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2097723</v>
+        <v>2097728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENC: CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:25</t>
+          <t>02/03/2026 02:50:23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:25</t>
+          <t>02/03/2026 02:50:23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 05 Hs 53 Min</t>
+          <t xml:space="preserve"> 05 Hs 35 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -10094,11 +10150,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05h 45min</t>
+          <t>04h 16min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -10108,7 +10164,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2097703</v>
+        <v>2097725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -10122,7 +10178,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -10132,18 +10188,18 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02/03/2026 01:12:23</t>
+          <t>02/03/2026 02:32:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>02/03/2026 01:12:23</t>
+          <t>02/03/2026 02:32:25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 07 Hs 09 Min</t>
+          <t xml:space="preserve"> 05 Hs 53 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -10153,11 +10209,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>06h 57min</t>
+          <t>05h 45min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -10176,7 +10232,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -10195,7 +10251,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -10214,7 +10270,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -10235,13 +10291,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -10254,13 +10310,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -10273,13 +10329,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -10292,7 +10348,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -10313,7 +10369,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -10332,7 +10388,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -10351,7 +10407,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -10370,13 +10426,13 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -10389,13 +10445,13 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -10408,13 +10464,13 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -10427,7 +10483,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10687,17 +10743,17 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2m 36s</t>
+          <t>3m 0s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2097834</v>
+        <v>2097836</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT EXTREMA  155402/155401</t>
+          <t>CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Henrique Baptista Santos</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:25</t>
+          <t>02/03/2026 08:15:23</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:27:28</t>
+          <t>02/03/2026 08:31:58</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:25</t>
+          <t>02/03/2026 08:15:23</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>06min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2097836</v>
+        <v>2097834</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT EXTREMA  155402/155401</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Gabriel Henrique Baptista Santos</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:23</t>
+          <t>02/03/2026 08:14:25</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:31:58</t>
+          <t>02/03/2026 08:27:28</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:23</t>
+          <t>02/03/2026 08:14:25</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2097831</v>
+        <v>2097848</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve">PEDÁGIO AVULSO - CYN2C57 </t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:27</t>
+          <t>02/03/2026 08:30:25</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:00</t>
+          <t>02/03/2026 08:37:51</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:27</t>
+          <t>02/03/2026 08:30:25</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>00min</t>
         </is>
       </c>
     </row>
@@ -942,30 +942,74 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>22min</t>
+          <t>25min</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
+        <v>2097831</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:08:27</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:17:00</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:08:27</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>21min</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr"/>
       <c r="B8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr"/>
@@ -981,7 +1025,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr"/>
@@ -994,70 +1038,26 @@
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Responsável: HERICA LIDIA BARBOSA SILVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>2097781</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>FILIAL MOGI</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PEDÁGIO AVULSO - EQU3D45 </t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 06:50:23</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:01:12</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 06:50:23</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>01h 33min</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2097811</v>
+        <v>2097805</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2603020003 NF- 627246</t>
+          <t>RES: emissão Reckitt SHI2602280019 NF- 627205</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:23</t>
+          <t>02/03/2026 07:28:26</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:25</t>
+          <t>02/03/2026 07:33:20</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:23</t>
+          <t>02/03/2026 07:28:26</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>01h 05min</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2097805</v>
+        <v>2097811</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>RES: emissão Reckitt SHI2602280019 NF- 627205</t>
+          <t>emissão Reckitt SHI2603020003 NF- 627246</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:26</t>
+          <t>02/03/2026 07:42:23</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:33:20</t>
+          <t>02/03/2026 07:57:25</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:26</t>
+          <t>02/03/2026 07:42:23</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 01min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -1188,11 +1188,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2097830</v>
+        <v>2097781</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1202,27 +1202,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EXTREMA - VIAGEM SHI2602270088 NF 155399</t>
+          <t xml:space="preserve">PEDÁGIO AVULSO - EQU3D45 </t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:26</t>
+          <t>02/03/2026 06:50:23</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:55</t>
+          <t>02/03/2026 07:01:12</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:26</t>
+          <t>02/03/2026 06:50:23</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>01h 37min</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2097818</v>
+        <v>2097786</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -1262,27 +1262,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2602280035 NF- 627236</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270032 NF 155379</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:52:23</t>
+          <t>02/03/2026 07:00:25</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:11:44</t>
+          <t>02/03/2026 07:16:56</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:52:23</t>
+          <t>02/03/2026 07:00:25</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>22min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2097787</v>
+        <v>2097814</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280004 NF- 627182</t>
+          <t>emissão Reckitt SHI2602280037 NF- 627240</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:27</t>
+          <t>02/03/2026 07:46:23</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:47</t>
+          <t>02/03/2026 08:04:05</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:27</t>
+          <t>02/03/2026 07:46:23</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>01h 09min</t>
+          <t>34min</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2097793</v>
+        <v>2097787</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2603020004 NF- 627248</t>
+          <t>emissão Reckitt SHI2602280004 NF- 627182</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:25</t>
+          <t>02/03/2026 07:00:27</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:29:22</t>
+          <t>02/03/2026 07:24:47</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:25</t>
+          <t>02/03/2026 07:00:27</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>01h 05min</t>
+          <t>01h 13min</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2097803</v>
+        <v>2097830</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270046 NF 155394</t>
+          <t>EMISSÃO RECKITT -  HUB X EXTREMA - VIAGEM SHI2602270088 NF 155399</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:23</t>
+          <t>02/03/2026 08:08:26</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:39:46</t>
+          <t>02/03/2026 08:17:55</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:23</t>
+          <t>02/03/2026 08:08:26</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>54min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2097814</v>
+        <v>2097793</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280037 NF- 627240</t>
+          <t>emissão Reckitt SHI2603020004 NF- 627248</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:46:23</t>
+          <t>02/03/2026 07:18:25</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:05</t>
+          <t>02/03/2026 07:29:22</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:46:23</t>
+          <t>02/03/2026 07:18:25</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>30min</t>
+          <t>01h 09min</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2097786</v>
+        <v>2097803</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270032 NF 155379</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270046 NF 155394</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:25</t>
+          <t>02/03/2026 07:28:23</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:16:56</t>
+          <t>02/03/2026 07:39:46</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:25</t>
+          <t>02/03/2026 07:28:23</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1597,25 +1597,69 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>01h 17min</t>
+          <t>58min</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B21" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
+        <v>2097818</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>RECKITT</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> emissão Reckitt SHI2602280035 NF- 627236</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Daniela da Cruz Moreira</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 07:52:23</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:11:44</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 07:52:23</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>26min</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="inlineStr"/>
@@ -1649,70 +1693,26 @@
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Responsável: LUANA CRISTINE SA DOS SANTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>2097797</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Motor de Emissão - nstech</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:20:23</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:26:44</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:20:24</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>01h 07min</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2097813</v>
+        <v>2097798</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1747,17 +1747,17 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:25</t>
+          <t>02/03/2026 07:20:25</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:45:04</t>
+          <t>02/03/2026 07:20:57</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:25</t>
+          <t>02/03/2026 07:20:25</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>49min</t>
+          <t>01h 17min</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1843,41 +1843,41 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2097773</v>
+        <v>2097796</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
+          <t>ENC: CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:28:25</t>
+          <t>02/03/2026 07:18:29</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:49:01</t>
+          <t>02/03/2026 07:19:39</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:28:25</t>
+          <t>02/03/2026 07:18:29</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>45min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2097855</v>
+        <v>2097835</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151085 - Série: 1</t>
+          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151038 - Série: 1</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:27</t>
+          <t>02/03/2026 08:14:26</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:33</t>
+          <t>02/03/2026 08:18:17</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:27</t>
+          <t>02/03/2026 08:14:26</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -1963,41 +1963,41 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2097782</v>
+        <v>2097837</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:23</t>
+          <t>02/03/2026 08:15:25</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:25:37</t>
+          <t>02/03/2026 08:16:40</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:23</t>
+          <t>02/03/2026 08:15:25</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 08min</t>
+          <t>21min</t>
         </is>
       </c>
     </row>
@@ -2023,41 +2023,41 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2097790</v>
+        <v>2097778</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270120 NF 155391</t>
+          <t xml:space="preserve">RES: INFORMAÇÕES PARA EMISSÃO DE CTE  </t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:24</t>
+          <t>02/03/2026 06:14:23</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:07:27</t>
+          <t>02/03/2026 07:57:42</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:24</t>
+          <t>02/03/2026 06:14:23</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 27min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -2083,11 +2083,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2097791</v>
+        <v>2097807</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2602280029 NF- 627224</t>
+          <t>CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:25</t>
+          <t>02/03/2026 07:38:23</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:07:30</t>
+          <t>02/03/2026 07:50:22</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:25</t>
+          <t>02/03/2026 07:38:23</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>01h 27min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2097839</v>
+        <v>2097832</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2157,27 +2157,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: Solicitação de coleta: ARGENTINA - PEÇAS - Fatura: 266677</t>
+          <t>ENC: CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:25</t>
+          <t>02/03/2026 08:08:29</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:26</t>
+          <t>02/03/2026 08:09:09</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:25</t>
+          <t>02/03/2026 08:08:29</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>29min</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2097798</v>
+        <v>2097850</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Relatório White</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:25</t>
+          <t>02/03/2026 08:30:28</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:57</t>
+          <t>02/03/2026 08:30:41</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:25</t>
+          <t>02/03/2026 08:30:28</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>01h 13min</t>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2097792</v>
+        <v>2097788</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
@@ -2277,27 +2277,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280019 NF- 627205</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270105 NF 155387</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:10:23</t>
+          <t>02/03/2026 07:02:23</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:11:44</t>
+          <t>02/03/2026 07:05:21</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:10:23</t>
+          <t>02/03/2026 07:02:23</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>01h 22min</t>
+          <t>01h 33min</t>
         </is>
       </c>
     </row>
@@ -2323,41 +2323,41 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2097748</v>
+        <v>2097821</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>RES: 13065319 ALEXANDRE HERMES PEREIRA IAP5D29 GIX4D54</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020002 NF- 627244</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:10:25</t>
+          <t>02/03/2026 07:58:23</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:33:33</t>
+          <t>02/03/2026 08:01:21</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:10:25</t>
+          <t>02/03/2026 07:58:23</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>01h 01min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -2383,41 +2383,41 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2097794</v>
+        <v>2097812</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: PEDÁGIO AVULSO - EQU3D45 </t>
+          <t>CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:26</t>
+          <t>02/03/2026 07:44:23</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:19:44</t>
+          <t>02/03/2026 08:17:52</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:26</t>
+          <t>02/03/2026 07:44:23</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>01h 14min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -2443,11 +2443,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2097804</v>
+        <v>2097816</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2457,27 +2457,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Favoe encerrar o MDFe do veículo: QXI3I84</t>
+          <t>CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Rodrigues Silva da Anunciação</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:25</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:30:56</t>
+          <t>02/03/2026 07:57:25</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:25</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -2503,11 +2503,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2097822</v>
+        <v>2097817</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2517,27 +2517,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>RES: cte 6920</t>
+          <t>ENC: CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Victor Oliveira Lamy</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:25</t>
+          <t>02/03/2026 07:50:24</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:36</t>
+          <t>02/03/2026 07:50:47</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:25</t>
+          <t>02/03/2026 07:50:24</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>47min</t>
         </is>
       </c>
     </row>
@@ -2563,11 +2563,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2097823</v>
+        <v>2097792</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2577,27 +2577,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+          <t>emissão Reckitt SHI2602280019 NF- 627205</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:02:23</t>
+          <t>02/03/2026 07:10:23</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:12</t>
+          <t>02/03/2026 07:11:44</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:02:24</t>
+          <t>02/03/2026 07:10:23</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>01h 26min</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2097807</v>
+        <v>2097809</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:23</t>
+          <t>02/03/2026 07:40:23</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:22</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:23</t>
+          <t>02/03/2026 07:40:23</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2097832</v>
+        <v>2097826</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2697,27 +2697,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Re: cte 6920</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:29</t>
+          <t>02/03/2026 08:04:25</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:09:09</t>
+          <t>02/03/2026 08:05:09</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:29</t>
+          <t>02/03/2026 08:04:25</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>25min</t>
+          <t>33min</t>
         </is>
       </c>
     </row>
@@ -2743,41 +2743,41 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2097809</v>
+        <v>2097763</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:23</t>
+          <t>02/03/2026 05:00:26</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 07:45:00</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:23</t>
+          <t>02/03/2026 05:00:26</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>53min</t>
         </is>
       </c>
     </row>
@@ -2803,11 +2803,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2097827</v>
+        <v>2097842</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2817,27 +2817,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020001 NF- 627242</t>
+          <t xml:space="preserve">RES: A51540 - CRT </t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Matheus Braz de Moura</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:26</t>
+          <t>02/03/2026 08:20:23</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:07</t>
+          <t>02/03/2026 08:33:44</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:26</t>
+          <t>02/03/2026 08:20:23</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -2863,11 +2863,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2097821</v>
+        <v>2097844</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2877,27 +2877,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020002 NF- 627244</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151084 - Série: 1</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:23</t>
+          <t>02/03/2026 08:22:25</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:01:21</t>
+          <t>02/03/2026 08:30:20</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:23</t>
+          <t>02/03/2026 08:22:25</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>08min</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2097837</v>
+        <v>2097783</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:25</t>
+          <t>02/03/2026 06:56:24</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:40</t>
+          <t>02/03/2026 06:59:51</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:25</t>
+          <t>02/03/2026 06:56:24</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -2983,11 +2983,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2097806</v>
+        <v>2097797</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2997,27 +2997,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:34:23</t>
+          <t>02/03/2026 07:20:23</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:38</t>
+          <t>02/03/2026 07:26:44</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:34:23</t>
+          <t>02/03/2026 07:20:24</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>01h 11min</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2097810</v>
+        <v>2097800</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:25</t>
+          <t>02/03/2026 07:20:28</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:46</t>
+          <t>02/03/2026 07:20:59</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:25</t>
+          <t>02/03/2026 07:20:28</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>01h 17min</t>
         </is>
       </c>
     </row>
@@ -3103,11 +3103,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2097820</v>
+        <v>2097810</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>RITMO - SEGUROS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RES: Emissão CT-e manual- Ritmo</t>
+          <t>ENC: CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Adrian Bitencourt</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:25</t>
+          <t>02/03/2026 07:40:25</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:57</t>
+          <t>02/03/2026 07:42:46</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:25</t>
+          <t>02/03/2026 07:40:25</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>55min</t>
         </is>
       </c>
     </row>
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2097783</v>
+        <v>2097820</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RITMO - SEGUROS</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3177,27 +3177,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emissão CT-e manual- Ritmo</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Adrian Bitencourt</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:24</t>
+          <t>02/03/2026 07:56:25</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:59:51</t>
+          <t>02/03/2026 08:16:57</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:24</t>
+          <t>02/03/2026 07:56:25</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>21min</t>
         </is>
       </c>
     </row>
@@ -3223,41 +3223,41 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2097755</v>
+        <v>2097823</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
+          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:46:23</t>
+          <t>02/03/2026 08:02:23</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:52</t>
+          <t>02/03/2026 08:08:12</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:46:23</t>
+          <t>02/03/2026 08:02:24</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -3283,11 +3283,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2097799</v>
+        <v>2097815</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3297,27 +3297,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Favor encerrar o MDFe do veículo: QXI0C85</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Eduardo Rodrigues Silva da Anunciação</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:26</t>
+          <t>02/03/2026 07:48:23</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:45</t>
+          <t>02/03/2026 07:50:46</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:26</t>
+          <t>02/03/2026 07:48:23</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>47min</t>
         </is>
       </c>
     </row>
@@ -3343,41 +3343,41 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2097812</v>
+        <v>2097794</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve">RES: PEDÁGIO AVULSO - EQU3D45 </t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:23</t>
+          <t>02/03/2026 07:18:26</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:52</t>
+          <t>02/03/2026 07:19:44</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:23</t>
+          <t>02/03/2026 07:18:26</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -3403,11 +3403,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2097817</v>
+        <v>2097806</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3417,27 +3417,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:24</t>
+          <t>02/03/2026 07:34:23</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:47</t>
+          <t>02/03/2026 07:38:38</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:24</t>
+          <t>02/03/2026 07:34:23</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>43min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2097788</v>
+        <v>2097827</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
@@ -3477,27 +3477,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270105 NF 155387</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020001 NF- 627242</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:23</t>
+          <t>02/03/2026 08:04:26</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:05:21</t>
+          <t>02/03/2026 08:05:07</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:23</t>
+          <t>02/03/2026 08:04:26</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>33min</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -3583,41 +3583,41 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2097842</v>
+        <v>2097782</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: A51540 - CRT </t>
+          <t>CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 06:56:23</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:33:44</t>
+          <t>02/03/2026 07:25:37</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 06:56:23</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>01h 12min</t>
         </is>
       </c>
     </row>
@@ -3643,41 +3643,41 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2097825</v>
+        <v>2097784</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.557 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:23</t>
+          <t>02/03/2026 06:56:26</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:10</t>
+          <t>02/03/2026 07:24:19</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:23</t>
+          <t>02/03/2026 06:56:26</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2097826</v>
+        <v>2097813</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3717,27 +3717,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Re: cte 6920</t>
+          <t>ENC: CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:25</t>
+          <t>02/03/2026 07:44:25</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:09</t>
+          <t>02/03/2026 07:45:04</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:25</t>
+          <t>02/03/2026 07:44:25</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>53min</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2097763</v>
+        <v>2097773</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:26</t>
+          <t>02/03/2026 05:28:25</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:45:00</t>
+          <t>02/03/2026 07:49:01</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:26</t>
+          <t>02/03/2026 05:28:25</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3823,41 +3823,41 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2097844</v>
+        <v>2097748</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151084 - Série: 1</t>
+          <t>RES: 13065319 ALEXANDRE HERMES PEREIRA IAP5D29 GIX4D54</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:22:25</t>
+          <t>02/03/2026 04:10:25</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:20</t>
+          <t>02/03/2026 07:33:33</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:22:25</t>
+          <t>02/03/2026 04:10:25</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>01h 04min</t>
         </is>
       </c>
     </row>
@@ -3883,41 +3883,41 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>2097784</v>
+        <v>2097795</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:26</t>
+          <t>02/03/2026 07:18:28</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:19</t>
+          <t>02/03/2026 07:26:42</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:26</t>
+          <t>02/03/2026 07:18:28</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>01h 11min</t>
         </is>
       </c>
     </row>
@@ -3943,11 +3943,11 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>2097815</v>
+        <v>2097819</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3957,27 +3957,27 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Favor encerrar o MDFe do veículo: QXI0C85</t>
+          <t xml:space="preserve">RES: Placa FPK5D43 Desagregado </t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Rodrigues Silva da Anunciação</t>
+          <t>leonardo Pedroso Horita</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:48:23</t>
+          <t>02/03/2026 07:56:23</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:46</t>
+          <t>02/03/2026 07:59:53</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:48:23</t>
+          <t>02/03/2026 07:56:23</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>43min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -4003,11 +4003,11 @@
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>2097800</v>
+        <v>2097789</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -4017,27 +4017,27 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270121 NF 155393</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:28</t>
+          <t>02/03/2026 07:02:25</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:59</t>
+          <t>02/03/2026 07:06:57</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:28</t>
+          <t>02/03/2026 07:02:25</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>01h 13min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -4063,11 +4063,11 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>2097795</v>
+        <v>2097822</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -4077,27 +4077,27 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: cte 6920</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Victor Oliveira Lamy</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:28</t>
+          <t>02/03/2026 07:58:25</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:42</t>
+          <t>02/03/2026 07:58:36</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:28</t>
+          <t>02/03/2026 07:58:25</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>39min</t>
         </is>
       </c>
     </row>
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>2097819</v>
+        <v>2097785</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -4137,27 +4137,27 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Placa FPK5D43 Desagregado </t>
+          <t>ENC: CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>leonardo Pedroso Horita</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:23</t>
+          <t>02/03/2026 06:56:27</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:59:53</t>
+          <t>02/03/2026 06:59:53</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:23</t>
+          <t>02/03/2026 06:56:27</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -4183,41 +4183,41 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>2097850</v>
+        <v>2097755</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>ENC: Relatório White</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:28</t>
+          <t>02/03/2026 04:46:23</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:41</t>
+          <t>02/03/2026 07:38:52</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:28</t>
+          <t>02/03/2026 04:46:23</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>03min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -4243,11 +4243,11 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>2097789</v>
+        <v>2097799</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -4257,27 +4257,27 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270121 NF 155393</t>
+          <t>CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:25</t>
+          <t>02/03/2026 07:20:26</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:57</t>
+          <t>02/03/2026 07:26:45</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:25</t>
+          <t>02/03/2026 07:20:26</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>01h 27min</t>
+          <t>01h 11min</t>
         </is>
       </c>
     </row>
@@ -4303,11 +4303,11 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>2097835</v>
+        <v>2097804</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -4317,27 +4317,27 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151038 - Série: 1</t>
+          <t>Favoe encerrar o MDFe do veículo: QXI3I84</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Eduardo Rodrigues Silva da Anunciação</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:26</t>
+          <t>02/03/2026 07:28:25</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:17</t>
+          <t>02/03/2026 07:30:56</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:26</t>
+          <t>02/03/2026 07:28:25</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>01h 07min</t>
         </is>
       </c>
     </row>
@@ -4363,41 +4363,41 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>2097778</v>
+        <v>2097825</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: INFORMAÇÕES PARA EMISSÃO DE CTE  </t>
+          <t>ENC: CT-e: 000.046.557 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:23</t>
+          <t>02/03/2026 08:04:23</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:42</t>
+          <t>02/03/2026 08:05:10</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:23</t>
+          <t>02/03/2026 08:04:23</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>36min</t>
+          <t>33min</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>2097785</v>
+        <v>2097855</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151085 - Série: 1</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4447,17 +4447,17 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:27</t>
+          <t>02/03/2026 08:32:27</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:59:53</t>
+          <t>02/03/2026 08:32:33</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:27</t>
+          <t>02/03/2026 08:32:27</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -4483,11 +4483,11 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>2097816</v>
+        <v>2097790</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -4497,27 +4497,27 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270120 NF 155391</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 07:06:24</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:25</t>
+          <t>02/03/2026 07:07:27</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 07:06:24</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>01h 30min</t>
         </is>
       </c>
     </row>
@@ -4543,11 +4543,11 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2097796</v>
+        <v>2097791</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -4557,27 +4557,27 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2602280029 NF- 627224</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:29</t>
+          <t>02/03/2026 07:06:25</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:19:39</t>
+          <t>02/03/2026 07:07:30</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:29</t>
+          <t>02/03/2026 07:06:25</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4592,25 +4592,69 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>01h 14min</t>
+          <t>01h 30min</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="4" t="inlineStr"/>
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B74" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr"/>
-      <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr"/>
+        <v>2097839</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>MERCOSUL - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>ENC: Solicitação de coleta: ARGENTINA - PEÇAS - Fatura: 266677</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Matheus Braz de Moura</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:18:25</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:32:26</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:18:25</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>05min</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="4" t="inlineStr"/>
@@ -4644,70 +4688,26 @@
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr"/>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="4" t="inlineStr"/>
+      <c r="B77" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="inlineStr"/>
+      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Responsável: MELISSA MARIA CALEFFI ZECHINI</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>2097802</v>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>AGREGADOS</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Reembolso_Pedágio_Coca_Fevereiro</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Beatriz Treiss Rodrigues</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:24:23</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 08:07:52</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:24:23</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>26min</t>
         </is>
       </c>
     </row>
@@ -4718,11 +4718,11 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2097829</v>
+        <v>2097801</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>AGREGADOS</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4732,27 +4732,27 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Desagregações Fevereiro </t>
+          <t>RES: REEMBOLSO SEM PARAR - BENS 2025/2026</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Saulo Henrique Oliveira de Souza</t>
+          <t>Beatriz Treiss Rodrigues</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:25</t>
+          <t>02/03/2026 07:22:25</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:30</t>
+          <t>02/03/2026 08:07:56</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:25</t>
+          <t>02/03/2026 07:22:25</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -4778,74 +4778,118 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>2097801</v>
+        <v>2097829</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
+          <t>FILIAL MARILIA</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RES: Desagregações Fevereiro </t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Saulo Henrique Oliveira de Souza</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:06:25</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:10:30</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:06:25</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>27min</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n">
+        <v>2097802</v>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
           <t>AGREGADOS</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>RES: REEMBOLSO SEM PARAR - BENS 2025/2026</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Reembolso_Pedágio_Coca_Fevereiro</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>Beatriz Treiss Rodrigues</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:22:25</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 08:07:56</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 07:22:25</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>26min</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="4" t="inlineStr"/>
-      <c r="B81" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
-      <c r="D81" s="4" t="inlineStr"/>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr"/>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
-      <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 07:24:23</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:07:52</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 07:24:23</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>30min</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="4" t="inlineStr"/>
@@ -4879,70 +4923,26 @@
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
     </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="4" t="inlineStr"/>
+      <c r="B84" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr"/>
+      <c r="L84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Responsável: OXANA ANDRELI DA SILVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="n">
-        <v>2097730</v>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>SPAL JUNDIAÍ</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151066 - Série: 1</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>XML Femsa</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 02:58:24</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 03:02:54</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 02:58:24</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>05h 31min</t>
         </is>
       </c>
     </row>
@@ -4953,11 +4953,11 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>2097727</v>
+        <v>2097734</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4967,27 +4967,27 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151065 - Série: 1</t>
+          <t>CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:42:23</t>
+          <t>02/03/2026 03:12:23</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:45:28</t>
+          <t>02/03/2026 04:17:57</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:42:23</t>
+          <t>02/03/2026 03:12:23</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>05h 49min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="B87" s="4" t="n">
-        <v>2097750</v>
+        <v>2097772</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -5037,17 +5037,17 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:29</t>
+          <t>02/03/2026 05:26:26</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:44</t>
+          <t>02/03/2026 05:36:49</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:29</t>
+          <t>02/03/2026 05:26:26</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>04h 15min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
@@ -5073,11 +5073,11 @@
         </is>
       </c>
       <c r="B88" s="4" t="n">
-        <v>2097710</v>
+        <v>2097694</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -5087,27 +5087,27 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:23</t>
+          <t>02/03/2026 00:26:24</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:42</t>
+          <t>02/03/2026 00:34:41</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:23</t>
+          <t>02/03/2026 00:26:25</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>06h 49min</t>
+          <t>08h 03min</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>2097770</v>
+        <v>2097767</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151079 - Série: 1</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -5157,17 +5157,17 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:26</t>
+          <t>02/03/2026 05:20:24</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:36:41</t>
+          <t>02/03/2026 05:22:43</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:26</t>
+          <t>02/03/2026 05:20:24</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -5193,11 +5193,11 @@
         </is>
       </c>
       <c r="B90" s="4" t="n">
-        <v>2097744</v>
+        <v>2097776</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -5207,27 +5207,27 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:23</t>
+          <t>02/03/2026 06:02:23</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:11</t>
+          <t>02/03/2026 06:13:38</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:23</t>
+          <t>02/03/2026 06:02:23</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>03h 56min</t>
+          <t>02h 24min</t>
         </is>
       </c>
     </row>
@@ -5253,11 +5253,11 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>2097745</v>
+        <v>2097708</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5267,27 +5267,27 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:25</t>
+          <t>02/03/2026 01:28:23</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:03:05</t>
+          <t>02/03/2026 01:28:35</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:25</t>
+          <t>02/03/2026 01:28:23</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>04h 31min</t>
+          <t>07h 09min</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B92" s="4" t="n">
-        <v>2097698</v>
+        <v>2097731</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:24</t>
+          <t>02/03/2026 03:02:23</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:58:42</t>
+          <t>02/03/2026 04:17:34</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:24</t>
+          <t>02/03/2026 03:02:23</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>07h 35min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>2097743</v>
+        <v>2097732</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:50:24</t>
+          <t>02/03/2026 03:02:25</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:51</t>
+          <t>02/03/2026 03:11:45</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:50:24</t>
+          <t>02/03/2026 03:02:25</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>04h 31min</t>
+          <t>05h 26min</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>2097714</v>
+        <v>2097768</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
@@ -5447,27 +5447,27 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:23</t>
+          <t>02/03/2026 05:24:23</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:41</t>
+          <t>02/03/2026 05:44:34</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:23</t>
+          <t>02/03/2026 05:24:23</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>06h 41min</t>
+          <t>02h 53min</t>
         </is>
       </c>
     </row>
@@ -5493,11 +5493,11 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>2097731</v>
+        <v>2097744</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5507,27 +5507,27 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:23</t>
+          <t>02/03/2026 03:58:23</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:17:34</t>
+          <t>02/03/2026 04:38:11</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:23</t>
+          <t>02/03/2026 03:58:23</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>04h 00min</t>
         </is>
       </c>
     </row>
@@ -5553,11 +5553,11 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>2097774</v>
+        <v>2097757</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:23</t>
+          <t>02/03/2026 04:52:26</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:01:20</t>
+          <t>02/03/2026 04:55:23</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:23</t>
+          <t>02/03/2026 04:52:26</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>03h 43min</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>2097758</v>
+        <v>2097699</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:28</t>
+          <t>02/03/2026 00:54:26</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:17:01</t>
+          <t>02/03/2026 00:55:36</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:28</t>
+          <t>02/03/2026 00:54:26</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>03h 17min</t>
+          <t>07h 42min</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>2097726</v>
+        <v>2097747</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -5697,17 +5697,17 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:27</t>
+          <t>02/03/2026 04:00:25</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:35:25</t>
+          <t>02/03/2026 04:03:15</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:27</t>
+          <t>02/03/2026 04:00:25</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>05h 59min</t>
+          <t>04h 35min</t>
         </is>
       </c>
     </row>
@@ -5733,11 +5733,11 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>2097752</v>
+        <v>2097695</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5747,27 +5747,27 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:26</t>
+          <t>02/03/2026 00:30:25</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:37:54</t>
+          <t>02/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:26</t>
+          <t>02/03/2026 00:30:25</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>03h 56min</t>
+          <t>07h 55min</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5793,11 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>2097706</v>
+        <v>2097700</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5807,27 +5807,27 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo BCY3J08</t>
+          <t>MANIFESTAR NORDESTE - ASR0C31</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>Gabriel  Molinari de Moraes</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:16:23</t>
+          <t>02/03/2026 01:06:23</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:21:04</t>
+          <t>02/03/2026 01:19:09</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:16:23</t>
+          <t>02/03/2026 01:06:23</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>07h 13min</t>
+          <t>07h 19min</t>
         </is>
       </c>
     </row>
@@ -5853,11 +5853,11 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>2097772</v>
+        <v>2097717</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5867,27 +5867,27 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:26</t>
+          <t>02/03/2026 01:56:23</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:36:49</t>
+          <t>02/03/2026 02:06:32</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:26</t>
+          <t>02/03/2026 01:56:23</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>06h 31min</t>
         </is>
       </c>
     </row>
@@ -5913,11 +5913,11 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>2097766</v>
+        <v>2097696</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5927,27 +5927,27 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151077 - Série: 1</t>
+          <t>CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:23</t>
+          <t>02/03/2026 00:36:23</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:50</t>
+          <t>02/03/2026 00:49:30</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:23</t>
+          <t>02/03/2026 00:36:23</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>03h 17min</t>
+          <t>07h 48min</t>
         </is>
       </c>
     </row>
@@ -5973,11 +5973,11 @@
         </is>
       </c>
       <c r="B103" s="4" t="n">
-        <v>2097746</v>
+        <v>2097737</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5987,27 +5987,27 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:23</t>
+          <t>02/03/2026 03:24:25</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:35</t>
+          <t>02/03/2026 04:02:26</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:23</t>
+          <t>02/03/2026 03:24:25</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>04h 15min</t>
+          <t>04h 35min</t>
         </is>
       </c>
     </row>
@@ -6033,11 +6033,11 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>2097701</v>
+        <v>2097710</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -6047,27 +6047,27 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:25</t>
+          <t>02/03/2026 01:36:23</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:48</t>
+          <t>02/03/2026 01:44:42</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:25</t>
+          <t>02/03/2026 01:36:23</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>07h 09min</t>
+          <t>06h 53min</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>2097721</v>
+        <v>2097762</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151037 - Série: 1</t>
+          <t>ENC: CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -6117,17 +6117,17 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:23</t>
+          <t>02/03/2026 05:00:24</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:10:16</t>
+          <t>02/03/2026 05:02:47</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:23</t>
+          <t>02/03/2026 05:00:24</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>06h 24min</t>
+          <t>03h 35min</t>
         </is>
       </c>
     </row>
@@ -6153,11 +6153,11 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>2097717</v>
+        <v>2097764</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6167,27 +6167,27 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:23</t>
+          <t>02/03/2026 05:14:23</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:32</t>
+          <t>02/03/2026 05:22:35</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:23</t>
+          <t>02/03/2026 05:14:23</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>06h 28min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -6213,11 +6213,11 @@
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>2097737</v>
+        <v>2097769</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6227,27 +6227,27 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:25</t>
+          <t>02/03/2026 05:24:24</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:26</t>
+          <t>02/03/2026 05:37:03</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:25</t>
+          <t>02/03/2026 05:24:24</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>04h 32min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
@@ -6273,11 +6273,11 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>2097738</v>
+        <v>2097733</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -6287,27 +6287,27 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:26:23</t>
+          <t>02/03/2026 03:08:25</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:05</t>
+          <t>02/03/2026 03:11:40</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:26:23</t>
+          <t>02/03/2026 03:08:25</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>04h 16min</t>
+          <t>05h 26min</t>
         </is>
       </c>
     </row>
@@ -6333,11 +6333,11 @@
         </is>
       </c>
       <c r="B109" s="4" t="n">
-        <v>2097776</v>
+        <v>2097777</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -6347,27 +6347,27 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>RES: INFORMAÇÕES PARA EMISSÃO DE CTE - 02/03/2026</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:02:23</t>
+          <t>02/03/2026 06:06:24</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:13:38</t>
+          <t>02/03/2026 06:14:59</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:02:23</t>
+          <t>02/03/2026 06:06:24</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>02h 23min</t>
         </is>
       </c>
     </row>
@@ -6393,11 +6393,11 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>2097732</v>
+        <v>2097705</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -6407,27 +6407,27 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo IXR2D00</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:25</t>
+          <t>02/03/2026 01:14:26</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:11:45</t>
+          <t>02/03/2026 01:21:00</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:25</t>
+          <t>02/03/2026 01:14:26</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>05h 22min</t>
+          <t>07h 17min</t>
         </is>
       </c>
     </row>
@@ -6453,11 +6453,11 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>2097764</v>
+        <v>2097709</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -6467,27 +6467,27 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:23</t>
+          <t>02/03/2026 01:30:23</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:22:35</t>
+          <t>02/03/2026 01:31:49</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:23</t>
+          <t>02/03/2026 01:30:23</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>03h 11min</t>
+          <t>07h 06min</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>2097704</v>
+        <v>2097727</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151065 - Série: 1</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -6537,17 +6537,17 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:25</t>
+          <t>02/03/2026 02:42:23</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:19:15</t>
+          <t>02/03/2026 02:45:28</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:25</t>
+          <t>02/03/2026 02:42:23</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>07h 15min</t>
+          <t>05h 52min</t>
         </is>
       </c>
     </row>
@@ -6573,11 +6573,11 @@
         </is>
       </c>
       <c r="B113" s="4" t="n">
-        <v>2097756</v>
+        <v>2097736</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -6587,27 +6587,27 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo PCQ2I98</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:23</t>
+          <t>02/03/2026 03:24:23</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:56</t>
+          <t>02/03/2026 04:06:06</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:23</t>
+          <t>02/03/2026 03:24:23</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>03h 17min</t>
+          <t>04h 32min</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>2097771</v>
+        <v>2097729</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -6647,27 +6647,27 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:24</t>
+          <t>02/03/2026 02:50:25</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:45:17</t>
+          <t>02/03/2026 02:51:37</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:24</t>
+          <t>02/03/2026 02:50:25</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>02h 49min</t>
+          <t>05h 46min</t>
         </is>
       </c>
     </row>
@@ -6693,11 +6693,11 @@
         </is>
       </c>
       <c r="B115" s="4" t="n">
-        <v>2097720</v>
+        <v>2097758</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -6707,27 +6707,27 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:25</t>
+          <t>02/03/2026 04:52:28</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:46</t>
+          <t>02/03/2026 05:17:01</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:25</t>
+          <t>02/03/2026 04:52:28</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>06h 27min</t>
+          <t>03h 21min</t>
         </is>
       </c>
     </row>
@@ -6753,11 +6753,11 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>2097742</v>
+        <v>2097743</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6767,27 +6767,27 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:48:23</t>
+          <t>02/03/2026 03:50:24</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:05</t>
+          <t>02/03/2026 04:02:51</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:48:23</t>
+          <t>02/03/2026 03:50:24</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>03h 56min</t>
+          <t>04h 35min</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="B117" s="4" t="n">
-        <v>2097775</v>
+        <v>2097735</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -6837,17 +6837,17 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:25</t>
+          <t>02/03/2026 03:12:25</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:47</t>
+          <t>02/03/2026 03:13:33</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:25</t>
+          <t>02/03/2026 03:12:25</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>02h 43min</t>
+          <t>05h 24min</t>
         </is>
       </c>
     </row>
@@ -6873,11 +6873,11 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>2097751</v>
+        <v>2097720</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -6887,27 +6887,27 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:23</t>
+          <t>02/03/2026 02:00:25</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:43:51</t>
+          <t>02/03/2026 02:06:46</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:23</t>
+          <t>02/03/2026 02:00:25</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>03h 50min</t>
+          <t>06h 31min</t>
         </is>
       </c>
     </row>
@@ -6933,11 +6933,11 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>2097734</v>
+        <v>2097760</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -6947,27 +6947,27 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:23</t>
+          <t>02/03/2026 04:54:23</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:17:57</t>
+          <t>02/03/2026 04:56:27</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:23</t>
+          <t>02/03/2026 04:54:23</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>04h 16min</t>
+          <t>03h 41min</t>
         </is>
       </c>
     </row>
@@ -6993,11 +6993,11 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>2097700</v>
+        <v>2097707</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -7007,27 +7007,27 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NORDESTE - ASR0C31</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Gabriel  Molinari de Moraes</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:23</t>
+          <t>02/03/2026 01:24:23</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:19:09</t>
+          <t>02/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:23</t>
+          <t>02/03/2026 01:24:23</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>07h 15min</t>
+          <t>07h 09min</t>
         </is>
       </c>
     </row>
@@ -7053,11 +7053,11 @@
         </is>
       </c>
       <c r="B121" s="4" t="n">
-        <v>2097715</v>
+        <v>2097779</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -7067,27 +7067,27 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:25</t>
+          <t>02/03/2026 06:16:23</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:50</t>
+          <t>02/03/2026 06:25:20</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:25</t>
+          <t>02/03/2026 06:16:23</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>06h 41min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -7113,11 +7113,11 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>2097696</v>
+        <v>2097754</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -7127,27 +7127,27 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:23</t>
+          <t>02/03/2026 04:36:24</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:49:30</t>
+          <t>02/03/2026 04:37:59</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:23</t>
+          <t>02/03/2026 04:36:24</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>07h 45min</t>
+          <t>04h 00min</t>
         </is>
       </c>
     </row>
@@ -7173,11 +7173,11 @@
         </is>
       </c>
       <c r="B123" s="4" t="n">
-        <v>2097697</v>
+        <v>2097756</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -7187,27 +7187,27 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:24</t>
+          <t>02/03/2026 04:52:23</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:43:23</t>
+          <t>02/03/2026 05:16:56</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:24</t>
+          <t>02/03/2026 04:52:23</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>07h 51min</t>
+          <t>03h 21min</t>
         </is>
       </c>
     </row>
@@ -7233,11 +7233,11 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>2097708</v>
+        <v>2097730</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -7247,27 +7247,27 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151066 - Série: 1</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:23</t>
+          <t>02/03/2026 02:58:24</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:35</t>
+          <t>02/03/2026 03:02:54</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:23</t>
+          <t>02/03/2026 02:58:24</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>07h 05min</t>
+          <t>05h 35min</t>
         </is>
       </c>
     </row>
@@ -7293,11 +7293,11 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
-        <v>2097761</v>
+        <v>2097740</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -7307,27 +7307,27 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:23</t>
+          <t>02/03/2026 03:44:23</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:20</t>
+          <t>02/03/2026 04:18:12</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:23</t>
+          <t>02/03/2026 03:44:23</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>03h 14min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>2097769</v>
+        <v>2097741</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -7367,27 +7367,27 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
+          <t>ENC: CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:24</t>
+          <t>02/03/2026 03:44:25</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:37:03</t>
+          <t>02/03/2026 04:02:44</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:24</t>
+          <t>02/03/2026 03:44:25</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>04h 35min</t>
         </is>
       </c>
     </row>
@@ -7413,11 +7413,11 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
-        <v>2097733</v>
+        <v>2097701</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -7427,27 +7427,27 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
+          <t>CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:08:25</t>
+          <t>02/03/2026 01:06:25</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:11:40</t>
+          <t>02/03/2026 01:24:48</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:08:25</t>
+          <t>02/03/2026 01:06:25</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>05h 22min</t>
+          <t>07h 13min</t>
         </is>
       </c>
     </row>
@@ -7473,11 +7473,11 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>2097777</v>
+        <v>2097719</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -7487,27 +7487,27 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>RES: INFORMAÇÕES PARA EMISSÃO DE CTE - 02/03/2026</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:06:24</t>
+          <t>02/03/2026 02:00:24</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:59</t>
+          <t>02/03/2026 02:06:39</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:06:24</t>
+          <t>02/03/2026 02:00:24</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>02h 19min</t>
+          <t>06h 31min</t>
         </is>
       </c>
     </row>
@@ -7533,11 +7533,11 @@
         </is>
       </c>
       <c r="B129" s="4" t="n">
-        <v>2097760</v>
+        <v>2097715</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -7547,27 +7547,27 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:54:23</t>
+          <t>02/03/2026 01:50:25</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:56:27</t>
+          <t>02/03/2026 01:52:50</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:54:23</t>
+          <t>02/03/2026 01:50:25</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>03h 38min</t>
+          <t>06h 45min</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>2097705</v>
+        <v>2097722</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo IXR2D00</t>
+          <t>encerramento da MDF-e do veículo PPH8A77</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -7617,17 +7617,17 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:26</t>
+          <t>02/03/2026 02:14:25</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:21:00</t>
+          <t>02/03/2026 02:16:29</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:26</t>
+          <t>02/03/2026 02:14:25</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>07h 13min</t>
+          <t>06h 21min</t>
         </is>
       </c>
     </row>
@@ -7653,11 +7653,11 @@
         </is>
       </c>
       <c r="B131" s="4" t="n">
-        <v>2097709</v>
+        <v>2097765</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -7667,27 +7667,27 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
+          <t>ENC: CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:30:23</t>
+          <t>02/03/2026 05:14:27</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:31:49</t>
+          <t>02/03/2026 05:17:12</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:30:23</t>
+          <t>02/03/2026 05:14:27</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>07h 02min</t>
+          <t>03h 21min</t>
         </is>
       </c>
     </row>
@@ -7713,11 +7713,11 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>2097740</v>
+        <v>2097774</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -7727,27 +7727,27 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:23</t>
+          <t>02/03/2026 05:50:23</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:12</t>
+          <t>02/03/2026 06:01:20</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:23</t>
+          <t>02/03/2026 05:50:23</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>04h 16min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="B133" s="4" t="n">
-        <v>2097719</v>
+        <v>2097716</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
@@ -7787,27 +7787,27 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:24</t>
+          <t>02/03/2026 01:54:23</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:39</t>
+          <t>02/03/2026 01:54:41</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:24</t>
+          <t>02/03/2026 01:54:23</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>06h 27min</t>
+          <t>06h 43min</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>2097749</v>
+        <v>2097751</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -7857,17 +7857,17 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:25</t>
+          <t>02/03/2026 04:34:23</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:17</t>
+          <t>02/03/2026 04:43:51</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:25</t>
+          <t>02/03/2026 04:34:23</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>03h 56min</t>
+          <t>03h 54min</t>
         </is>
       </c>
     </row>
@@ -7893,11 +7893,11 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
-        <v>2097729</v>
+        <v>2097698</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -7907,27 +7907,27 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:25</t>
+          <t>02/03/2026 00:54:24</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:51:37</t>
+          <t>02/03/2026 00:58:42</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:25</t>
+          <t>02/03/2026 00:54:24</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>05h 42min</t>
+          <t>07h 39min</t>
         </is>
       </c>
     </row>
@@ -7953,11 +7953,11 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>2097768</v>
+        <v>2097706</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -7967,27 +7967,27 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo BCY3J08</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:23</t>
+          <t>02/03/2026 01:16:23</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:44:34</t>
+          <t>02/03/2026 01:21:04</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:23</t>
+          <t>02/03/2026 01:16:23</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>07h 17min</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="B137" s="4" t="n">
-        <v>2097724</v>
+        <v>2097771</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -8037,17 +8037,17 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:28</t>
+          <t>02/03/2026 05:26:24</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:29:44</t>
+          <t>02/03/2026 05:45:17</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:28</t>
+          <t>02/03/2026 05:26:24</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>06h 04min</t>
+          <t>02h 53min</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>2097716</v>
+        <v>2097714</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
@@ -8087,27 +8087,27 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:23</t>
+          <t>02/03/2026 01:50:23</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:41</t>
+          <t>02/03/2026 01:52:41</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:23</t>
+          <t>02/03/2026 01:50:23</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>06h 39min</t>
+          <t>06h 45min</t>
         </is>
       </c>
     </row>
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="B139" s="4" t="n">
-        <v>2097779</v>
+        <v>2097718</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -8147,27 +8147,27 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>ENC: CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:16:23</t>
+          <t>02/03/2026 01:56:24</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:25:20</t>
+          <t>02/03/2026 01:58:00</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:16:23</t>
+          <t>02/03/2026 01:56:24</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>06h 40min</t>
         </is>
       </c>
     </row>
@@ -8193,11 +8193,11 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>2097757</v>
+        <v>2097738</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -8207,27 +8207,27 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:26</t>
+          <t>02/03/2026 03:26:23</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:55:23</t>
+          <t>02/03/2026 04:18:05</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:26</t>
+          <t>02/03/2026 03:26:23</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>03h 39min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B141" s="4" t="n">
-        <v>2097699</v>
+        <v>2097711</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -8277,17 +8277,17 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:26</t>
+          <t>02/03/2026 01:36:24</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:55:36</t>
+          <t>02/03/2026 01:39:03</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:26</t>
+          <t>02/03/2026 01:36:24</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>07h 38min</t>
+          <t>06h 59min</t>
         </is>
       </c>
     </row>
@@ -8313,11 +8313,11 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>2097735</v>
+        <v>2097742</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -8327,27 +8327,27 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:25</t>
+          <t>02/03/2026 03:48:23</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:13:33</t>
+          <t>02/03/2026 04:38:05</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:25</t>
+          <t>02/03/2026 03:48:23</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>05h 21min</t>
+          <t>04h 00min</t>
         </is>
       </c>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="B143" s="4" t="n">
-        <v>2097694</v>
+        <v>2097780</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -8387,27 +8387,27 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020005 NF- 627250</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:26:24</t>
+          <t>02/03/2026 06:18:23</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:34:41</t>
+          <t>02/03/2026 06:28:47</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:26:25</t>
+          <t>02/03/2026 06:18:23</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>07h 59min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -8433,11 +8433,11 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>2097736</v>
+        <v>2097745</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -8447,27 +8447,27 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo PCQ2I98</t>
+          <t>ENC: CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:23</t>
+          <t>02/03/2026 03:58:25</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:06:06</t>
+          <t>02/03/2026 04:03:05</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:23</t>
+          <t>02/03/2026 03:58:25</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>04h 28min</t>
+          <t>04h 35min</t>
         </is>
       </c>
     </row>
@@ -8493,11 +8493,11 @@
         </is>
       </c>
       <c r="B145" s="4" t="n">
-        <v>2097711</v>
+        <v>2097753</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -8507,27 +8507,27 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:24</t>
+          <t>02/03/2026 04:36:23</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:39:03</t>
+          <t>02/03/2026 04:43:57</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:24</t>
+          <t>02/03/2026 04:36:23</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>06h 55min</t>
+          <t>03h 54min</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>2097762</v>
+        <v>2097752</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -8577,17 +8577,17 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:24</t>
+          <t>02/03/2026 04:34:26</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:02:47</t>
+          <t>02/03/2026 04:37:54</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:24</t>
+          <t>02/03/2026 04:34:26</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>03h 31min</t>
+          <t>04h 00min</t>
         </is>
       </c>
     </row>
@@ -8613,11 +8613,11 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
-        <v>2097780</v>
+        <v>2097721</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -8627,27 +8627,27 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020005 NF- 627250</t>
+          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151037 - Série: 1</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:18:23</t>
+          <t>02/03/2026 02:06:23</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:28:47</t>
+          <t>02/03/2026 02:10:16</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:18:23</t>
+          <t>02/03/2026 02:06:23</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>06h 28min</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>2097753</v>
+        <v>2097749</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:23</t>
+          <t>02/03/2026 04:18:25</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:43:57</t>
+          <t>02/03/2026 04:38:17</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:23</t>
+          <t>02/03/2026 04:18:25</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>03h 50min</t>
+          <t>04h 00min</t>
         </is>
       </c>
     </row>
@@ -8733,11 +8733,11 @@
         </is>
       </c>
       <c r="B149" s="4" t="n">
-        <v>2097754</v>
+        <v>2097761</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -8747,27 +8747,27 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:24</t>
+          <t>02/03/2026 05:00:23</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:37:59</t>
+          <t>02/03/2026 05:20:20</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:24</t>
+          <t>02/03/2026 05:00:23</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>03h 56min</t>
+          <t>03h 18min</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>2097759</v>
+        <v>2097775</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -8817,17 +8817,17 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:29</t>
+          <t>02/03/2026 05:50:25</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:55:28</t>
+          <t>02/03/2026 05:50:47</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:29</t>
+          <t>02/03/2026 05:50:25</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>03h 39min</t>
+          <t>02h 47min</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="B151" s="4" t="n">
-        <v>2097741</v>
+        <v>2097704</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -8877,17 +8877,17 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:25</t>
+          <t>02/03/2026 01:14:25</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:44</t>
+          <t>02/03/2026 01:19:15</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:25</t>
+          <t>02/03/2026 01:14:25</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>04h 31min</t>
+          <t>07h 19min</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>2097747</v>
+        <v>2097726</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -8937,17 +8937,17 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:25</t>
+          <t>02/03/2026 02:32:27</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:03:15</t>
+          <t>02/03/2026 02:35:25</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:25</t>
+          <t>02/03/2026 02:32:27</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>04h 31min</t>
+          <t>06h 02min</t>
         </is>
       </c>
     </row>
@@ -8973,11 +8973,11 @@
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>2097695</v>
+        <v>2097766</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -8987,27 +8987,27 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151077 - Série: 1</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:30:25</t>
+          <t>02/03/2026 05:16:23</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:43:18</t>
+          <t>02/03/2026 05:16:50</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:30:25</t>
+          <t>02/03/2026 05:16:23</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>07h 51min</t>
+          <t>03h 21min</t>
         </is>
       </c>
     </row>
@@ -9033,11 +9033,11 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>2097702</v>
+        <v>2097746</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -9047,27 +9047,27 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:26</t>
+          <t>02/03/2026 04:00:23</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:07:57</t>
+          <t>02/03/2026 04:18:35</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:26</t>
+          <t>02/03/2026 04:00:23</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>07h 26min</t>
+          <t>04h 19min</t>
         </is>
       </c>
     </row>
@@ -9093,11 +9093,11 @@
         </is>
       </c>
       <c r="B155" s="4" t="n">
-        <v>2097712</v>
+        <v>2097702</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -9107,27 +9107,27 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:23</t>
+          <t>02/03/2026 01:06:26</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:34</t>
+          <t>02/03/2026 01:07:57</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:23</t>
+          <t>02/03/2026 01:06:26</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>06h 42min</t>
+          <t>07h 30min</t>
         </is>
       </c>
     </row>
@@ -9153,11 +9153,11 @@
         </is>
       </c>
       <c r="B156" s="4" t="n">
-        <v>2097713</v>
+        <v>2097712</v>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -9167,27 +9167,27 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:25</t>
+          <t>02/03/2026 01:44:23</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:45:50</t>
+          <t>02/03/2026 01:52:34</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:25</t>
+          <t>02/03/2026 01:44:23</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>06h 48min</t>
+          <t>06h 45min</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="B157" s="4" t="n">
-        <v>2097718</v>
+        <v>2097713</v>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:24</t>
+          <t>02/03/2026 01:44:25</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:58:00</t>
+          <t>02/03/2026 01:45:50</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:24</t>
+          <t>02/03/2026 01:44:25</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>06h 36min</t>
+          <t>06h 52min</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="B158" s="4" t="n">
-        <v>2097767</v>
+        <v>2097697</v>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151079 - Série: 1</t>
+          <t>ENC: CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -9297,17 +9297,17 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:24</t>
+          <t>02/03/2026 00:36:24</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:22:43</t>
+          <t>02/03/2026 00:43:23</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:24</t>
+          <t>02/03/2026 00:36:24</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>03h 11min</t>
+          <t>07h 55min</t>
         </is>
       </c>
     </row>
@@ -9333,11 +9333,11 @@
         </is>
       </c>
       <c r="B159" s="4" t="n">
-        <v>2097722</v>
+        <v>2097750</v>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -9347,27 +9347,27 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo PPH8A77</t>
+          <t>ENC: CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:14:25</t>
+          <t>02/03/2026 04:18:29</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:16:29</t>
+          <t>02/03/2026 04:18:44</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:14:25</t>
+          <t>02/03/2026 04:18:29</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>06h 18min</t>
+          <t>04h 19min</t>
         </is>
       </c>
     </row>
@@ -9393,11 +9393,11 @@
         </is>
       </c>
       <c r="B160" s="4" t="n">
-        <v>2097765</v>
+        <v>2097724</v>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -9407,27 +9407,27 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:27</t>
+          <t>02/03/2026 02:28:28</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:17:12</t>
+          <t>02/03/2026 02:29:44</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:27</t>
+          <t>02/03/2026 02:28:28</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>03h 17min</t>
+          <t>06h 08min</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>04h 31min</t>
+          <t>04h 35min</t>
         </is>
       </c>
     </row>
@@ -9513,11 +9513,11 @@
         </is>
       </c>
       <c r="B162" s="4" t="n">
-        <v>2097707</v>
+        <v>2097770</v>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -9527,27 +9527,27 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
+          <t>ENC: CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:23</t>
+          <t>02/03/2026 05:24:26</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:40</t>
+          <t>02/03/2026 05:36:41</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:23</t>
+          <t>02/03/2026 05:24:26</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -9562,25 +9562,69 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>07h 05min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="4" t="inlineStr"/>
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B163" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="C163" s="4" t="inlineStr"/>
-      <c r="D163" s="4" t="inlineStr"/>
-      <c r="E163" s="4" t="inlineStr"/>
-      <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr"/>
-      <c r="H163" s="4" t="inlineStr"/>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
-      <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr"/>
+        <v>2097759</v>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>ENC: CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>XML Femsa</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 04:52:29</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 04:55:28</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 04:52:29</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>03h 42min</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="4" t="inlineStr"/>
@@ -9614,70 +9658,26 @@
       <c r="K165" s="4" t="inlineStr"/>
       <c r="L165" s="4" t="inlineStr"/>
     </row>
-    <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="4" t="inlineStr"/>
+      <c r="B166" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="C166" s="4" t="inlineStr"/>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
+      <c r="F166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr"/>
+      <c r="K166" s="4" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Responsável: PAULO ROBERTO DA SILVA JUNIOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="n">
-        <v>2097845</v>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>CCR</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>Murilo Tiago de Oliveira Duarte</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 08:26:23</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 08:30:03</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>02/03/2026 08:26:23</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>04min</t>
         </is>
       </c>
     </row>
@@ -9688,11 +9688,11 @@
         </is>
       </c>
       <c r="B168" s="4" t="n">
-        <v>2097843</v>
+        <v>2097845</v>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -9707,22 +9707,22 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>Murilo Tiago de Oliveira Duarte</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:25</t>
+          <t>02/03/2026 08:26:23</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:24</t>
+          <t>02/03/2026 08:30:03</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:25</t>
+          <t>02/03/2026 08:26:23</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>08min</t>
         </is>
       </c>
     </row>
@@ -9797,25 +9797,69 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>08min</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="4" t="inlineStr"/>
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B170" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C170" s="4" t="inlineStr"/>
-      <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr"/>
-      <c r="F170" s="4" t="inlineStr"/>
-      <c r="G170" s="4" t="inlineStr"/>
-      <c r="H170" s="4" t="inlineStr"/>
-      <c r="I170" s="4" t="inlineStr"/>
-      <c r="J170" s="4" t="inlineStr"/>
-      <c r="K170" s="4" t="inlineStr"/>
-      <c r="L170" s="4" t="inlineStr"/>
+        <v>2097843</v>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>FILIAL TAQUARI</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Rafael da Silva Zang</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:20:25</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:24</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:20:25</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>08min</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="4" t="inlineStr"/>
@@ -9852,7 +9896,7 @@
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="4" t="inlineStr"/>
       <c r="B173" s="4" t="n">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
       <c r="D173" s="4" t="inlineStr"/>
@@ -9868,7 +9912,7 @@
     <row r="174" ht="18" customHeight="1">
       <c r="A174" s="4" t="inlineStr"/>
       <c r="B174" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C174" s="4" t="inlineStr"/>
       <c r="D174" s="4" t="inlineStr"/>
@@ -9884,7 +9928,7 @@
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="4" t="inlineStr"/>
       <c r="B175" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C175" s="4" t="inlineStr"/>
       <c r="D175" s="4" t="inlineStr"/>
@@ -9896,6 +9940,22 @@
       <c r="J175" s="4" t="inlineStr"/>
       <c r="K175" s="4" t="inlineStr"/>
       <c r="L175" s="4" t="inlineStr"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="4" t="inlineStr"/>
+      <c r="B176" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="C176" s="4" t="inlineStr"/>
+      <c r="D176" s="4" t="inlineStr"/>
+      <c r="E176" s="4" t="inlineStr"/>
+      <c r="F176" s="4" t="inlineStr"/>
+      <c r="G176" s="4" t="inlineStr"/>
+      <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" s="4" t="inlineStr"/>
+      <c r="J176" s="4" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9908,7 +9968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9980,42 +10040,42 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2097846</v>
+        <v>2097857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ENC: [FORVIA - DIVISION FAS - SAO JOSE DOS PINHAIS SITE - NATIONAL ROAD CARRIER] Announcement - Mastercargo</t>
+          <t>ENC: Nenhuma Duplicidade Encontrada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marcelo Ramos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:26:25</t>
+          <t>02/03/2026 08:34:25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:26:25</t>
+          <t>02/03/2026 08:34:25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 06 Min</t>
+          <t xml:space="preserve"> 00 Hs 02 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -10036,42 +10096,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2097851</v>
+        <v>2097833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Re: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+          <t>RES: Pendência de Emissão - 20/02/2026.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Bruno Castro</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:30</t>
+          <t>02/03/2026 08:10:25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:30</t>
+          <t>02/03/2026 08:10:26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 02 Min</t>
+          <t xml:space="preserve"> 00 Hs 26 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -10081,7 +10141,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>08min</t>
         </is>
       </c>
     </row>
@@ -10092,11 +10152,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2097838</v>
+        <v>2097846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS DE PAULA SOARES</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10106,28 +10166,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
+          <t>ENC: [FORVIA - DIVISION FAS - SAO JOSE DOS PINHAIS SITE - NATIONAL ROAD CARRIER] Announcement - Mastercargo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Priscila Eredes da Silva Lourenço</t>
+          <t>Marcelo Ramos</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:26:25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:26:25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 16 Min</t>
+          <t xml:space="preserve"> 00 Hs 10 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10137,7 +10197,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -10148,11 +10208,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2097853</v>
+        <v>2097852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FILIAL PONTA GROSSA</t>
+          <t>RAIZEN CENTRO-SUL PAULISTA S.A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10162,28 +10222,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Romaneio 1791087 - EMU6F61 - DT 12225427</t>
+          <t>RES: CTe 278 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Antunes Steiner</t>
+          <t>Rodrigo Couto da Silva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:33</t>
+          <t>02/03/2026 08:30:32</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:33</t>
+          <t>02/03/2026 08:30:32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 02 Min</t>
+          <t xml:space="preserve"> 00 Hs 05 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -10193,7 +10253,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -10204,11 +10264,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2097852</v>
+        <v>2097854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RAIZEN CENTRO-SUL PAULISTA S.A</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10218,28 +10278,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RES: CTe 278 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>W10 CRT 862 | LEAR PRESTIGE | BSAS X NVT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodrigo Couto da Silva</t>
+          <t>Osvaldo Antonio Moralez</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:32</t>
+          <t>02/03/2026 08:32:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:32</t>
+          <t>02/03/2026 08:32:26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 02 Min</t>
+          <t xml:space="preserve"> 00 Hs 04 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -10249,7 +10309,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -10260,42 +10320,42 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2097833</v>
+        <v>2097847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RES: Pendência de Emissão - 20/02/2026.</t>
+          <t>RES: Estadias Adiantadas Fevereiro 2026 - R$99.700,00 - Parte 4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bruno Castro</t>
+          <t>William Marques da Silva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:25</t>
+          <t>02/03/2026 08:28:25</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:26</t>
+          <t>02/03/2026 08:28:26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 22 Min</t>
+          <t xml:space="preserve"> 00 Hs 08 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -10305,7 +10365,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>08min</t>
         </is>
       </c>
     </row>
@@ -10316,11 +10376,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2097854</v>
+        <v>2097858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10330,23 +10390,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>W10 CRT 862 | LEAR PRESTIGE | BSAS X NVT</t>
+          <t>RES: A66510 -Comunicado de Desagregação DEXCO Taquari  IJH-0258</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Osvaldo Antonio Moralez</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:25</t>
+          <t>02/03/2026 08:36:25</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:26</t>
+          <t>02/03/2026 08:36:25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -10372,11 +10432,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2097847</v>
+        <v>2097851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10386,28 +10446,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RES: Estadias Adiantadas Fevereiro 2026 - R$99.700,00 - Parte 4</t>
+          <t>Re: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>William Marques da Silva</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02/03/2026 08:28:25</t>
+          <t>02/03/2026 08:30:30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>02/03/2026 08:28:26</t>
+          <t>02/03/2026 08:30:30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 04 Min</t>
+          <t xml:space="preserve"> 00 Hs 06 Min</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -10417,7 +10477,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>06min</t>
         </is>
       </c>
     </row>
@@ -10428,42 +10488,42 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2097849</v>
+        <v>2097838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>ANTONIO CARLOS DE PAULA SOARES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>W10 CRT 860 861 | MARO MAHLE VOLVO | BAIRES X CURITIBA</t>
+          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Osvaldo Antonio Moralez</t>
+          <t>Priscila Eredes da Silva Lourenço</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:27</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:27</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 02 Min</t>
+          <t xml:space="preserve"> 00 Hs 20 Min</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -10473,7 +10533,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -10484,11 +10544,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2097848</v>
+        <v>2097853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL PONTA GROSSA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10498,38 +10558,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDÁGIO AVULSO - CYN2C57 </t>
+          <t>Romaneio 1791087 - EMU6F61 - DT 12225427</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>Carlos Eduardo Antunes Steiner</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:25</t>
+          <t>02/03/2026 08:30:33</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:25</t>
+          <t>02/03/2026 08:30:33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 02 Min</t>
+          <t xml:space="preserve"> 00 Hs 05 Min</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Pendente de Atendimento</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>01min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -10540,11 +10600,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2097842</v>
+        <v>2097856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10554,38 +10614,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: A51540 - CRT </t>
+          <t>RES: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>Victor Oliveira Lamy</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 08:34:23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 08:34:23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 12 Min</t>
+          <t xml:space="preserve"> 00 Hs 02 Min</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Pendente de Atendimento</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>02min</t>
         </is>
       </c>
     </row>
@@ -10596,11 +10656,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2097840</v>
+        <v>2097848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10610,38 +10670,150 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CTE RITMO Fevereiro | Situação</t>
+          <t xml:space="preserve">PEDÁGIO AVULSO - CYN2C57 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gustavo Delirio Luiz</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:27</t>
+          <t>02/03/2026 08:30:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
+          <t>02/03/2026 08:30:25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 06 Min</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>04min</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2097849</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MERCOSUL - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>W10 CRT 860 861 | MARO MAHLE VOLVO | BAIRES X CURITIBA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Osvaldo Antonio Moralez</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:27</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:27</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 06 Min</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>02min</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2097840</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CTE RITMO Fevereiro | Situação</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gustavo Delirio Luiz</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>02/03/2026 08:18:27</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 14 Min</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:18:27</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 18 Min</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>04min</t>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -10754,42 +10926,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2097723</v>
+        <v>2097728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ENC: CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:25</t>
+          <t>02/03/2026 02:50:23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:25</t>
+          <t>02/03/2026 02:50:23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 06 Hs 04 Min</t>
+          <t xml:space="preserve"> 05 Hs 46 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -10799,7 +10971,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05h 56min</t>
+          <t>04h 27min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -10813,42 +10985,42 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2097725</v>
+        <v>2097723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:25</t>
+          <t>02/03/2026 02:28:25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:25</t>
+          <t>02/03/2026 02:28:25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 06 Hs 00 Min</t>
+          <t xml:space="preserve"> 06 Hs 08 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10858,7 +11030,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05h 53min</t>
+          <t>05h 59min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -10872,7 +11044,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2097728</v>
+        <v>2097725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -10886,7 +11058,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -10896,18 +11068,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:23</t>
+          <t>02/03/2026 02:32:25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:23</t>
+          <t>02/03/2026 02:32:25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 05 Hs 42 Min</t>
+          <t xml:space="preserve"> 06 Hs 04 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -10917,7 +11089,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>05h 56min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -10966,7 +11138,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 07 Hs 20 Min</t>
+          <t xml:space="preserve"> 07 Hs 24 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -10976,7 +11148,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07h 08min</t>
+          <t>07h 11min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -10986,7 +11158,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -11005,7 +11177,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -11024,7 +11196,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -11277,7 +11449,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -11296,7 +11468,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -11315,7 +11487,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -11400,11 +11572,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12m 4s</t>
+          <t>11m 8s</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -11556,76 +11728,76 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2097846</v>
+        <v>2097833</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ENC: [FORVIA - DIVISION FAS - SAO JOSE DOS PINHAIS SITE - NATIONAL ROAD CARRIER] Announcement - Mastercargo</t>
+          <t>RES: Pendência de Emissão - 20/02/2026.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marcelo Ramos</t>
+          <t>Bruno Castro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:26:25</t>
+          <t>02/03/2026 08:10:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2097838</v>
+        <v>2097846</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS DE PAULA SOARES</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
+          <t>ENC: [FORVIA - DIVISION FAS - SAO JOSE DOS PINHAIS SITE - NATIONAL ROAD CARRIER] Announcement - Mastercargo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Priscila Eredes da Silva Lourenço</t>
+          <t>Marcelo Ramos</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:26:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2097833</v>
+        <v>2097838</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>ANTONIO CARLOS DE PAULA SOARES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RES: Pendência de Emissão - 20/02/2026.</t>
+          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bruno Castro</t>
+          <t>Priscila Eredes da Silva Lourenço</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:25</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
     </row>
@@ -11677,23 +11849,23 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1m 19s</t>
+          <t>2m 45s</t>
         </is>
       </c>
     </row>
@@ -11751,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -11893,7 +12065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2097831</v>
+        <v>2097836</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:27</t>
+          <t>02/03/2026 08:15:23</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:00</t>
+          <t>02/03/2026 08:31:58</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:27</t>
+          <t>02/03/2026 08:15:23</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>25min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>33min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2097834</v>
+        <v>2097848</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT EXTREMA  155402/155401</t>
+          <t xml:space="preserve">PEDÁGIO AVULSO - CYN2C57 </t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Henrique Baptista Santos</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:25</t>
+          <t>02/03/2026 08:30:25</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:27:28</t>
+          <t>02/03/2026 08:37:51</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:25</t>
+          <t>02/03/2026 08:30:25</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>14min</t>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2097848</v>
+        <v>2097831</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDÁGIO AVULSO - CYN2C57 </t>
+          <t>CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:25</t>
+          <t>02/03/2026 08:08:27</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:37:51</t>
+          <t>02/03/2026 08:17:00</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:25</t>
+          <t>02/03/2026 08:08:27</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2097836</v>
+        <v>2097834</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT EXTREMA  155402/155401</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Gabriel Henrique Baptista Santos</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:23</t>
+          <t>02/03/2026 08:14:25</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:31:58</t>
+          <t>02/03/2026 08:27:28</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:23</t>
+          <t>02/03/2026 08:14:25</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>10min</t>
+          <t>18min</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2097811</v>
+        <v>2097814</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2603020003 NF- 627246</t>
+          <t>emissão Reckitt SHI2602280037 NF- 627240</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:23</t>
+          <t>02/03/2026 07:46:23</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:25</t>
+          <t>02/03/2026 08:04:05</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:23</t>
+          <t>02/03/2026 07:46:23</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>41min</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2097805</v>
+        <v>2097787</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>RES: emissão Reckitt SHI2602280019 NF- 627205</t>
+          <t>emissão Reckitt SHI2602280004 NF- 627182</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:26</t>
+          <t>02/03/2026 07:00:27</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:33:20</t>
+          <t>02/03/2026 07:24:47</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:26</t>
+          <t>02/03/2026 07:00:27</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 09min</t>
+          <t>01h 20min</t>
         </is>
       </c>
     </row>
@@ -1188,11 +1188,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2097781</v>
+        <v>2097811</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1202,27 +1202,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDÁGIO AVULSO - EQU3D45 </t>
+          <t>emissão Reckitt SHI2603020003 NF- 627246</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:50:23</t>
+          <t>02/03/2026 07:42:23</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:01:12</t>
+          <t>02/03/2026 07:57:25</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:50:23</t>
+          <t>02/03/2026 07:42:23</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 41min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2097818</v>
+        <v>2097830</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -1262,27 +1262,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2602280035 NF- 627236</t>
+          <t>EMISSÃO RECKITT -  HUB X EXTREMA - VIAGEM SHI2602270088 NF 155399</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:52:23</t>
+          <t>02/03/2026 08:08:26</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:11:44</t>
+          <t>02/03/2026 08:17:55</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:52:23</t>
+          <t>02/03/2026 08:08:26</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>30min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2097803</v>
+        <v>2097786</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270046 NF 155394</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270032 NF 155379</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:23</t>
+          <t>02/03/2026 07:00:25</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:39:46</t>
+          <t>02/03/2026 07:16:56</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:28:23</t>
+          <t>02/03/2026 07:00:25</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>01h 02min</t>
+          <t>01h 28min</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2097830</v>
+        <v>2097793</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -1382,27 +1382,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EXTREMA - VIAGEM SHI2602270088 NF 155399</t>
+          <t>emissão Reckitt SHI2603020004 NF- 627248</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:26</t>
+          <t>02/03/2026 07:18:25</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:55</t>
+          <t>02/03/2026 07:29:22</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:26</t>
+          <t>02/03/2026 07:18:25</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>01h 16min</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2097793</v>
+        <v>2097805</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2603020004 NF- 627248</t>
+          <t>RES: emissão Reckitt SHI2602280019 NF- 627205</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:25</t>
+          <t>02/03/2026 07:28:26</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:29:22</t>
+          <t>02/03/2026 07:33:20</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:25</t>
+          <t>02/03/2026 07:28:26</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2097787</v>
+        <v>2097781</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1502,27 +1502,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280004 NF- 627182</t>
+          <t xml:space="preserve">PEDÁGIO AVULSO - EQU3D45 </t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:27</t>
+          <t>02/03/2026 06:50:23</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:47</t>
+          <t>02/03/2026 07:01:12</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:27</t>
+          <t>02/03/2026 06:50:23</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>01h 17min</t>
+          <t>01h 44min</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2097814</v>
+        <v>2097803</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1562,27 +1562,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280037 NF- 627240</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270046 NF 155394</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:46:23</t>
+          <t>02/03/2026 07:28:23</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:05</t>
+          <t>02/03/2026 07:39:46</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:46:23</t>
+          <t>02/03/2026 07:28:23</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>38min</t>
+          <t>01h 05min</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2097786</v>
+        <v>2097818</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1622,27 +1622,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270032 NF 155379</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2602280035 NF- 627236</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:25</t>
+          <t>02/03/2026 07:52:23</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:16:56</t>
+          <t>02/03/2026 08:11:44</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:00:25</t>
+          <t>02/03/2026 07:52:23</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>01h 25min</t>
+          <t>33min</t>
         </is>
       </c>
     </row>
@@ -1723,41 +1723,41 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2097808</v>
+        <v>2097812</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:25</t>
+          <t>02/03/2026 07:44:23</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:42</t>
+          <t>02/03/2026 08:17:52</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:25</t>
+          <t>02/03/2026 07:44:23</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2097850</v>
+        <v>2097817</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>ENC: Relatório White</t>
+          <t>ENC: CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:28</t>
+          <t>02/03/2026 07:50:24</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:41</t>
+          <t>02/03/2026 07:50:47</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:28</t>
+          <t>02/03/2026 07:50:24</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>54min</t>
         </is>
       </c>
     </row>
@@ -1843,41 +1843,41 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2097778</v>
+        <v>2097807</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: INFORMAÇÕES PARA EMISSÃO DE CTE  </t>
+          <t>CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:23</t>
+          <t>02/03/2026 07:38:23</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:42</t>
+          <t>02/03/2026 07:50:22</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:23</t>
+          <t>02/03/2026 07:38:23</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>55min</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 11min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -1963,41 +1963,41 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2097763</v>
+        <v>2097835</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
+          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151038 - Série: 1</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:26</t>
+          <t>02/03/2026 08:14:26</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:45:00</t>
+          <t>02/03/2026 08:18:17</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:26</t>
+          <t>02/03/2026 08:14:26</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -2023,11 +2023,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2097828</v>
+        <v>2097815</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2037,27 +2037,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO DE CTE- MFV-5C36------------DEXCO-----------------DT-6100685957</t>
+          <t>Favor encerrar o MDFe do veículo: QXI0C85</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>Eduardo Rodrigues Silva da Anunciação</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:23</t>
+          <t>02/03/2026 07:48:23</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:17</t>
+          <t>02/03/2026 07:50:46</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:23</t>
+          <t>02/03/2026 07:48:23</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>54min</t>
         </is>
       </c>
     </row>
@@ -2083,11 +2083,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2097791</v>
+        <v>2097816</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2602280029 NF- 627224</t>
+          <t>CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:25</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:07:30</t>
+          <t>02/03/2026 07:57:25</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:25</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2097816</v>
+        <v>2097808</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2157,27 +2157,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 07:38:25</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:57:25</t>
+          <t>02/03/2026 07:38:42</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 07:38:25</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>01h 06min</t>
         </is>
       </c>
     </row>
@@ -2203,11 +2203,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2097817</v>
+        <v>2097819</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.556 / 007 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve">RES: Placa FPK5D43 Desagregado </t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>leonardo Pedroso Horita</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:24</t>
+          <t>02/03/2026 07:56:23</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:47</t>
+          <t>02/03/2026 07:59:53</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:24</t>
+          <t>02/03/2026 07:56:23</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>45min</t>
         </is>
       </c>
     </row>
@@ -2263,41 +2263,41 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2097796</v>
+        <v>2097763</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:29</t>
+          <t>02/03/2026 05:00:26</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:19:39</t>
+          <t>02/03/2026 07:45:00</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:29</t>
+          <t>02/03/2026 05:00:26</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>01h 22min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -2323,11 +2323,11 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2097835</v>
+        <v>2097788</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2337,27 +2337,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151038 - Série: 1</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270105 NF 155387</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:26</t>
+          <t>02/03/2026 07:02:23</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:17</t>
+          <t>02/03/2026 07:05:21</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:14:26</t>
+          <t>02/03/2026 07:02:23</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>01h 40min</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2097783</v>
+        <v>2097855</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151085 - Série: 1</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:24</t>
+          <t>02/03/2026 08:32:27</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:59:51</t>
+          <t>02/03/2026 08:32:33</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:24</t>
+          <t>02/03/2026 08:32:27</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -2443,11 +2443,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2097797</v>
+        <v>2097844</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2457,27 +2457,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151084 - Série: 1</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:23</t>
+          <t>02/03/2026 08:22:25</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:44</t>
+          <t>02/03/2026 08:30:20</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:24</t>
+          <t>02/03/2026 08:22:25</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>01h 15min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -2503,41 +2503,41 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2097798</v>
+        <v>2097784</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:25</t>
+          <t>02/03/2026 06:56:26</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:57</t>
+          <t>02/03/2026 07:24:19</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:25</t>
+          <t>02/03/2026 06:56:26</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2563,11 +2563,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2097795</v>
+        <v>2097798</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2577,27 +2577,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:28</t>
+          <t>02/03/2026 07:20:25</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:42</t>
+          <t>02/03/2026 07:20:57</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:28</t>
+          <t>02/03/2026 07:20:25</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>01h 15min</t>
+          <t>01h 24min</t>
         </is>
       </c>
     </row>
@@ -2623,11 +2623,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2097810</v>
+        <v>2097799</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2637,27 +2637,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:25</t>
+          <t>02/03/2026 07:20:26</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:42:46</t>
+          <t>02/03/2026 07:26:45</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:25</t>
+          <t>02/03/2026 07:20:26</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2097819</v>
+        <v>2097792</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2697,27 +2697,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Placa FPK5D43 Desagregado </t>
+          <t>emissão Reckitt SHI2602280019 NF- 627205</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>leonardo Pedroso Horita</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:23</t>
+          <t>02/03/2026 07:10:23</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:59:53</t>
+          <t>02/03/2026 07:11:44</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:23</t>
+          <t>02/03/2026 07:10:23</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>42min</t>
+          <t>01h 33min</t>
         </is>
       </c>
     </row>
@@ -2743,41 +2743,41 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2097837</v>
+        <v>2097773</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:25</t>
+          <t>02/03/2026 05:28:25</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:40</t>
+          <t>02/03/2026 07:49:01</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:15:25</t>
+          <t>02/03/2026 05:28:25</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>25min</t>
+          <t>56min</t>
         </is>
       </c>
     </row>
@@ -2803,11 +2803,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2097844</v>
+        <v>2097858</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2817,27 +2817,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151084 - Série: 1</t>
+          <t>RES: A66510 -Comunicado de Desagregação DEXCO Taquari  IJH-0258</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:22:25</t>
+          <t>02/03/2026 08:36:25</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:20</t>
+          <t>02/03/2026 08:41:24</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:22:25</t>
+          <t>02/03/2026 08:36:25</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>12min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -2863,11 +2863,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2097792</v>
+        <v>2097806</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2877,27 +2877,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>emissão Reckitt SHI2602280019 NF- 627205</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:10:23</t>
+          <t>02/03/2026 07:34:23</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:11:44</t>
+          <t>02/03/2026 07:38:38</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:10:23</t>
+          <t>02/03/2026 07:34:23</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>01h 30min</t>
+          <t>01h 06min</t>
         </is>
       </c>
     </row>
@@ -2923,11 +2923,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2097832</v>
+        <v>2097827</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2937,27 +2937,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020001 NF- 627242</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:29</t>
+          <t>02/03/2026 08:04:26</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:09:09</t>
+          <t>02/03/2026 08:05:07</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:29</t>
+          <t>02/03/2026 08:04:26</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -2983,41 +2983,41 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2097748</v>
+        <v>2097857</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: 13065319 ALEXANDRE HERMES PEREIRA IAP5D29 GIX4D54</t>
+          <t>ENC: Nenhuma Duplicidade Encontrada</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:10:25</t>
+          <t>02/03/2026 08:34:25</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:33:33</t>
+          <t>02/03/2026 08:41:23</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:10:25</t>
+          <t>02/03/2026 08:34:25</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>01h 08min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -3043,41 +3043,41 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2097773</v>
+        <v>2097789</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270121 NF 155393</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:28:25</t>
+          <t>02/03/2026 07:02:25</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:49:01</t>
+          <t>02/03/2026 07:06:57</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:28:25</t>
+          <t>02/03/2026 07:02:25</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>53min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -3103,11 +3103,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2097794</v>
+        <v>2097821</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: PEDÁGIO AVULSO - EQU3D45 </t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020002 NF- 627244</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Vitor Hugo da Silva Barbosa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:26</t>
+          <t>02/03/2026 07:58:23</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:19:44</t>
+          <t>02/03/2026 08:01:21</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:18:26</t>
+          <t>02/03/2026 07:58:23</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>01h 22min</t>
+          <t>44min</t>
         </is>
       </c>
     </row>
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2097809</v>
+        <v>2097823</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3177,27 +3177,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:23</t>
+          <t>02/03/2026 08:02:23</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:23</t>
+          <t>02/03/2026 08:08:12</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:40:23</t>
+          <t>02/03/2026 08:02:24</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -3223,11 +3223,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2097827</v>
+        <v>2097783</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3237,27 +3237,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020001 NF- 627242</t>
+          <t>ENC: CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:26</t>
+          <t>02/03/2026 06:56:24</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:07</t>
+          <t>02/03/2026 06:59:51</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:26</t>
+          <t>02/03/2026 06:56:24</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>01h 45min</t>
         </is>
       </c>
     </row>
@@ -3283,11 +3283,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2097790</v>
+        <v>2097797</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3297,27 +3297,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270120 NF 155391</t>
+          <t>CTe 43678 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:24</t>
+          <t>02/03/2026 07:20:23</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:07:27</t>
+          <t>02/03/2026 07:26:44</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:24</t>
+          <t>02/03/2026 07:20:24</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2097825</v>
+        <v>2097832</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.557 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.558 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:23</t>
+          <t>02/03/2026 08:08:29</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:10</t>
+          <t>02/03/2026 08:09:09</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:23</t>
+          <t>02/03/2026 08:08:29</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>36min</t>
         </is>
       </c>
     </row>
@@ -3403,11 +3403,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2097857</v>
+        <v>2097791</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3417,27 +3417,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ENC: Nenhuma Duplicidade Encontrada</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2602280029 NF- 627224</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:25</t>
+          <t>02/03/2026 07:06:25</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:41:23</t>
+          <t>02/03/2026 07:07:30</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:25</t>
+          <t>02/03/2026 07:06:25</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -3463,41 +3463,41 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2097821</v>
+        <v>2097755</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020002 NF- 627244</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:23</t>
+          <t>02/03/2026 04:46:23</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:01:21</t>
+          <t>02/03/2026 07:38:52</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:23</t>
+          <t>02/03/2026 04:46:23</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>40min</t>
+          <t>01h 06min</t>
         </is>
       </c>
     </row>
@@ -3523,11 +3523,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2097799</v>
+        <v>2097856</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3537,27 +3537,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Victor Oliveira Lamy</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:26</t>
+          <t>02/03/2026 08:34:23</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:26:45</t>
+          <t>02/03/2026 08:41:27</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:26</t>
+          <t>02/03/2026 08:34:23</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>01h 15min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -3583,11 +3583,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2097800</v>
+        <v>2097822</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3597,27 +3597,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: cte 6920</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Victor Oliveira Lamy</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:28</t>
+          <t>02/03/2026 07:58:25</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:59</t>
+          <t>02/03/2026 07:58:36</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:20:28</t>
+          <t>02/03/2026 07:58:25</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>46min</t>
         </is>
       </c>
     </row>
@@ -3643,41 +3643,41 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2097812</v>
+        <v>2097828</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL TAQUARI</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO DE CTE- MFV-5C36------------DEXCO-----------------DT-6100685957</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Rafael da Silva Zang</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:23</t>
+          <t>02/03/2026 08:06:23</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:17:52</t>
+          <t>02/03/2026 08:08:17</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:23</t>
+          <t>02/03/2026 08:06:23</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2097847</v>
+        <v>2097842</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3717,27 +3717,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>RES: Estadias Adiantadas Fevereiro 2026 - R$99.700,00 - Parte 4</t>
+          <t xml:space="preserve">RES: A51540 - CRT </t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>William Marques da Silva</t>
+          <t>Matheus Braz de Moura</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:28:25</t>
+          <t>02/03/2026 08:20:23</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:41:39</t>
+          <t>02/03/2026 08:33:44</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:28:26</t>
+          <t>02/03/2026 08:20:23</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>11min</t>
         </is>
       </c>
     </row>
@@ -3763,11 +3763,11 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2097788</v>
+        <v>2097785</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3777,27 +3777,27 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270105 NF 155387</t>
+          <t>ENC: CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:23</t>
+          <t>02/03/2026 06:56:27</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:05:21</t>
+          <t>02/03/2026 06:59:53</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:23</t>
+          <t>02/03/2026 06:56:27</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>01h 36min</t>
+          <t>01h 45min</t>
         </is>
       </c>
     </row>
@@ -3823,11 +3823,11 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2097789</v>
+        <v>2097813</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3837,27 +3837,27 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270121 NF 155393</t>
+          <t>ENC: CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Vagner Matos de Souza</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:25</t>
+          <t>02/03/2026 07:44:25</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:06:57</t>
+          <t>02/03/2026 07:45:04</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:02:25</t>
+          <t>02/03/2026 07:44:25</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>01h 35min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>2097822</v>
+        <v>2097794</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3897,27 +3897,27 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>RES: cte 6920</t>
+          <t xml:space="preserve">RES: PEDÁGIO AVULSO - EQU3D45 </t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Victor Oliveira Lamy</t>
+          <t>Vitor Hugo da Silva Barbosa</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:25</t>
+          <t>02/03/2026 07:18:26</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:36</t>
+          <t>02/03/2026 07:19:44</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:58:25</t>
+          <t>02/03/2026 07:18:26</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>43min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -3943,11 +3943,11 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>2097842</v>
+        <v>2097796</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3957,27 +3957,27 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: A51540 - CRT </t>
+          <t>ENC: CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 07:18:29</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:33:44</t>
+          <t>02/03/2026 07:19:39</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:20:23</t>
+          <t>02/03/2026 07:18:29</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>08min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -4003,11 +4003,11 @@
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>2097815</v>
+        <v>2097837</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -4017,27 +4017,27 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Favor encerrar o MDFe do veículo: QXI0C85</t>
+          <t>ENC: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Eduardo Rodrigues Silva da Anunciação</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:48:23</t>
+          <t>02/03/2026 08:15:25</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:46</t>
+          <t>02/03/2026 08:16:40</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:48:23</t>
+          <t>02/03/2026 08:15:25</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -4063,41 +4063,41 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>2097839</v>
+        <v>2097778</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>ENC: Solicitação de coleta: ARGENTINA - PEÇAS - Fatura: 266677</t>
+          <t xml:space="preserve">RES: INFORMAÇÕES PARA EMISSÃO DE CTE  </t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:25</t>
+          <t>02/03/2026 06:14:23</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:26</t>
+          <t>02/03/2026 07:57:42</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:25</t>
+          <t>02/03/2026 06:14:23</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>47min</t>
         </is>
       </c>
     </row>
@@ -4123,41 +4123,41 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>2097755</v>
+        <v>2097839</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
+          <t>ENC: Solicitação de coleta: ARGENTINA - PEÇAS - Fatura: 266677</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>Matheus Braz de Moura</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:46:23</t>
+          <t>02/03/2026 08:18:25</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:52</t>
+          <t>02/03/2026 08:32:26</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:46:23</t>
+          <t>02/03/2026 08:18:25</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -4183,11 +4183,11 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>2097813</v>
+        <v>2097809</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -4197,27 +4197,27 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.006.920 / 061 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:25</t>
+          <t>02/03/2026 07:40:23</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:45:04</t>
+          <t>02/03/2026 07:50:23</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:44:25</t>
+          <t>02/03/2026 07:40:23</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>55min</t>
         </is>
       </c>
     </row>
@@ -4243,11 +4243,11 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>2097807</v>
+        <v>2097810</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -4257,27 +4257,27 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>CTe 43680 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43681 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:23</t>
+          <t>02/03/2026 07:40:25</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:50:22</t>
+          <t>02/03/2026 07:42:46</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:23</t>
+          <t>02/03/2026 07:40:25</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>01h 02min</t>
         </is>
       </c>
     </row>
@@ -4303,11 +4303,11 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>2097858</v>
+        <v>2097825</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -4317,27 +4317,27 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>RES: A66510 -Comunicado de Desagregação DEXCO Taquari  IJH-0258</t>
+          <t>ENC: CT-e: 000.046.557 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:36:25</t>
+          <t>02/03/2026 08:04:23</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:41:24</t>
+          <t>02/03/2026 08:05:10</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:36:25</t>
+          <t>02/03/2026 08:04:23</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>2097806</v>
+        <v>2097826</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>Re: cte 6920</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:34:23</t>
+          <t>02/03/2026 08:04:25</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:38:38</t>
+          <t>02/03/2026 08:05:09</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:34:23</t>
+          <t>02/03/2026 08:04:25</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -4423,11 +4423,11 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>2097820</v>
+        <v>2097847</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>RITMO - SEGUROS</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -4437,27 +4437,27 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>RES: Emissão CT-e manual- Ritmo</t>
+          <t>RES: Estadias Adiantadas Fevereiro 2026 - R$99.700,00 - Parte 4</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Adrian Bitencourt</t>
+          <t>William Marques da Silva</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:25</t>
+          <t>02/03/2026 08:28:25</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:57</t>
+          <t>02/03/2026 08:41:39</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:56:25</t>
+          <t>02/03/2026 08:28:26</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>25min</t>
+          <t>03min</t>
         </is>
       </c>
     </row>
@@ -4483,41 +4483,41 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
-        <v>2097826</v>
+        <v>2097782</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Re: cte 6920</t>
+          <t>CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:25</t>
+          <t>02/03/2026 06:56:23</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:05:09</t>
+          <t>02/03/2026 07:25:37</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:04:25</t>
+          <t>02/03/2026 06:56:23</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>01h 19min</t>
         </is>
       </c>
     </row>
@@ -4543,11 +4543,11 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>2097856</v>
+        <v>2097790</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -4557,27 +4557,27 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO RECKITT -  HUB X EMBU - VIAGEM SHI2602270120 NF 155391</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Victor Oliveira Lamy</t>
+          <t>Vagner Matos de Souza</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:23</t>
+          <t>02/03/2026 07:06:24</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:41:27</t>
+          <t>02/03/2026 07:07:27</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:23</t>
+          <t>02/03/2026 07:06:24</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -4603,11 +4603,11 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>2097823</v>
+        <v>2097800</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -4617,27 +4617,27 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+          <t>ENC: CTe 43679 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:02:23</t>
+          <t>02/03/2026 07:20:28</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:08:12</t>
+          <t>02/03/2026 07:20:59</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:02:24</t>
+          <t>02/03/2026 07:20:28</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>01h 24min</t>
         </is>
       </c>
     </row>
@@ -4663,41 +4663,41 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>2097855</v>
+        <v>2097748</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151085 - Série: 1</t>
+          <t>RES: 13065319 ALEXANDRE HERMES PEREIRA IAP5D29 GIX4D54</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:27</t>
+          <t>02/03/2026 04:10:25</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:33</t>
+          <t>02/03/2026 07:33:33</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:27</t>
+          <t>02/03/2026 04:10:25</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>01h 12min</t>
         </is>
       </c>
     </row>
@@ -4723,41 +4723,41 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
-        <v>2097782</v>
+        <v>2097795</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.554 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43677 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:23</t>
+          <t>02/03/2026 07:18:28</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:25:37</t>
+          <t>02/03/2026 07:26:42</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:23</t>
+          <t>02/03/2026 07:18:28</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>01h 16min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -4783,41 +4783,41 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>2097784</v>
+        <v>2097820</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RITMO - SEGUROS</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emissão CT-e manual- Ritmo</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Adrian Bitencourt</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:26</t>
+          <t>02/03/2026 07:56:25</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:24:19</t>
+          <t>02/03/2026 08:16:57</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:26</t>
+          <t>02/03/2026 07:56:25</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>2097785</v>
+        <v>2097850</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.555 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Relatório White</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:27</t>
+          <t>02/03/2026 08:30:28</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:59:53</t>
+          <t>02/03/2026 08:30:41</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:56:27</t>
+          <t>02/03/2026 08:30:28</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>14min</t>
         </is>
       </c>
     </row>
@@ -4958,11 +4958,11 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>2097801</v>
+        <v>2097829</v>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>AGREGADOS</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4972,27 +4972,27 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>RES: REEMBOLSO SEM PARAR - BENS 2025/2026</t>
+          <t xml:space="preserve">RES: Desagregações Fevereiro </t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Beatriz Treiss Rodrigues</t>
+          <t>Saulo Henrique Oliveira de Souza</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:22:25</t>
+          <t>02/03/2026 08:06:25</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:07:56</t>
+          <t>02/03/2026 08:10:30</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 07:22:25</t>
+          <t>02/03/2026 08:06:25</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>35min</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -5078,11 +5078,11 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
-        <v>2097829</v>
+        <v>2097801</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>AGREGADOS</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -5092,27 +5092,27 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Desagregações Fevereiro </t>
+          <t>RES: REEMBOLSO SEM PARAR - BENS 2025/2026</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Saulo Henrique Oliveira de Souza</t>
+          <t>Beatriz Treiss Rodrigues</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:25</t>
+          <t>02/03/2026 07:22:25</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:30</t>
+          <t>02/03/2026 08:07:56</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:06:25</t>
+          <t>02/03/2026 07:22:25</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>31min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="B90" s="4" t="n">
-        <v>2097699</v>
+        <v>2097741</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:26</t>
+          <t>02/03/2026 03:44:25</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:55:36</t>
+          <t>02/03/2026 04:02:44</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:26</t>
+          <t>02/03/2026 03:44:25</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>07h 46min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -5253,11 +5253,11 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>2097735</v>
+        <v>2097712</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5267,27 +5267,27 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:25</t>
+          <t>02/03/2026 01:44:23</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:13:33</t>
+          <t>02/03/2026 01:52:34</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:25</t>
+          <t>02/03/2026 01:44:23</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>05h 28min</t>
+          <t>06h 52min</t>
         </is>
       </c>
     </row>
@@ -5313,11 +5313,11 @@
         </is>
       </c>
       <c r="B92" s="4" t="n">
-        <v>2097746</v>
+        <v>2097696</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -5327,27 +5327,27 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:23</t>
+          <t>02/03/2026 00:36:23</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:35</t>
+          <t>02/03/2026 00:49:30</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:23</t>
+          <t>02/03/2026 00:36:23</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>04h 23min</t>
+          <t>07h 56min</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>2097720</v>
+        <v>2097727</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151065 - Série: 1</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:25</t>
+          <t>02/03/2026 02:42:23</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:46</t>
+          <t>02/03/2026 02:45:28</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:25</t>
+          <t>02/03/2026 02:42:23</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>06h 35min</t>
+          <t>06h 00min</t>
         </is>
       </c>
     </row>
@@ -5433,11 +5433,11 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>2097738</v>
+        <v>2097711</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -5447,27 +5447,27 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:26:23</t>
+          <t>02/03/2026 01:36:24</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:05</t>
+          <t>02/03/2026 01:39:03</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:26:23</t>
+          <t>02/03/2026 01:36:24</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>07h 06min</t>
         </is>
       </c>
     </row>
@@ -5493,11 +5493,11 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>2097776</v>
+        <v>2097761</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5507,27 +5507,27 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:02:23</t>
+          <t>02/03/2026 05:00:23</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:13:38</t>
+          <t>02/03/2026 05:20:20</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:02:23</t>
+          <t>02/03/2026 05:00:23</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>02h 28min</t>
+          <t>03h 25min</t>
         </is>
       </c>
     </row>
@@ -5553,11 +5553,11 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>2097731</v>
+        <v>2097752</v>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:23</t>
+          <t>02/03/2026 04:34:26</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:17:34</t>
+          <t>02/03/2026 04:37:54</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:23</t>
+          <t>02/03/2026 04:34:26</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>04h 07min</t>
         </is>
       </c>
     </row>
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>2097709</v>
+        <v>2097699</v>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
+          <t>ENC: CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:30:23</t>
+          <t>02/03/2026 00:54:26</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:31:49</t>
+          <t>02/03/2026 00:55:36</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:30:23</t>
+          <t>02/03/2026 00:54:26</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>07h 10min</t>
+          <t>07h 49min</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>2097756</v>
+        <v>2097734</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -5697,17 +5697,17 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:23</t>
+          <t>02/03/2026 03:12:23</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:56</t>
+          <t>02/03/2026 04:17:57</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:23</t>
+          <t>02/03/2026 03:12:23</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>03h 25min</t>
+          <t>04h 27min</t>
         </is>
       </c>
     </row>
@@ -5733,11 +5733,11 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>2097751</v>
+        <v>2097735</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5747,27 +5747,27 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:23</t>
+          <t>02/03/2026 03:12:25</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:43:51</t>
+          <t>02/03/2026 03:13:33</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:23</t>
+          <t>02/03/2026 03:12:25</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>03h 58min</t>
+          <t>05h 32min</t>
         </is>
       </c>
     </row>
@@ -5793,11 +5793,11 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>2097706</v>
+        <v>2097718</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5807,27 +5807,27 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo BCY3J08</t>
+          <t>ENC: CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:16:23</t>
+          <t>02/03/2026 01:56:24</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:21:04</t>
+          <t>02/03/2026 01:58:00</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:16:23</t>
+          <t>02/03/2026 01:56:24</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>07h 21min</t>
+          <t>06h 47min</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>2097772</v>
+        <v>2097775</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -5877,17 +5877,17 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:26</t>
+          <t>02/03/2026 05:50:25</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:36:49</t>
+          <t>02/03/2026 05:50:47</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:26</t>
+          <t>02/03/2026 05:50:25</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>03h 05min</t>
+          <t>02h 54min</t>
         </is>
       </c>
     </row>
@@ -5913,11 +5913,11 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>2097719</v>
+        <v>2097707</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5927,27 +5927,27 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:24</t>
+          <t>02/03/2026 01:24:23</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:39</t>
+          <t>02/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:00:24</t>
+          <t>02/03/2026 01:24:23</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>06h 35min</t>
+          <t>07h 16min</t>
         </is>
       </c>
     </row>
@@ -5973,11 +5973,11 @@
         </is>
       </c>
       <c r="B103" s="4" t="n">
-        <v>2097721</v>
+        <v>2097709</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5987,27 +5987,27 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151037 - Série: 1</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:23</t>
+          <t>02/03/2026 01:30:23</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:10:16</t>
+          <t>02/03/2026 01:31:49</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:23</t>
+          <t>02/03/2026 01:30:23</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>06h 32min</t>
+          <t>07h 13min</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>2097696</v>
+        <v>2097716</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
@@ -6047,27 +6047,27 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:23</t>
+          <t>02/03/2026 01:54:23</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:49:30</t>
+          <t>02/03/2026 01:54:41</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:23</t>
+          <t>02/03/2026 01:54:23</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>07h 52min</t>
+          <t>06h 50min</t>
         </is>
       </c>
     </row>
@@ -6093,11 +6093,11 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>2097708</v>
+        <v>2097745</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -6107,27 +6107,27 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:23</t>
+          <t>02/03/2026 03:58:25</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:35</t>
+          <t>02/03/2026 04:03:05</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:23</t>
+          <t>02/03/2026 03:58:25</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>07h 13min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -6153,11 +6153,11 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>2097765</v>
+        <v>2097738</v>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6167,27 +6167,27 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:27</t>
+          <t>02/03/2026 03:26:23</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:17:12</t>
+          <t>02/03/2026 04:18:05</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:27</t>
+          <t>02/03/2026 03:26:23</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>03h 25min</t>
+          <t>04h 27min</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="B107" s="4" t="n">
-        <v>2097777</v>
+        <v>2097708</v>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>RES: INFORMAÇÕES PARA EMISSÃO DE CTE - 02/03/2026</t>
+          <t>RES: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:06:24</t>
+          <t>02/03/2026 01:28:23</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:14:59</t>
+          <t>02/03/2026 01:28:35</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:06:24</t>
+          <t>02/03/2026 01:28:23</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>02h 27min</t>
+          <t>07h 16min</t>
         </is>
       </c>
     </row>
@@ -6273,11 +6273,11 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>2097700</v>
+        <v>2097733</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -6287,27 +6287,27 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NORDESTE - ASR0C31</t>
+          <t>EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Gabriel  Molinari de Moraes</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:23</t>
+          <t>02/03/2026 03:08:25</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:19:09</t>
+          <t>02/03/2026 03:11:40</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:23</t>
+          <t>02/03/2026 03:08:25</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>07h 23min</t>
+          <t>05h 33min</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="B109" s="4" t="n">
-        <v>2097712</v>
+        <v>2097774</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -6357,17 +6357,17 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:23</t>
+          <t>02/03/2026 05:50:23</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:34</t>
+          <t>02/03/2026 06:01:20</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:23</t>
+          <t>02/03/2026 05:50:23</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>06h 49min</t>
+          <t>02h 44min</t>
         </is>
       </c>
     </row>
@@ -6393,11 +6393,11 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>2097714</v>
+        <v>2097705</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -6407,27 +6407,27 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo IXR2D00</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:23</t>
+          <t>02/03/2026 01:14:26</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:41</t>
+          <t>02/03/2026 01:21:00</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:23</t>
+          <t>02/03/2026 01:14:26</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>06h 49min</t>
+          <t>07h 24min</t>
         </is>
       </c>
     </row>
@@ -6453,11 +6453,11 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>2097742</v>
+        <v>2097754</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -6467,27 +6467,27 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:48:23</t>
+          <t>02/03/2026 04:36:24</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:05</t>
+          <t>02/03/2026 04:37:59</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:48:23</t>
+          <t>02/03/2026 04:36:24</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>04h 07min</t>
         </is>
       </c>
     </row>
@@ -6513,11 +6513,11 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>2097733</v>
+        <v>2097726</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -6527,27 +6527,27 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13071552 - ICARO BORGES DA FONSECA - KPX9F35 - ENM6665</t>
+          <t>ENC: CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:08:25</t>
+          <t>02/03/2026 02:32:27</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:11:40</t>
+          <t>02/03/2026 02:35:25</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:08:25</t>
+          <t>02/03/2026 02:32:27</t>
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>05h 30min</t>
+          <t>06h 10min</t>
         </is>
       </c>
     </row>
@@ -6573,11 +6573,11 @@
         </is>
       </c>
       <c r="B113" s="4" t="n">
-        <v>2097743</v>
+        <v>2097706</v>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -6587,27 +6587,27 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo BCY3J08</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:50:24</t>
+          <t>02/03/2026 01:16:23</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:51</t>
+          <t>02/03/2026 01:21:04</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:50:24</t>
+          <t>02/03/2026 01:16:23</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>07h 24min</t>
         </is>
       </c>
     </row>
@@ -6633,11 +6633,11 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>2097771</v>
+        <v>2097694</v>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -6647,27 +6647,27 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:24</t>
+          <t>02/03/2026 00:26:24</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:45:17</t>
+          <t>02/03/2026 00:34:41</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:26:24</t>
+          <t>02/03/2026 00:26:25</t>
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>08h 10min</t>
         </is>
       </c>
     </row>
@@ -6693,11 +6693,11 @@
         </is>
       </c>
       <c r="B115" s="4" t="n">
-        <v>2097766</v>
+        <v>2097719</v>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -6707,27 +6707,27 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151077 - Série: 1</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:23</t>
+          <t>02/03/2026 02:00:24</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:50</t>
+          <t>02/03/2026 02:06:39</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:16:23</t>
+          <t>02/03/2026 02:00:24</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>03h 25min</t>
+          <t>06h 38min</t>
         </is>
       </c>
     </row>
@@ -6753,11 +6753,11 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>2097736</v>
+        <v>2097720</v>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -6767,27 +6767,27 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo PCQ2I98</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:23</t>
+          <t>02/03/2026 02:00:25</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:06:06</t>
+          <t>02/03/2026 02:06:46</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:23</t>
+          <t>02/03/2026 02:00:25</t>
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>04h 36min</t>
+          <t>06h 38min</t>
         </is>
       </c>
     </row>
@@ -6813,11 +6813,11 @@
         </is>
       </c>
       <c r="B117" s="4" t="n">
-        <v>2097750</v>
+        <v>2097714</v>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -6827,27 +6827,27 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:29</t>
+          <t>02/03/2026 01:50:23</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:44</t>
+          <t>02/03/2026 01:52:41</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:29</t>
+          <t>02/03/2026 01:50:23</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>04h 23min</t>
+          <t>06h 52min</t>
         </is>
       </c>
     </row>
@@ -6873,11 +6873,11 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>2097729</v>
+        <v>2097736</v>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -6887,27 +6887,27 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo PCQ2I98</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:25</t>
+          <t>02/03/2026 03:24:23</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:51:37</t>
+          <t>02/03/2026 04:06:06</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:25</t>
+          <t>02/03/2026 03:24:23</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>05h 50min</t>
+          <t>04h 39min</t>
         </is>
       </c>
     </row>
@@ -6933,11 +6933,11 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
-        <v>2097764</v>
+        <v>2097737</v>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -6947,27 +6947,27 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:23</t>
+          <t>02/03/2026 03:24:25</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:22:35</t>
+          <t>02/03/2026 04:02:26</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:14:23</t>
+          <t>02/03/2026 03:24:25</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>03h 19min</t>
+          <t>04h 43min</t>
         </is>
       </c>
     </row>
@@ -6993,11 +6993,11 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>2097768</v>
+        <v>2097722</v>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -7007,27 +7007,27 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>encerramento da MDF-e do veículo PPH8A77</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Denis da Silva Moreira</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:23</t>
+          <t>02/03/2026 02:14:25</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:44:34</t>
+          <t>02/03/2026 02:16:29</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:23</t>
+          <t>02/03/2026 02:14:25</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>06h 29min</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="B121" s="4" t="n">
-        <v>2097770</v>
+        <v>2097732</v>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:26</t>
+          <t>02/03/2026 03:02:25</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:36:41</t>
+          <t>02/03/2026 03:11:45</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:26</t>
+          <t>02/03/2026 03:02:25</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>03h 05min</t>
+          <t>05h 33min</t>
         </is>
       </c>
     </row>
@@ -7113,11 +7113,11 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>2097745</v>
+        <v>2097742</v>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -7127,27 +7127,27 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:25</t>
+          <t>02/03/2026 03:48:23</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:03:05</t>
+          <t>02/03/2026 04:38:05</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:25</t>
+          <t>02/03/2026 03:48:23</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>04h 07min</t>
         </is>
       </c>
     </row>
@@ -7173,11 +7173,11 @@
         </is>
       </c>
       <c r="B123" s="4" t="n">
-        <v>2097753</v>
+        <v>2097764</v>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -7187,27 +7187,27 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:23</t>
+          <t>02/03/2026 05:14:23</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:43:57</t>
+          <t>02/03/2026 05:22:35</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:23</t>
+          <t>02/03/2026 05:14:23</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>03h 58min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>2097754</v>
+        <v>2097765</v>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.553 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -7257,17 +7257,17 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:24</t>
+          <t>02/03/2026 05:14:27</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:37:59</t>
+          <t>02/03/2026 05:17:12</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:36:24</t>
+          <t>02/03/2026 05:14:27</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -7293,11 +7293,11 @@
         </is>
       </c>
       <c r="B125" s="4" t="n">
-        <v>2097759</v>
+        <v>2097724</v>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -7307,27 +7307,27 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:29</t>
+          <t>02/03/2026 02:28:28</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:55:28</t>
+          <t>02/03/2026 02:29:44</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:29</t>
+          <t>02/03/2026 02:28:28</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>03h 46min</t>
+          <t>06h 15min</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>2097747</v>
+        <v>2097739</v>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Aceite de coleta PepsiCo</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -7377,17 +7377,17 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:25</t>
+          <t>02/03/2026 03:42:25</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:03:15</t>
+          <t>02/03/2026 04:02:35</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:00:25</t>
+          <t>02/03/2026 03:42:25</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="B127" s="4" t="n">
-        <v>2097697</v>
+        <v>2097704</v>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -7437,17 +7437,17 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:24</t>
+          <t>02/03/2026 01:14:25</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:43:23</t>
+          <t>02/03/2026 01:19:15</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:36:24</t>
+          <t>02/03/2026 01:14:25</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>07h 58min</t>
+          <t>07h 26min</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>2097749</v>
+        <v>2097753</v>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43672 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -7497,17 +7497,17 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:25</t>
+          <t>02/03/2026 04:36:23</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:17</t>
+          <t>02/03/2026 04:43:57</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:25</t>
+          <t>02/03/2026 04:36:23</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>04h 01min</t>
         </is>
       </c>
     </row>
@@ -7533,11 +7533,11 @@
         </is>
       </c>
       <c r="B129" s="4" t="n">
-        <v>2097767</v>
+        <v>2097758</v>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -7547,27 +7547,27 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151079 - Série: 1</t>
+          <t>CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:24</t>
+          <t>02/03/2026 04:52:28</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:22:43</t>
+          <t>02/03/2026 05:17:01</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:24</t>
+          <t>02/03/2026 04:52:28</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>03h 19min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -7593,11 +7593,11 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>2097761</v>
+        <v>2097743</v>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -7607,27 +7607,27 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43668 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:23</t>
+          <t>02/03/2026 03:50:24</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:20:20</t>
+          <t>02/03/2026 04:02:51</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:23</t>
+          <t>02/03/2026 03:50:24</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -7653,11 +7653,11 @@
         </is>
       </c>
       <c r="B131" s="4" t="n">
-        <v>2097775</v>
+        <v>2097771</v>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -7667,27 +7667,27 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:25</t>
+          <t>02/03/2026 05:26:24</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:47</t>
+          <t>02/03/2026 05:45:17</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:25</t>
+          <t>02/03/2026 05:26:24</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>02h 51min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>2097704</v>
+        <v>2097702</v>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -7737,17 +7737,17 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:25</t>
+          <t>02/03/2026 01:06:26</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:19:15</t>
+          <t>02/03/2026 01:07:57</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:25</t>
+          <t>02/03/2026 01:06:26</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>07h 23min</t>
+          <t>07h 37min</t>
         </is>
       </c>
     </row>
@@ -7773,11 +7773,11 @@
         </is>
       </c>
       <c r="B133" s="4" t="n">
-        <v>2097707</v>
+        <v>2097731</v>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -7787,27 +7787,27 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13075146 - NILSON GENTIL DE OLIVERIRA FILHO  - LQN9H23 - FLX6806</t>
+          <t>CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:23</t>
+          <t>02/03/2026 03:02:23</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:28:40</t>
+          <t>02/03/2026 04:17:34</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:23</t>
+          <t>02/03/2026 03:02:23</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>07h 13min</t>
+          <t>04h 27min</t>
         </is>
       </c>
     </row>
@@ -7833,11 +7833,11 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>2097780</v>
+        <v>2097769</v>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -7847,27 +7847,27 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> emissão Reckitt SHI2603020005 NF- 627250</t>
+          <t>EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Daniela da Cruz Moreira</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:18:23</t>
+          <t>02/03/2026 05:24:24</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:28:47</t>
+          <t>02/03/2026 05:37:03</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:18:23</t>
+          <t>02/03/2026 05:24:24</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>02h 13min</t>
+          <t>03h 08min</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="B135" s="4" t="n">
-        <v>2097758</v>
+        <v>2097740</v>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -7917,17 +7917,17 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:28</t>
+          <t>02/03/2026 03:44:23</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:17:01</t>
+          <t>02/03/2026 04:18:12</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:28</t>
+          <t>02/03/2026 03:44:23</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>03h 25min</t>
+          <t>04h 27min</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>2097730</v>
+        <v>2097747</v>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151066 - Série: 1</t>
+          <t>ENC: CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:58:24</t>
+          <t>02/03/2026 04:00:25</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:54</t>
+          <t>02/03/2026 04:03:15</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:58:24</t>
+          <t>02/03/2026 04:00:25</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>05h 39min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -8013,11 +8013,11 @@
         </is>
       </c>
       <c r="B137" s="4" t="n">
-        <v>2097740</v>
+        <v>2097700</v>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -8027,27 +8027,27 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NORDESTE - ASR0C31</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Gabriel  Molinari de Moraes</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:23</t>
+          <t>02/03/2026 01:06:23</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:18:12</t>
+          <t>02/03/2026 01:19:09</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:23</t>
+          <t>02/03/2026 01:06:23</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>07h 26min</t>
         </is>
       </c>
     </row>
@@ -8073,11 +8073,11 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>2097694</v>
+        <v>2097701</v>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -8087,27 +8087,27 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
+          <t>CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:26:24</t>
+          <t>02/03/2026 01:06:25</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:34:41</t>
+          <t>02/03/2026 01:24:48</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:26:25</t>
+          <t>02/03/2026 01:06:25</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>08h 07min</t>
+          <t>07h 20min</t>
         </is>
       </c>
     </row>
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="B139" s="4" t="n">
-        <v>2097695</v>
+        <v>2097721</v>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -8147,27 +8147,27 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
+          <t>ENC: Cancelamento da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151037 - Série: 1</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Monitoramento Ipaussu</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:30:25</t>
+          <t>02/03/2026 02:06:23</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:43:18</t>
+          <t>02/03/2026 02:10:16</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:30:25</t>
+          <t>02/03/2026 02:06:23</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>07h 59min</t>
+          <t>06h 35min</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>2097715</v>
+        <v>2097713</v>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -8217,17 +8217,17 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:25</t>
+          <t>02/03/2026 01:44:25</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:52:50</t>
+          <t>02/03/2026 01:45:50</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:50:25</t>
+          <t>02/03/2026 01:44:25</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>06h 49min</t>
+          <t>06h 59min</t>
         </is>
       </c>
     </row>
@@ -8253,11 +8253,11 @@
         </is>
       </c>
       <c r="B141" s="4" t="n">
-        <v>2097711</v>
+        <v>2097760</v>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -8267,27 +8267,27 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:24</t>
+          <t>02/03/2026 04:54:23</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:39:03</t>
+          <t>02/03/2026 04:56:27</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:24</t>
+          <t>02/03/2026 04:54:23</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>07h 03min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -8313,11 +8313,11 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>2097722</v>
+        <v>2097770</v>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -8327,27 +8327,27 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo PPH8A77</t>
+          <t>ENC: CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:14:25</t>
+          <t>02/03/2026 05:24:26</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:16:29</t>
+          <t>02/03/2026 05:36:41</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:14:25</t>
+          <t>02/03/2026 05:24:26</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>06h 25min</t>
+          <t>03h 08min</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="B143" s="4" t="n">
-        <v>2097762</v>
+        <v>2097772</v>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43675 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -8397,17 +8397,17 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:24</t>
+          <t>02/03/2026 05:26:26</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:02:47</t>
+          <t>02/03/2026 05:36:49</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:00:24</t>
+          <t>02/03/2026 05:26:26</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>03h 39min</t>
+          <t>03h 08min</t>
         </is>
       </c>
     </row>
@@ -8433,11 +8433,11 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>2097774</v>
+        <v>2097766</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -8447,27 +8447,27 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>CTe 43676 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151077 - Série: 1</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:23</t>
+          <t>02/03/2026 05:16:23</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:01:20</t>
+          <t>02/03/2026 05:16:50</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:50:23</t>
+          <t>02/03/2026 05:16:23</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>02h 41min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -8493,11 +8493,11 @@
         </is>
       </c>
       <c r="B145" s="4" t="n">
-        <v>2097760</v>
+        <v>2097715</v>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -8507,27 +8507,27 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13070370 - EVANDRO MARCOS MOREIRA DE REZENDE - ODP4H37 - ETZ8146</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:54:23</t>
+          <t>02/03/2026 01:50:25</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:56:27</t>
+          <t>02/03/2026 01:52:50</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:54:23</t>
+          <t>02/03/2026 01:50:25</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>06h 52min</t>
         </is>
       </c>
     </row>
@@ -8553,11 +8553,11 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>2097752</v>
+        <v>2097717</v>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -8567,27 +8567,27 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:26</t>
+          <t>02/03/2026 01:56:23</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:37:54</t>
+          <t>02/03/2026 02:06:32</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:34:26</t>
+          <t>02/03/2026 01:56:23</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>06h 39min</t>
         </is>
       </c>
     </row>
@@ -8613,11 +8613,11 @@
         </is>
       </c>
       <c r="B147" s="4" t="n">
-        <v>2097698</v>
+        <v>2097697</v>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -8627,27 +8627,27 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43664 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:24</t>
+          <t>02/03/2026 00:36:24</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:58:42</t>
+          <t>02/03/2026 00:43:23</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 00:54:24</t>
+          <t>02/03/2026 00:36:24</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>07h 43min</t>
+          <t>08h 02min</t>
         </is>
       </c>
     </row>
@@ -8673,11 +8673,11 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>2097734</v>
+        <v>2097749</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -8687,27 +8687,27 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.547 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:23</t>
+          <t>02/03/2026 04:18:25</t>
         </is>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:17:57</t>
+          <t>02/03/2026 04:38:17</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:12:23</t>
+          <t>02/03/2026 04:18:25</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>04h 07min</t>
         </is>
       </c>
     </row>
@@ -8733,11 +8733,11 @@
         </is>
       </c>
       <c r="B149" s="4" t="n">
-        <v>2097741</v>
+        <v>2097776</v>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -8747,27 +8747,27 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.549 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Operacional Pepsico</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:25</t>
+          <t>02/03/2026 06:02:23</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:44</t>
+          <t>02/03/2026 06:13:38</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:44:25</t>
+          <t>02/03/2026 06:02:23</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>02h 31min</t>
         </is>
       </c>
     </row>
@@ -8793,11 +8793,11 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>2097702</v>
+        <v>2097710</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -8807,27 +8807,27 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:26</t>
+          <t>02/03/2026 01:36:23</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:07:57</t>
+          <t>02/03/2026 01:44:42</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:26</t>
+          <t>02/03/2026 01:36:23</t>
         </is>
       </c>
       <c r="J150" s="4" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>07h 34min</t>
+          <t>07h 00min</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="B151" s="4" t="n">
-        <v>2097718</v>
+        <v>2097762</v>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43673 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -8877,17 +8877,17 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:24</t>
+          <t>02/03/2026 05:00:24</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:58:00</t>
+          <t>02/03/2026 05:02:47</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:24</t>
+          <t>02/03/2026 05:00:24</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>06h 44min</t>
+          <t>03h 42min</t>
         </is>
       </c>
     </row>
@@ -8913,11 +8913,11 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>2097727</v>
+        <v>2097768</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -8927,27 +8927,27 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151065 - Série: 1</t>
+          <t>CTe 43674 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:42:23</t>
+          <t>02/03/2026 05:24:23</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:45:28</t>
+          <t>02/03/2026 05:44:34</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:42:23</t>
+          <t>02/03/2026 05:24:23</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>05h 56min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -8973,11 +8973,11 @@
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>2097737</v>
+        <v>2097777</v>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -8987,27 +8987,27 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.548 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: INFORMAÇÕES PARA EMISSÃO DE CTE - 02/03/2026</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:25</t>
+          <t>02/03/2026 06:06:24</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:26</t>
+          <t>02/03/2026 06:14:59</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:24:25</t>
+          <t>02/03/2026 06:06:24</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -9033,11 +9033,11 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>2097724</v>
+        <v>2097780</v>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -9047,27 +9047,27 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>CTe 2492 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t xml:space="preserve"> emissão Reckitt SHI2603020005 NF- 627250</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Daniela da Cruz Moreira</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:28</t>
+          <t>02/03/2026 06:18:23</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:29:44</t>
+          <t>02/03/2026 06:28:47</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:28:28</t>
+          <t>02/03/2026 06:18:23</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>06h 12min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -9093,11 +9093,11 @@
         </is>
       </c>
       <c r="B155" s="4" t="n">
-        <v>2097705</v>
+        <v>2097744</v>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>FILIAL JACAREI</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -9107,27 +9107,27 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>encerramento da MDF-e do veículo IXR2D00</t>
+          <t>CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Denis da Silva Moreira</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:26</t>
+          <t>02/03/2026 03:58:23</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:21:00</t>
+          <t>02/03/2026 04:38:11</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:14:26</t>
+          <t>02/03/2026 03:58:23</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>07h 21min</t>
+          <t>04h 07min</t>
         </is>
       </c>
     </row>
@@ -9153,11 +9153,11 @@
         </is>
       </c>
       <c r="B156" s="4" t="n">
-        <v>2097716</v>
+        <v>2097757</v>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -9167,27 +9167,27 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:23</t>
+          <t>02/03/2026 04:52:26</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:41</t>
+          <t>02/03/2026 04:55:23</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:54:23</t>
+          <t>02/03/2026 04:52:26</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>06h 47min</t>
+          <t>03h 50min</t>
         </is>
       </c>
     </row>
@@ -9213,11 +9213,11 @@
         </is>
       </c>
       <c r="B157" s="4" t="n">
-        <v>2097779</v>
+        <v>2097759</v>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Pepsico</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -9227,27 +9227,27 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
+          <t>ENC: CT-e: 000.046.552 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Operacional Pepsico</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:16:23</t>
+          <t>02/03/2026 04:52:29</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:25:20</t>
+          <t>02/03/2026 04:55:28</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 06:16:23</t>
+          <t>02/03/2026 04:52:29</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>02h 17min</t>
+          <t>03h 50min</t>
         </is>
       </c>
     </row>
@@ -9273,11 +9273,11 @@
         </is>
       </c>
       <c r="B158" s="4" t="n">
-        <v>2097744</v>
+        <v>2097698</v>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -9287,27 +9287,27 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>CTe 43669 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.541 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:23</t>
+          <t>02/03/2026 00:54:24</t>
         </is>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:38:11</t>
+          <t>02/03/2026 00:58:42</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:58:23</t>
+          <t>02/03/2026 00:54:24</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>07h 46min</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="B159" s="4" t="n">
-        <v>2097726</v>
+        <v>2097730</v>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.544 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151066 - Série: 1</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -9357,17 +9357,17 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:27</t>
+          <t>02/03/2026 02:58:24</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:35:25</t>
+          <t>02/03/2026 03:02:54</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:32:27</t>
+          <t>02/03/2026 02:58:24</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>06h 06min</t>
+          <t>05h 42min</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="B160" s="4" t="n">
-        <v>2097701</v>
+        <v>2097746</v>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.542 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.550 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -9417,17 +9417,17 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:25</t>
+          <t>02/03/2026 04:00:23</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:24:48</t>
+          <t>02/03/2026 04:18:35</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:06:25</t>
+          <t>02/03/2026 04:00:23</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>07h 17min</t>
+          <t>04h 26min</t>
         </is>
       </c>
     </row>
@@ -9453,11 +9453,11 @@
         </is>
       </c>
       <c r="B161" s="4" t="n">
-        <v>2097713</v>
+        <v>2097695</v>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>Pepsico</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -9467,27 +9467,27 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 43666 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO PEPSICO - DT 13070916 - JULIO CARLOS PEREIRA MARTINS - CUD6G49 - GAH1691</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Monitoramento Ipaussu</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:25</t>
+          <t>02/03/2026 00:30:25</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:45:50</t>
+          <t>02/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:25</t>
+          <t>02/03/2026 00:30:25</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>06h 56min</t>
+          <t>08h 02min</t>
         </is>
       </c>
     </row>
@@ -9513,11 +9513,11 @@
         </is>
       </c>
       <c r="B162" s="4" t="n">
-        <v>2097717</v>
+        <v>2097750</v>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -9527,27 +9527,27 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>CTe 43667 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 43670 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:23</t>
+          <t>02/03/2026 04:18:29</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 02:06:32</t>
+          <t>02/03/2026 04:18:44</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:56:23</t>
+          <t>02/03/2026 04:18:29</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>06h 35min</t>
+          <t>04h 26min</t>
         </is>
       </c>
     </row>
@@ -9573,11 +9573,11 @@
         </is>
       </c>
       <c r="B163" s="4" t="n">
-        <v>2097710</v>
+        <v>2097767</v>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -9587,27 +9587,27 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>CTe 43665 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151079 - Série: 1</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:23</t>
+          <t>02/03/2026 05:20:24</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:44:42</t>
+          <t>02/03/2026 05:22:43</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:36:23</t>
+          <t>02/03/2026 05:20:24</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>06h 57min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="B164" s="4" t="n">
-        <v>2097732</v>
+        <v>2097729</v>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.546 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -9657,17 +9657,17 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:25</t>
+          <t>02/03/2026 02:50:25</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:11:45</t>
+          <t>02/03/2026 02:51:37</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:02:25</t>
+          <t>02/03/2026 02:50:25</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>05h 30min</t>
+          <t>05h 53min</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="B165" s="4" t="n">
-        <v>2097769</v>
+        <v>2097779</v>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO PEPSICO - DT 13071378 - RUMENIG MORAIS DA SILVA - EZU2H88 - FLX6820</t>
+          <t>RES: 13070358 JULIO CARLOS PEREIRA MARTINS CUD6G49 ERF4I66</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -9717,17 +9717,17 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:24</t>
+          <t>02/03/2026 06:16:23</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:37:03</t>
+          <t>02/03/2026 06:25:20</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 05:24:24</t>
+          <t>02/03/2026 06:16:23</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>03h 05min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -9753,11 +9753,11 @@
         </is>
       </c>
       <c r="B166" s="4" t="n">
-        <v>2097739</v>
+        <v>2097756</v>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -9767,27 +9767,27 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>ENC: Aceite de coleta PepsiCo</t>
+          <t>CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:42:25</t>
+          <t>02/03/2026 04:52:23</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:02:35</t>
+          <t>02/03/2026 05:16:56</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 03:42:25</t>
+          <t>02/03/2026 04:52:23</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -9813,11 +9813,11 @@
         </is>
       </c>
       <c r="B167" s="4" t="n">
-        <v>2097757</v>
+        <v>2097751</v>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -9827,27 +9827,27 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.046.551 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 43671 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:26</t>
+          <t>02/03/2026 04:34:23</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:55:23</t>
+          <t>02/03/2026 04:43:51</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>02/03/2026 04:52:26</t>
+          <t>02/03/2026 04:34:23</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>03h 46min</t>
+          <t>04h 01min</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>12min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>12min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10280,42 +10280,42 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2097856</v>
+        <v>2097838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>ANTONIO CARLOS DE PAULA SOARES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.006.921 / 061 - RITMO LOGISTICA S/A</t>
+          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Victor Oliveira Lamy</t>
+          <t>Priscila Eredes da Silva Lourenço</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:23</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:23</t>
+          <t>02/03/2026 08:16:23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 05 Min</t>
+          <t xml:space="preserve"> 00 Hs 27 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -10336,11 +10336,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2097859</v>
+        <v>2097862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>FILIAL JACAREI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10350,23 +10350,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RES: EMBARQUE 09 MOTORES ARGENTINA -LCB SCANIA- TRANSPORTADOR RITMO LOGISTICA -25/02/2025</t>
+          <t>EMITIR CTE IVV2A82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Matheus Braz de Moura</t>
+          <t>Adriano Francisco Souza</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02/03/2026 08:38:25</t>
+          <t>02/03/2026 08:42:26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>02/03/2026 08:38:25</t>
+          <t>02/03/2026 08:42:26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -10392,11 +10392,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2097858</v>
+        <v>2097864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FILIAL TAQUARI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10406,28 +10406,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RES: A66510 -Comunicado de Desagregação DEXCO Taquari  IJH-0258</t>
+          <t>ENC: CTe 43682 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rafael da Silva Zang</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:36:25</t>
+          <t>02/03/2026 08:42:29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026 08:36:25</t>
+          <t>02/03/2026 08:42:29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 03 Min</t>
+          <t xml:space="preserve"> 00 Hs 01 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>03min</t>
+          <t>01min</t>
         </is>
       </c>
     </row>
@@ -10448,11 +10448,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2097847</v>
+        <v>2097859</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10462,28 +10462,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RES: Estadias Adiantadas Fevereiro 2026 - R$99.700,00 - Parte 4</t>
+          <t>RES: EMBARQUE 09 MOTORES ARGENTINA -LCB SCANIA- TRANSPORTADOR RITMO LOGISTICA -25/02/2025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>William Marques da Silva</t>
+          <t>Matheus Braz de Moura</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02/03/2026 08:28:25</t>
+          <t>02/03/2026 08:38:25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>02/03/2026 08:28:26</t>
+          <t>02/03/2026 08:38:25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 11 Min</t>
+          <t xml:space="preserve"> 00 Hs 05 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -10504,42 +10504,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2097838</v>
+        <v>2097865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANTONIO CARLOS DE PAULA SOARES</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RES: EMISSÃO CTE FRETE RITMO - FRETE JABOTICABAL X MOGI GUAÇU X CURITIBA</t>
+          <t>ENC: Envio da NFe - Emitente: PEPSICO DO BRASIL IND COM ALI LTDA N.Doc: 151086 - Série: 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Priscila Eredes da Silva Lourenço</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:42:31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>02/03/2026 08:16:23</t>
+          <t>02/03/2026 08:42:31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 23 Min</t>
+          <t xml:space="preserve"> 00 Hs 01 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>01min</t>
         </is>
       </c>
     </row>
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2097857</v>
+        <v>2097854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>MERCOSUL - MATRIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10574,28 +10574,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENC: Nenhuma Duplicidade Encontrada</t>
+          <t>W10 CRT 862 | LEAR PRESTIGE | BSAS X NVT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Osvaldo Antonio Moralez</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:25</t>
+          <t>02/03/2026 08:32:25</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>02/03/2026 08:34:25</t>
+          <t>02/03/2026 08:32:26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 05 Min</t>
+          <t xml:space="preserve"> 00 Hs 11 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>11min</t>
         </is>
       </c>
     </row>
@@ -10616,11 +10616,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2097851</v>
+        <v>2097863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10630,28 +10630,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Re: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
+          <t>CTe 43682 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:30</t>
+          <t>02/03/2026 08:42:28</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:30</t>
+          <t>02/03/2026 08:42:28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 09 Min</t>
+          <t xml:space="preserve"> 00 Hs 01 Min</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>01min</t>
         </is>
       </c>
     </row>
@@ -10672,42 +10672,42 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2097846</v>
+        <v>2097860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ENC: [FORVIA - DIVISION FAS - SAO JOSE DOS PINHAIS SITE - NATIONAL ROAD CARRIER] Announcement - Mastercargo</t>
+          <t>RES: CTe 278 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marcelo Ramos</t>
+          <t>Ingrid de Sousa Costa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02/03/2026 08:26:25</t>
+          <t>02/03/2026 08:40:26</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>02/03/2026 08:26:25</t>
+          <t>02/03/2026 08:40:26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 13 Min</t>
+          <t xml:space="preserve"> 00 Hs 03 Min</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>03min</t>
         </is>
       </c>
     </row>
@@ -10728,11 +10728,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2097854</v>
+        <v>2097851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10742,28 +10742,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>W10 CRT 862 | LEAR PRESTIGE | BSAS X NVT</t>
+          <t>Re: EMISSÃO DE CTE- IJT-3F45--------------DEXCO------------------6100685636</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Osvaldo Antonio Moralez</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:25</t>
+          <t>02/03/2026 08:30:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>02/03/2026 08:32:26</t>
+          <t>02/03/2026 08:30:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 07 Min</t>
+          <t xml:space="preserve"> 00 Hs 13 Min</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -10784,42 +10784,42 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2097833</v>
+        <v>2097852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>RAIZEN CENTRO-SUL PAULISTA S.A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PENDÊNCIAS</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RES: Pendência de Emissão - 20/02/2026.</t>
+          <t>RES: CTe 278 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bruno Castro</t>
+          <t>Rodrigo Couto da Silva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:25</t>
+          <t>02/03/2026 08:30:32</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>02/03/2026 08:10:26</t>
+          <t>02/03/2026 08:30:32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 29 Min</t>
+          <t xml:space="preserve"> 00 Hs 13 Min</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -10840,42 +10840,42 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2097852</v>
+        <v>2097846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RAIZEN CENTRO-SUL PAULISTA S.A</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RES: CTe 278 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: [FORVIA - DIVISION FAS - SAO JOSE DOS PINHAIS SITE - NATIONAL ROAD CARRIER] Announcement - Mastercargo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rodrigo Couto da Silva</t>
+          <t>Marcelo Ramos</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:32</t>
+          <t>02/03/2026 08:26:25</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:32</t>
+          <t>02/03/2026 08:26:25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 09 Min</t>
+          <t xml:space="preserve"> 00 Hs 17 Min</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -10896,52 +10896,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2097853</v>
+        <v>2097833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FILIAL PONTA GROSSA</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>PENDÊNCIAS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Romaneio 1791087 - EMU6F61 - DT 12225427</t>
+          <t>RES: Pendência de Emissão - 20/02/2026.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Antunes Steiner</t>
+          <t>Bruno Castro</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:33</t>
+          <t>02/03/2026 08:10:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:33</t>
+          <t>02/03/2026 08:10:26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 09 Min</t>
+          <t xml:space="preserve"> 00 Hs 33 Min</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Pendente de Atendimento</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -10952,11 +10952,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2097849</v>
+        <v>2097861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MERCOSUL - MATRIZ</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10966,38 +10966,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>W10 CRT 860 861 | MARO MAHLE VOLVO | BAIRES X CURITIBA</t>
+          <t>ENC: Aceite de coleta PepsiCo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Osvaldo Antonio Moralez</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:27</t>
+          <t>02/03/2026 08:42:25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>02/03/2026 08:30:27</t>
+          <t>02/03/2026 08:42:25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 09 Min</t>
+          <t xml:space="preserve"> 00 Hs 01 Min</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Pendente de Atendimento</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>06min</t>
+          <t>01min</t>
         </is>
       </c>
     </row>
@@ -11008,11 +11008,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2097840</v>
+        <v>2097866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>NESTLE  - ITUIUTABA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11022,38 +11022,206 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CTE RITMO Fevereiro | Situação</t>
+          <t>VEÍCULOS PENDENTES DE CHEGADA NA PLANTA RITMO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gustavo Delirio Luiz</t>
+          <t>Execucao,Operacao,CORDEIROPOLIS,,BR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>02/03/2026 08:18:27</t>
+          <t>02/03/2026 08:42:32</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
+          <t>02/03/2026 08:42:32</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 01 Min</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>01min</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2097853</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FILIAL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Romaneio 1791087 - EMU6F61 - DT 12225427</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Antunes Steiner</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:33</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:33</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 13 Min</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>04min</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2097849</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MERCOSUL - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>W10 CRT 860 861 | MARO MAHLE VOLVO | BAIRES X CURITIBA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Osvaldo Antonio Moralez</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:27</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:30:27</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 13 Min</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10min</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2097840</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CTE RITMO Fevereiro | Situação</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gustavo Delirio Luiz</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>02/03/2026 08:18:27</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 21 Min</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>02/03/2026 08:18:27</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 25 Min</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Em Atendimento</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>11min</t>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11334,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2097728</v>
+        <v>2097703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -11180,7 +11348,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -11190,18 +11358,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:23</t>
+          <t>02/03/2026 01:12:23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>02/03/2026 02:50:23</t>
+          <t>02/03/2026 01:12:23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 05 Hs 49 Min</t>
+          <t xml:space="preserve"> 07 Hs 31 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -11211,7 +11379,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>04h 31min</t>
+          <t>07h 19min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -11225,7 +11393,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2097703</v>
+        <v>2097728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -11239,7 +11407,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CT-e: 000.046.543 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.046.545 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -11249,18 +11417,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:12:23</t>
+          <t>02/03/2026 02:50:23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>02/03/2026 01:12:23</t>
+          <t>02/03/2026 02:50:23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 07 Hs 27 Min</t>
+          <t xml:space="preserve"> 05 Hs 53 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -11270,7 +11438,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07h 15min</t>
+          <t>04h 35min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -11319,7 +11487,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 06 Hs 11 Min</t>
+          <t xml:space="preserve"> 06 Hs 15 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -11329,7 +11497,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>06h 03min</t>
+          <t>06h 07min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -11378,7 +11546,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 06 Hs 07 Min</t>
+          <t xml:space="preserve"> 06 Hs 11 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -11388,7 +11556,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>06h 00min</t>
+          <t>06h 04min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -11398,7 +11566,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -11417,7 +11585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -11436,7 +11604,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -11689,7 +11857,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -11708,7 +11876,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -11727,7 +11895,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -12095,17 +12263,17 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2m 59s</t>
+          <t>4m 22s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -7,6 +7,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DadosAte" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outros Setores" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atendentes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendencias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Métricas Gerais" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clientes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GraficoHora" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +55,9 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -72,7 +83,7 @@
       <patternFill/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -218,11 +229,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -235,6 +252,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13720,4 +13740,2169 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Em execução</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Núm. protocolo</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Abertura</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Fechamento</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Primeira interação</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Aberto há</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Situação</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Alterado há</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2100943</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MASTERCARGO - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Viagem 2 (VOLTA) - Emissão Forvia - Emerson Julio Miranda BEY5D57 // ANE6835 - Manifesto: 255670220</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Thaiane Elisamari Moraes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:42:24</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:42:24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 06 Min</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>06min</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2100949</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CT-e: 000.006.933 / 061 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:44:30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:44:30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 04 Min</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>04min</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2100951</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MASTERCARGO - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Viagem 3 (IDA) - Emissão Forvia - Emerson Julio Miranda BEY5D57// ANE6835 - Manifesto: 255670224</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thaiane Elisamari Moraes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:46:25</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:46:25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 02 Min</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>02min</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2100954</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MASTERCARGO - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RES: Viagem 3 (IDA) - Emissão Forvia - Emerson Julio Miranda BEY5D57// ANE6835 - Manifesto: 255670224</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Thaiane Elisamari Moraes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:48:33</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:48:33</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 00 Min</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00min</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2100955</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FILIAL MOGI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PEDAGIO AVULSO - GZV5G07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wellington Graciano Nascimento</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:48:35</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:48:35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 00 Min</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00min</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2100953</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MASTERCARGO - MATRIZ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Viagem 3 (VOLTA) - Emissão Forvia - Emerson Julio Miranda BEY5D57// ANE6835 - Manifesto: RET. EMB 255670224</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Thaiane Elisamari Moraes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:48:25</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:48:26</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 00 Min</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00min</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2100952</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CONTROLE DE VÍNCULOS | AGING</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Heloisa Debarba Hansen</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:46:27</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:46:27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 02 Min</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>02min</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2100947</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.769 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:44:26</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:44:26</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 04 Min</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>04min</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2100942</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FILIAL TAQUARI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Senhas Bob- Dexco -Taquari-RS - 05/03/2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rafael da Silva Zang</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:42:23</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:42:23</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 06 Min</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00min</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2100925</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FATURAMENTO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RES: Faturas em atraso - Cargill  - Chamado #336345 519mil - 432mil acima de 60 dias</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanessa Czelusniak</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:32:24</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:32:24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 16 Min</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>09min</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2100941</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RECKITT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>emissão Reckitt SHI2603050007 NF- 627525</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Daniela da Cruz Moreira</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:40:27</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:40:27</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 08 Min</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>04min</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Em execução</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Núm. protocolo</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Abertura</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Fechamento</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Primeira interação</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Aberto há</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Situação</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Alterado há</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Contagem Única</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Responsável: </t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2100751</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SEGUROS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CT-e NÃO EVOLUIU- 602975171</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Marcelo Marques Oliveira, Anderson</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:46:25</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:46:25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 08 Hs 02 Min</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>07h 26min</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2100749</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SEGUROS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.749 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:44:34</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:44:34</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 08 Hs 04 Min</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>07h 40min</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2100934</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FILIAIS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.767 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:38:23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:38:23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 10 Min</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>04min</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2100937</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FILIAIS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.768 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:38:27</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>05/03/2026 08:38:27</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 10 Min</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>03min</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2100747</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FILIAIS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.748 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:44:31</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:44:31</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 08 Hs 04 Min</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>07h 44min</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2100734</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FILIAIS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RE: Emissão de CT-e manual RITMO.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Feitosa de Santana, Sabrina</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:30:31</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>05/03/2026 00:30:31</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 08 Hs 18 Min</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>07h 49min</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2100818</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CT-e: 000.046.754 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>05/03/2026 03:06:27</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>05/03/2026 03:06:27</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 05 Hs 42 Min</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05h 17min</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Responsável: LUANA CRISTINE SA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Responsável: MELISSA MARIA CALEFFI ZECHINI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Responsável: PAULO ROBERTO DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>18</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>18</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>atendimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Atendimentos</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>tempoMedio</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Herica Lidia Barbosa Silva</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11m 26s</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jean Lucas Ferreira</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12m 52s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Luana Cristine Sa dos Santos</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>38</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13m 1s</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Melissa Maria Caleffi Zechini</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>22m 4s</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Paulo Roberto da Silva Junior</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16m 46s</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sheila Catarina de Campos</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>106</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7m 47s</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Núm. protocolo</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Abertura</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>chamadosFinalizados</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>chamadosPendentes</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>filaEspera</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>chamadosEmAtendimento</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>totalAtendimentos</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>tempoMedioEspera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>225</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2m 50s</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>atendimentos</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>porcentagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>77</v>
+      </c>
+      <c r="C2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HEINEKEN</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CCR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>hora</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>atendimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0h</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121289</v>
+        <v>2121317</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>02h 56min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121320</v>
+        <v>2121318</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 27min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121293</v>
+        <v>2121320</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>02h 47min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121315</v>
+        <v>2121329</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>17min</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121279</v>
+        <v>2121331</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>17min</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121316</v>
+        <v>2121278</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121327</v>
+        <v>2121281</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>18min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121313</v>
+        <v>2121279</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121296</v>
+        <v>2121324</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121286</v>
+        <v>2121296</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>03h 16min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121284</v>
+        <v>2121326</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>02h 56min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121329</v>
+        <v>2121284</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121321</v>
+        <v>2121325</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121325</v>
+        <v>2121293</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1517,17 +1517,17 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>02h 51min</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121309</v>
+        <v>2121319</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121322</v>
+        <v>2121323</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>01h 24min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121298</v>
+        <v>2121309</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121299</v>
+        <v>2121322</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>01h 28min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121311</v>
+        <v>2121314</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1817,17 +1817,17 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>41min</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121331</v>
+        <v>2121327</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>22min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121281</v>
+        <v>2121311</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121282</v>
+        <v>2121321</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>02h 56min</t>
+          <t>17min</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121295</v>
+        <v>2121315</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2057,17 +2057,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>02h 42min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121314</v>
+        <v>2121299</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121326</v>
+        <v>2121282</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121319</v>
+        <v>2121295</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>01h 27min</t>
+          <t>02h 45min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121323</v>
+        <v>2121298</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>02h 36min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121318</v>
+        <v>2121289</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121278</v>
+        <v>2121286</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>03h 19min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121324</v>
+        <v>2121316</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2477,17 +2477,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121317</v>
+        <v>2121313</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -2628,11 +2628,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2121307</v>
+        <v>2121312</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2642,27 +2642,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>03h 17min</t>
+          <t>03h 21min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121302</v>
+        <v>2121277</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>01h 24min</t>
+          <t>02h 32min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121287</v>
+        <v>2121297</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>01h 25min</t>
+          <t>02h 39min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121291</v>
+        <v>2121310</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121305</v>
+        <v>2121292</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>01h 14min</t>
+          <t>02h 06min</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 03min</t>
+          <t>02h 06min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121301</v>
+        <v>2121283</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 14min</t>
+          <t>02h 40min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121285</v>
+        <v>2121303</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 03min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121312</v>
+        <v>2121291</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 13min</t>
+          <t>02h 17min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121303</v>
+        <v>2121301</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>02h 18min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121277</v>
+        <v>2121285</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 29min</t>
+          <t>02h 06min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121292</v>
+        <v>2121307</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>02h 03min</t>
+          <t>01h 13min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121297</v>
+        <v>2121287</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 36min</t>
+          <t>01h 29min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121310</v>
+        <v>2121305</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121283</v>
+        <v>2121302</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>01h 27min</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 13 Min</t>
+          <t xml:space="preserve"> 00 Hs 16 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 13 Min</t>
+          <t xml:space="preserve"> 00 Hs 16 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 03 Min</t>
+          <t xml:space="preserve"> 02 Hs 06 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -3988,11 +3988,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121313</v>
+        <v>2121308</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4002,28 +4002,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 01 Hs 43 Min</t>
+          <t xml:space="preserve"> 01 Hs 52 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4033,63 +4033,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16min</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2121308</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FILIAL MOGI</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MANIFESTAR NF DJC1E58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Jonas Antonio Torres Garcia</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:34:40</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:34:40</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 01 Hs 49 Min</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>01h 42min</t>
+          <t>01h 45min</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4136,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -4237,7 +4181,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 55 Min</t>
+          <t xml:space="preserve"> 02 Hs 58 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4247,11 +4191,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>18min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4296,7 +4240,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 53 Min</t>
+          <t xml:space="preserve"> 02 Hs 56 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4306,11 +4250,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>02h 13min</t>
+          <t>02h 17min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -4355,7 +4299,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 01 Hs 55 Min</t>
+          <t xml:space="preserve"> 01 Hs 58 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4365,11 +4309,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01h 11min</t>
+          <t>01h 14min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -4414,7 +4358,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 23 Min</t>
+          <t xml:space="preserve"> 03 Hs 26 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4424,11 +4368,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01h 30min</t>
+          <t>01h 34min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -4447,7 +4391,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -4466,7 +4410,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -4485,7 +4429,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -4506,13 +4450,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4525,13 +4469,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4544,13 +4488,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4563,7 +4507,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -4584,7 +4528,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4603,7 +4547,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -4622,7 +4566,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -4641,13 +4585,13 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -4660,13 +4604,13 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -4679,13 +4623,13 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -4698,7 +4642,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4898,17 +4842,17 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10m 5s</t>
+          <t>7m 1s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121317</v>
+        <v>2121327</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>26min</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121318</v>
+        <v>2121323</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121320</v>
+        <v>2121325</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -857,17 +857,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121329</v>
+        <v>2121309</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121331</v>
+        <v>2121313</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>08min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121278</v>
+        <v>2121329</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>21min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121281</v>
+        <v>2121314</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>45min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121279</v>
+        <v>2121315</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121324</v>
+        <v>2121317</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121296</v>
+        <v>2121318</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>02h 30min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121326</v>
+        <v>2121319</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121284</v>
+        <v>2121321</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>21min</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121325</v>
+        <v>2121322</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121293</v>
+        <v>2121299</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>02h 51min</t>
+          <t>02h 34min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121319</v>
+        <v>2121279</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121323</v>
+        <v>2121281</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121309</v>
+        <v>2121282</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121322</v>
+        <v>2121295</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>02h 49min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121314</v>
+        <v>2121316</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>41min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121327</v>
+        <v>2121326</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>22min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121311</v>
+        <v>2121320</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121321</v>
+        <v>2121298</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>02h 40min</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121315</v>
+        <v>2121286</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2057,17 +2057,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>03h 23min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121299</v>
+        <v>2121284</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>02h 30min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121282</v>
+        <v>2121278</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121295</v>
+        <v>2121289</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>02h 45min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121298</v>
+        <v>2121296</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>02h 36min</t>
+          <t>02h 34min</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121289</v>
+        <v>2121331</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>21min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121286</v>
+        <v>2121324</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>03h 19min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121316</v>
+        <v>2121293</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>02h 55min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121313</v>
+        <v>2121311</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -2628,11 +2628,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2121312</v>
+        <v>2121297</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2642,27 +2642,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>02h 43min</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121276</v>
+        <v>2121283</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>03h 21min</t>
+          <t>02h 44min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121277</v>
+        <v>2121312</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>02h 32min</t>
+          <t>01h 51min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121297</v>
+        <v>2121307</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>01h 17min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121310</v>
+        <v>2121292</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>02h 10min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121292</v>
+        <v>2121301</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>02h 06min</t>
+          <t>02h 22min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121294</v>
+        <v>2121302</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 06min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121283</v>
+        <v>2121294</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 40min</t>
+          <t>02h 10min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121303</v>
+        <v>2121291</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>01h 51min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121291</v>
+        <v>2121276</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>03h 25min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121300</v>
+        <v>2121305</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 17min</t>
+          <t>01h 22min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121301</v>
+        <v>2121300</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>02h 18min</t>
+          <t>02h 21min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121285</v>
+        <v>2121303</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 06min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121307</v>
+        <v>2121285</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>01h 13min</t>
+          <t>02h 10min</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>01h 33min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121305</v>
+        <v>2121277</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>02h 36min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121302</v>
+        <v>2121310</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>01h 27min</t>
+          <t>01h 51min</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2121328</v>
+        <v>2121330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3844,18 +3844,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 16 Min</t>
+          <t xml:space="preserve"> 00 Hs 20 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121330</v>
+        <v>2121328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3900,18 +3900,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 16 Min</t>
+          <t xml:space="preserve"> 00 Hs 20 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -3932,11 +3932,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121304</v>
+        <v>2121308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3946,28 +3946,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 06 Min</t>
+          <t xml:space="preserve"> 01 Hs 56 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3977,63 +3977,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20min</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2121308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FILIAL MOGI</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MANIFESTAR NF DJC1E58</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Jonas Antonio Torres Garcia</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:34:40</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:34:40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 01 Hs 52 Min</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>01h 45min</t>
+          <t>01h 49min</t>
         </is>
       </c>
     </row>
@@ -4048,7 +3992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,7 +4125,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 58 Min</t>
+          <t xml:space="preserve"> 03 Hs 02 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4191,7 +4135,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18min</t>
+          <t>22min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4205,11 +4149,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121290</v>
+        <v>2121304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4219,28 +4163,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 56 Min</t>
+          <t xml:space="preserve"> 02 Hs 10 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4250,7 +4194,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>02h 17min</t>
+          <t>03min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4264,42 +4208,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121306</v>
+        <v>2121280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 01 Hs 58 Min</t>
+          <t xml:space="preserve"> 03 Hs 30 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4309,7 +4253,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01h 14min</t>
+          <t>01h 37min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4323,42 +4267,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121280</v>
+        <v>2121290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 26 Min</t>
+          <t xml:space="preserve"> 03 Hs 00 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4368,7 +4312,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>02h 20min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4376,20 +4320,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>2121306</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FILIAL MARILIA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FILIAIS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ricardo Cardoso da Costa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:28:40</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:28:40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 02 Hs 02 Min</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>01h 18min</t>
+        </is>
+      </c>
       <c r="M7" t="n">
         <v>16</v>
       </c>
@@ -4397,7 +4381,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4416,7 +4400,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4433,12 +4417,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Responsável: JEAN LUCAS FERREIRA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -4454,10 +4436,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Responsável: OXANA ANDRELI DA SILVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -4511,12 +4495,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Responsável: OXANA ANDRELI DA SILVA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -4534,7 +4516,7 @@
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -4553,7 +4535,7 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -4572,7 +4554,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -4585,63 +4567,6 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="n">
-        <v>8</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
-        <v>8</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4668,7 +4593,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4723,7 +4648,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -4842,17 +4767,17 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7m 1s</t>
+          <t>0m 0s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121286</v>
+        <v>2121315</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>03h 27min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121317</v>
+        <v>2121324</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121320</v>
+        <v>2121309</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121278</v>
+        <v>2121311</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121318</v>
+        <v>2121313</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121321</v>
+        <v>2121286</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>03h 30min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121322</v>
+        <v>2121331</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>01h 35min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121331</v>
+        <v>2121293</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>03h 02min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121327</v>
+        <v>2121295</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>02h 56min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121314</v>
+        <v>2121326</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>48min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121281</v>
+        <v>2121317</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121323</v>
+        <v>2121322</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>01h 39min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121289</v>
+        <v>2121316</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>03h 07min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121311</v>
+        <v>2121325</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121313</v>
+        <v>2121318</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121296</v>
+        <v>2121321</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121329</v>
+        <v>2121278</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121284</v>
+        <v>2121281</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>03h 07min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121324</v>
+        <v>2121314</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>52min</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121325</v>
+        <v>2121299</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121295</v>
+        <v>2121279</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>02h 53min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121326</v>
+        <v>2121319</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121298</v>
+        <v>2121320</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121279</v>
+        <v>2121329</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121282</v>
+        <v>2121298</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>03h 07min</t>
+          <t>02h 47min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121319</v>
+        <v>2121327</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>01h 38min</t>
+          <t>33min</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121315</v>
+        <v>2121289</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>03h 11min</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121299</v>
+        <v>2121296</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121316</v>
+        <v>2121284</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>03h 11min</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121293</v>
+        <v>2121282</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>02h 58min</t>
+          <t>03h 11min</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121309</v>
+        <v>2121323</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>01h 07min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>01h 24min</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121303</v>
+        <v>2121301</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>02h 13min</t>
+          <t>02h 29min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121302</v>
+        <v>2121285</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>01h 35min</t>
+          <t>02h 17min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121305</v>
+        <v>2121283</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>01h 26min</t>
+          <t>02h 51min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121294</v>
+        <v>2121300</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>02h 14min</t>
+          <t>02h 28min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121292</v>
+        <v>2121287</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>02h 14min</t>
+          <t>01h 40min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121297</v>
+        <v>2121276</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 47min</t>
+          <t>03h 32min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121285</v>
+        <v>2121291</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 14min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121283</v>
+        <v>2121303</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121276</v>
+        <v>2121297</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>03h 28min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121300</v>
+        <v>2121302</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 24min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121312</v>
+        <v>2121277</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>02h 43min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121310</v>
+        <v>2121308</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>02min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121287</v>
+        <v>2121312</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>01h 36min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121301</v>
+        <v>2121305</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 25min</t>
+          <t>01h 29min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121277</v>
+        <v>2121294</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 40min</t>
+          <t>02h 17min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121291</v>
+        <v>2121310</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,30 +3637,74 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>01h 55min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="4" t="inlineStr"/>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B55" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C55" s="4" t="inlineStr"/>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr"/>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
+        <v>2121292</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:36:40</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:22:19</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:36:40</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>02h 17min</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="4" t="inlineStr"/>
       <c r="B56" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="inlineStr"/>
@@ -3676,7 +3720,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="4" t="inlineStr"/>
       <c r="B57" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
       <c r="D57" s="4" t="inlineStr"/>
@@ -3692,7 +3736,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="4" t="inlineStr"/>
       <c r="B58" s="4" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr"/>
@@ -3708,7 +3752,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="4" t="inlineStr"/>
       <c r="B59" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
@@ -3724,7 +3768,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="4" t="inlineStr"/>
       <c r="B60" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
       <c r="D60" s="4" t="inlineStr"/>
@@ -3736,6 +3780,22 @@
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3748,7 +3808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3855,7 +3915,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 24 Min</t>
+          <t xml:space="preserve"> 00 Hs 27 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3865,7 +3925,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3971,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 24 Min</t>
+          <t xml:space="preserve"> 00 Hs 27 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -3921,63 +3981,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24min</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2121308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FILIAL MOGI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MANIFESTAR NF DJC1E58</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Jonas Antonio Torres Garcia</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:34:40</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:34:40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 02 Hs 00 Min</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>01h 53min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,7 +4084,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -4090,11 +4094,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121306</v>
+        <v>2121304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4104,28 +4108,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 06 Min</t>
+          <t xml:space="preserve"> 02 Hs 17 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4135,11 +4139,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01h 22min</t>
+          <t>10min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4149,7 +4153,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121288</v>
+        <v>2121280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4158,12 +4162,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4173,18 +4177,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 06 Min</t>
+          <t xml:space="preserve"> 03 Hs 37 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4194,11 +4198,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>01h 45min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -4208,7 +4212,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121280</v>
+        <v>2121288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4217,12 +4221,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4232,18 +4236,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 34 Min</t>
+          <t xml:space="preserve"> 03 Hs 09 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4253,11 +4257,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01h 41min</t>
+          <t>29min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -4267,11 +4271,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121304</v>
+        <v>2121290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4281,28 +4285,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 14 Min</t>
+          <t xml:space="preserve"> 03 Hs 07 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4312,11 +4316,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>02h 28min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -4326,11 +4330,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121290</v>
+        <v>2121306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4340,28 +4344,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 04 Min</t>
+          <t xml:space="preserve"> 02 Hs 09 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4371,11 +4375,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02h 24min</t>
+          <t>01h 25min</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -4394,7 +4398,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -4413,7 +4417,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -4432,16 +4436,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Responsável: OXANA ANDRELI DA SILVA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -4453,13 +4455,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4472,13 +4474,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4491,83 +4493,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="n">
-        <v>8</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="n">
-        <v>8</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4659,16 +4585,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34m 47s</t>
+          <t>39m 41s</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -4761,19 +4687,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" t="n">
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4822,7 +4748,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -4835,7 +4761,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -4907,7 +4833,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121315</v>
+        <v>2121318</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121324</v>
+        <v>2121314</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>56min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121309</v>
+        <v>2121293</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>03h 06min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121311</v>
+        <v>2121295</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121313</v>
+        <v>2121326</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121286</v>
+        <v>2121322</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>03h 30min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>28min</t>
+          <t>32min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121293</v>
+        <v>2121299</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>03h 02min</t>
+          <t>02h 45min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121295</v>
+        <v>2121281</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>02h 56min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121326</v>
+        <v>2121311</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121317</v>
+        <v>2121313</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>19min</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121322</v>
+        <v>2121279</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121316</v>
+        <v>2121323</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -1457,17 +1457,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121318</v>
+        <v>2121317</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121321</v>
+        <v>2121329</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>28min</t>
+          <t>32min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121278</v>
+        <v>2121284</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>03h 33min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121281</v>
+        <v>2121278</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>03h 33min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121314</v>
+        <v>2121316</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>52min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121299</v>
+        <v>2121282</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 41min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121279</v>
+        <v>2121289</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>03h 33min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121319</v>
+        <v>2121296</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>02h 45min</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121320</v>
+        <v>2121286</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2057,17 +2057,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>03h 34min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121329</v>
+        <v>2121319</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>28min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121298</v>
+        <v>2121320</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>02h 47min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121327</v>
+        <v>2121321</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>32min</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121289</v>
+        <v>2121315</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>03h 11min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121296</v>
+        <v>2121298</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>02h 41min</t>
+          <t>02h 51min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121284</v>
+        <v>2121327</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>03h 11min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121282</v>
+        <v>2121324</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>03h 11min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121323</v>
+        <v>2121309</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -2628,11 +2628,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2121307</v>
+        <v>2121283</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2642,27 +2642,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>01h 24min</t>
+          <t>02h 55min</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121301</v>
+        <v>2121305</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>02h 29min</t>
+          <t>01h 33min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121285</v>
+        <v>2121312</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>02h 17min</t>
+          <t>02h 02min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121283</v>
+        <v>2121302</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>02h 51min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121300</v>
+        <v>2121292</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>02h 28min</t>
+          <t>02h 21min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121287</v>
+        <v>2121300</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>01h 40min</t>
+          <t>02h 32min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121276</v>
+        <v>2121308</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>03h 32min</t>
+          <t>06min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121291</v>
+        <v>2121276</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>03h 36min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121303</v>
+        <v>2121277</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>02h 47min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121297</v>
+        <v>2121307</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>01h 28min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121302</v>
+        <v>2121287</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>01h 38min</t>
+          <t>01h 44min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121277</v>
+        <v>2121291</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>02h 43min</t>
+          <t>02h 02min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121308</v>
+        <v>2121297</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>02h 54min</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121312</v>
+        <v>2121310</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>02h 02min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121305</v>
+        <v>2121285</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>02h 21min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121294</v>
+        <v>2121301</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 17min</t>
+          <t>02h 33min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121310</v>
+        <v>2121294</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>02h 21min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121292</v>
+        <v>2121303</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 17min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 27 Min</t>
+          <t xml:space="preserve"> 00 Hs 31 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27min</t>
+          <t>31min</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 27 Min</t>
+          <t xml:space="preserve"> 00 Hs 31 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27min</t>
+          <t>31min</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 17 Min</t>
+          <t xml:space="preserve"> 02 Hs 21 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10min</t>
+          <t>14min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4153,42 +4153,42 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121280</v>
+        <v>2121306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 37 Min</t>
+          <t xml:space="preserve"> 02 Hs 13 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01h 45min</t>
+          <t>01h 29min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4212,11 +4212,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121288</v>
+        <v>2121290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4226,28 +4226,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 09 Min</t>
+          <t xml:space="preserve"> 03 Hs 11 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>02h 31min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4271,42 +4271,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121290</v>
+        <v>2121280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 07 Min</t>
+          <t xml:space="preserve"> 03 Hs 41 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 28min</t>
+          <t>01h 48min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4330,11 +4330,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121306</v>
+        <v>2121288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4344,28 +4344,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 09 Min</t>
+          <t xml:space="preserve"> 03 Hs 13 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01h 25min</t>
+          <t>33min</t>
         </is>
       </c>
       <c r="M7" t="n">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121321</v>
+        <v>2121314</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121314</v>
+        <v>2121331</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>39min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121296</v>
+        <v>2121323</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121281</v>
+        <v>2121293</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>03h 13min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121282</v>
+        <v>2121319</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>01h 53min</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121325</v>
+        <v>2121299</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121293</v>
+        <v>2121279</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 09min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121295</v>
+        <v>2121281</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>03h 04min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121326</v>
+        <v>2121289</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121319</v>
+        <v>2121296</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>01h 49min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121320</v>
+        <v>2121322</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 49min</t>
+          <t>01h 50min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121329</v>
+        <v>2121324</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121327</v>
+        <v>2121284</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>40min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121323</v>
+        <v>2121282</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121309</v>
+        <v>2121333</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>01h 17min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121286</v>
+        <v>2121309</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>03h 38min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121317</v>
+        <v>2121320</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 53min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121298</v>
+        <v>2121278</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>02h 54min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121278</v>
+        <v>2121295</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>03h 07min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121333</v>
+        <v>2121286</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>01min</t>
+          <t>03h 41min</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121322</v>
+        <v>2121325</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>01h 46min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121284</v>
+        <v>2121326</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121279</v>
+        <v>2121321</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>39min</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121324</v>
+        <v>2121316</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -2177,17 +2177,17 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 18min</t>
+          <t>01h 53min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121289</v>
+        <v>2121311</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121318</v>
+        <v>2121313</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 49min</t>
+          <t>26min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121316</v>
+        <v>2121317</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 53min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121331</v>
+        <v>2121318</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>01h 53min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121299</v>
+        <v>2121329</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>39min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121311</v>
+        <v>2121298</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>01h 17min</t>
+          <t>02h 58min</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121313</v>
+        <v>2121327</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>22min</t>
+          <t>44min</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121276</v>
+        <v>2121287</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>03h 39min</t>
+          <t>01h 51min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121277</v>
+        <v>2121292</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>02h 51min</t>
+          <t>02h 28min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121297</v>
+        <v>2121312</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>02h 58min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121307</v>
+        <v>2121285</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>02h 29min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121300</v>
+        <v>2121307</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>02h 35min</t>
+          <t>01h 35min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121287</v>
+        <v>2121291</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121305</v>
+        <v>2121303</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>01h 36min</t>
+          <t>02h 27min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121292</v>
+        <v>2121277</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 25min</t>
+          <t>02h 55min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121312</v>
+        <v>2121294</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>02h 28min</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121294</v>
+        <v>2121283</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3252,17 +3252,17 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 25min</t>
+          <t>03h 02min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121291</v>
+        <v>2121297</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>03h 02min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121301</v>
+        <v>2121300</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 36min</t>
+          <t>02h 39min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121308</v>
+        <v>2121301</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>02h 40min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121285</v>
+        <v>2121308</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 25min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121283</v>
+        <v>2121302</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 59min</t>
+          <t>01h 49min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121303</v>
+        <v>2121305</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>02h 23min</t>
+          <t>01h 40min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121302</v>
+        <v>2121310</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>01h 46min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121310</v>
+        <v>2121276</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3732,17 +3732,17 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>03h 43min</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2121330</v>
+        <v>2121328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3964,18 +3964,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 35 Min</t>
+          <t xml:space="preserve"> 00 Hs 38 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 01 Min</t>
+          <t xml:space="preserve"> 00 Hs 04 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121328</v>
+        <v>2121330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4076,18 +4076,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 35 Min</t>
+          <t xml:space="preserve"> 00 Hs 38 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121288</v>
+        <v>2121290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4224,28 +4224,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 17 Min</t>
+          <t xml:space="preserve"> 03 Hs 18 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>02h 39min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4269,11 +4269,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121306</v>
+        <v>2121288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4283,28 +4283,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 17 Min</t>
+          <t xml:space="preserve"> 03 Hs 20 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01h 33min</t>
+          <t>40min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4328,42 +4328,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121304</v>
+        <v>2121280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 25 Min</t>
+          <t xml:space="preserve"> 03 Hs 48 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18min</t>
+          <t>01h 56min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4387,11 +4387,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121290</v>
+        <v>2121304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4401,28 +4401,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 15 Min</t>
+          <t xml:space="preserve"> 02 Hs 28 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 35min</t>
+          <t>21min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4446,42 +4446,42 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121280</v>
+        <v>2121306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 45 Min</t>
+          <t xml:space="preserve"> 02 Hs 20 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01h 52min</t>
+          <t>01h 36min</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33m 55s</t>
+          <t>34m 2s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121314</v>
+        <v>2121322</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>01h 03min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121331</v>
+        <v>2121327</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>39min</t>
+          <t>48min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121323</v>
+        <v>2121279</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>03h 48min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121293</v>
+        <v>2121281</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>03h 13min</t>
+          <t>03h 48min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121319</v>
+        <v>2121295</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>01h 53min</t>
+          <t>03h 11min</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121299</v>
+        <v>2121317</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>02h 52min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121279</v>
+        <v>2121321</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 44min</t>
+          <t>43min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121281</v>
+        <v>2121293</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>03h 44min</t>
+          <t>03h 17min</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121296</v>
+        <v>2121309</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>02h 52min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121322</v>
+        <v>2121316</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121324</v>
+        <v>2121282</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121315</v>
+        <v>2121313</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121284</v>
+        <v>2121326</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121282</v>
+        <v>2121319</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121333</v>
+        <v>2121298</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>03h 02min</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121309</v>
+        <v>2121323</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121320</v>
+        <v>2121286</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>01h 53min</t>
+          <t>03h 45min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121278</v>
+        <v>2121333</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>03h 44min</t>
+          <t>09min</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121295</v>
+        <v>2121296</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>03h 07min</t>
+          <t>02h 56min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121286</v>
+        <v>2121318</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>03h 41min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121325</v>
+        <v>2121331</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>43min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121326</v>
+        <v>2121278</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>03h 48min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121321</v>
+        <v>2121324</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>39min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121316</v>
+        <v>2121320</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 53min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121311</v>
+        <v>2121284</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121313</v>
+        <v>2121329</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>43min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121317</v>
+        <v>2121314</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 53min</t>
+          <t>01h 07min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121318</v>
+        <v>2121315</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 53min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121329</v>
+        <v>2121299</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>39min</t>
+          <t>02h 56min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121298</v>
+        <v>2121325</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>02h 58min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121327</v>
+        <v>2121311</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121287</v>
+        <v>2121307</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>01h 51min</t>
+          <t>01h 39min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121292</v>
+        <v>2121305</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>02h 28min</t>
+          <t>01h 44min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121312</v>
+        <v>2121291</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>02h 29min</t>
+          <t>02h 32min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121307</v>
+        <v>2121297</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>01h 35min</t>
+          <t>03h 05min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121291</v>
+        <v>2121300</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>02h 43min</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121303</v>
+        <v>2121276</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 27min</t>
+          <t>03h 47min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121277</v>
+        <v>2121294</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 55min</t>
+          <t>02h 32min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121294</v>
+        <v>2121303</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 28min</t>
+          <t>02h 31min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121283</v>
+        <v>2121310</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>03h 02min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121297</v>
+        <v>2121312</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>03h 02min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121300</v>
+        <v>2121302</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>01h 53min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121301</v>
+        <v>2121287</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>02h 40min</t>
+          <t>01h 55min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121308</v>
+        <v>2121301</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>02h 44min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121302</v>
+        <v>2121308</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>01h 49min</t>
+          <t>17min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121305</v>
+        <v>2121283</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>01h 40min</t>
+          <t>03h 06min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121310</v>
+        <v>2121277</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>02h 58min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121276</v>
+        <v>2121292</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>03h 43min</t>
+          <t>02h 32min</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2121328</v>
+        <v>2121332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3964,28 +3964,28 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 38 Min</t>
+          <t xml:space="preserve"> 00 Hs 08 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pendente de Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>38min</t>
+          <t>03min</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121332</v>
+        <v>2121330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4020,28 +4020,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 04 Min</t>
+          <t xml:space="preserve"> 00 Hs 42 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pendente de Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>03min</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121330</v>
+        <v>2121328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4076,28 +4076,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 38 Min</t>
+          <t xml:space="preserve"> 00 Hs 42 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pendente de Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>38min</t>
+          <t>03min</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4210,11 +4210,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121290</v>
+        <v>2121288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4224,28 +4224,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 18 Min</t>
+          <t xml:space="preserve"> 03 Hs 24 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>44min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4269,11 +4269,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121288</v>
+        <v>2121306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4283,28 +4283,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 20 Min</t>
+          <t xml:space="preserve"> 02 Hs 24 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40min</t>
+          <t>01h 40min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 48 Min</t>
+          <t xml:space="preserve"> 03 Hs 52 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01h 56min</t>
+          <t>01h 59min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4387,11 +4387,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121304</v>
+        <v>2121290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4401,28 +4401,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 28 Min</t>
+          <t xml:space="preserve"> 03 Hs 22 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>21min</t>
+          <t>02h 42min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4446,11 +4446,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121306</v>
+        <v>2121304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4460,28 +4460,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 20 Min</t>
+          <t xml:space="preserve"> 02 Hs 32 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01h 36min</t>
+          <t>25min</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -4501,7 +4501,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4539,7 +4539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -4556,10 +4556,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Responsável: JEAN LUCAS FERREIRA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -4577,7 +4579,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4596,7 +4598,7 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4609,6 +4611,82 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4690,7 +4768,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4897,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34m 2s</t>
+          <t>0m 0s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121289</v>
+        <v>2121298</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>03h 09min</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121318</v>
+        <v>2121311</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>02h 00min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121331</v>
+        <v>2121313</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>46min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121298</v>
+        <v>2121299</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>03h 05min</t>
+          <t>03h 03min</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121299</v>
+        <v>2121296</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>02h 59min</t>
+          <t>03h 03min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121284</v>
+        <v>2121318</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121281</v>
+        <v>2121320</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121321</v>
+        <v>2121323</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>46min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121279</v>
+        <v>2121326</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121311</v>
+        <v>2121322</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>02h 01min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121313</v>
+        <v>2121316</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121296</v>
+        <v>2121278</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>02h 59min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121316</v>
+        <v>2121317</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121323</v>
+        <v>2121319</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1517,17 +1517,17 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121325</v>
+        <v>2121315</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121295</v>
+        <v>2121327</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>03h 15min</t>
+          <t>55min</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121322</v>
+        <v>2121333</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>01h 57min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121314</v>
+        <v>2121286</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>03h 52min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121278</v>
+        <v>2121314</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1817,17 +1817,17 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>01h 14min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121293</v>
+        <v>2121284</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>03h 20min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121286</v>
+        <v>2121279</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>03h 49min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121317</v>
+        <v>2121281</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121315</v>
+        <v>2121282</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121282</v>
+        <v>2121325</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121324</v>
+        <v>2121309</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121333</v>
+        <v>2121321</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>12min</t>
+          <t>50min</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121326</v>
+        <v>2121329</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 29min</t>
+          <t>50min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121319</v>
+        <v>2121331</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>02h 00min</t>
+          <t>50min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121320</v>
+        <v>2121324</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>02h 00min</t>
+          <t>01h 32min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121329</v>
+        <v>2121293</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>46min</t>
+          <t>03h 24min</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121327</v>
+        <v>2121295</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>03h 18min</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121309</v>
+        <v>2121289</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121285</v>
+        <v>2121276</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>02h 36min</t>
+          <t>03h 54min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121277</v>
+        <v>2121291</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>03h 02min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121303</v>
+        <v>2121301</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>02h 34min</t>
+          <t>02h 51min</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>01h 42min</t>
+          <t>01h 46min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121287</v>
+        <v>2121283</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>03h 13min</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121283</v>
+        <v>2121285</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>03h 10min</t>
+          <t>02h 39min</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121305</v>
+        <v>2121302</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -3072,17 +3072,17 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>02h 00min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121294</v>
+        <v>2121287</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 35min</t>
+          <t>02h 02min</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>03h 09min</t>
+          <t>03h 13min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121302</v>
+        <v>2121294</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>01h 57min</t>
+          <t>02h 39min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121308</v>
+        <v>2121310</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>20min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121310</v>
+        <v>2121305</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>01h 51min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121276</v>
+        <v>2121300</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>03h 50min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121292</v>
+        <v>2121308</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 36min</t>
+          <t>24min</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121291</v>
+        <v>2121277</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>03h 06min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121300</v>
+        <v>2121292</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>02h 39min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121301</v>
+        <v>2121303</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>02h 47min</t>
+          <t>02h 38min</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2121328</v>
+        <v>2121330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3964,18 +3964,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 46 Min</t>
+          <t xml:space="preserve"> 00 Hs 49 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121330</v>
+        <v>2121328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4020,18 +4020,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 46 Min</t>
+          <t xml:space="preserve"> 00 Hs 49 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 12 Min</t>
+          <t xml:space="preserve"> 00 Hs 15 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 26 Min</t>
+          <t xml:space="preserve"> 03 Hs 29 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>02h 50min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 36 Min</t>
+          <t xml:space="preserve"> 02 Hs 39 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29min</t>
+          <t>32min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4328,42 +4328,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121306</v>
+        <v>2121280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 28 Min</t>
+          <t xml:space="preserve"> 03 Hs 59 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01h 44min</t>
+          <t>02h 06min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4387,42 +4387,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121280</v>
+        <v>2121306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 56 Min</t>
+          <t xml:space="preserve"> 02 Hs 31 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 03min</t>
+          <t>01h 47min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 28 Min</t>
+          <t xml:space="preserve"> 03 Hs 31 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>48min</t>
+          <t>51min</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17m 1s</t>
+          <t>34m 2s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121298</v>
+        <v>2121329</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>03h 09min</t>
+          <t>54min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121311</v>
+        <v>2121295</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121313</v>
+        <v>2121311</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121299</v>
+        <v>2121293</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>03h 03min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121296</v>
+        <v>2121320</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>03h 03min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121318</v>
+        <v>2121284</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121320</v>
+        <v>2121326</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121323</v>
+        <v>2121279</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>03h 59min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121326</v>
+        <v>2121324</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121322</v>
+        <v>2121286</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>03h 56min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121316</v>
+        <v>2121315</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121278</v>
+        <v>2121331</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>03h 55min</t>
+          <t>54min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121317</v>
+        <v>2121316</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121319</v>
+        <v>2121323</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -1517,17 +1517,17 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121315</v>
+        <v>2121318</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121327</v>
+        <v>2121321</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>54min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121333</v>
+        <v>2121314</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>16min</t>
+          <t>01h 18min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121286</v>
+        <v>2121327</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>03h 52min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121314</v>
+        <v>2121281</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>01h 14min</t>
+          <t>03h 59min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121284</v>
+        <v>2121282</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>03h 33min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121279</v>
+        <v>2121296</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>03h 55min</t>
+          <t>03h 07min</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121281</v>
+        <v>2121317</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>03h 55min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121282</v>
+        <v>2121322</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>03h 33min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121325</v>
+        <v>2121299</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>03h 07min</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121321</v>
+        <v>2121313</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>50min</t>
+          <t>41min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121329</v>
+        <v>2121319</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>50min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121331</v>
+        <v>2121298</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>50min</t>
+          <t>03h 13min</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121324</v>
+        <v>2121278</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>03h 59min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121293</v>
+        <v>2121325</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>03h 24min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121295</v>
+        <v>2121289</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121289</v>
+        <v>2121333</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>03h 33min</t>
+          <t>20min</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121276</v>
+        <v>2121283</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2702,27 +2702,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>03h 54min</t>
+          <t>03h 17min</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2121291</v>
+        <v>2121294</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2762,27 +2762,27 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>02h 43min</t>
         </is>
       </c>
     </row>
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>2121301</v>
+        <v>2121291</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2822,27 +2822,27 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>02h 51min</t>
+          <t>02h 24min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121307</v>
+        <v>2121297</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>01h 46min</t>
+          <t>03h 16min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121283</v>
+        <v>2121310</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>03h 13min</t>
+          <t>02h 24min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121285</v>
+        <v>2121287</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>02h 06min</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121302</v>
+        <v>2121307</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 00min</t>
+          <t>01h 50min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121287</v>
+        <v>2121292</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 02min</t>
+          <t>02h 43min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121297</v>
+        <v>2121285</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>03h 13min</t>
+          <t>02h 43min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121294</v>
+        <v>2121276</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>03h 58min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121310</v>
+        <v>2121305</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>01h 55min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121305</v>
+        <v>2121300</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>01h 51min</t>
+          <t>02h 54min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121300</v>
+        <v>2121301</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>02h 55min</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>02h 24min</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>03h 06min</t>
+          <t>03h 09min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121292</v>
+        <v>2121303</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>02h 42min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121303</v>
+        <v>2121302</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>02h 38min</t>
+          <t>02h 04min</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2121330</v>
+        <v>2121332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3964,18 +3964,18 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 49 Min</t>
+          <t xml:space="preserve"> 00 Hs 19 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10min</t>
+          <t>14min</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 49 Min</t>
+          <t xml:space="preserve"> 00 Hs 53 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10min</t>
+          <t>14min</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121332</v>
+        <v>2121330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4076,18 +4076,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 15 Min</t>
+          <t xml:space="preserve"> 00 Hs 53 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10min</t>
+          <t>14min</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121290</v>
+        <v>2121304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4224,28 +4224,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 29 Min</t>
+          <t xml:space="preserve"> 02 Hs 43 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>36min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4269,11 +4269,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121304</v>
+        <v>2121290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4283,28 +4283,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 39 Min</t>
+          <t xml:space="preserve"> 03 Hs 33 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>32min</t>
+          <t>02h 53min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 59 Min</t>
+          <t xml:space="preserve"> 04 Hs 03 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02h 06min</t>
+          <t>02h 10min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 31 Min</t>
+          <t xml:space="preserve"> 02 Hs 35 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>01h 51min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 31 Min</t>
+          <t xml:space="preserve"> 03 Hs 35 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>51min</t>
+          <t>55min</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34m 2s</t>
+          <t>0m 7s</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121299</v>
+        <v>2121286</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>03h 10min</t>
+          <t>04h 03min</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121327</v>
+        <v>2121317</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 02min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121279</v>
+        <v>2121289</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121325</v>
+        <v>2121315</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121296</v>
+        <v>2121329</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>03h 10min</t>
+          <t>01h 01min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121286</v>
+        <v>2121332</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>04h 00min</t>
+          <t>02min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121330</v>
+        <v>2121311</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>00min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121295</v>
+        <v>2121326</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>03h 26min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121333</v>
+        <v>2121321</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>23min</t>
+          <t>01h 01min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121278</v>
+        <v>2121299</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>03h 14min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121311</v>
+        <v>2121284</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121319</v>
+        <v>2121281</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>02h 11min</t>
+          <t>04h 06min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121321</v>
+        <v>2121318</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121329</v>
+        <v>2121328</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>06min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121298</v>
+        <v>2121327</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>03h 16min</t>
+          <t>01h 06min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121282</v>
+        <v>2121324</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121323</v>
+        <v>2121320</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>01h 40min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121293</v>
+        <v>2121322</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>03h 31min</t>
+          <t>02h 12min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121289</v>
+        <v>2121330</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>04min</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121318</v>
+        <v>2121316</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 11min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121320</v>
+        <v>2121278</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>02h 11min</t>
+          <t>04h 06min</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121315</v>
+        <v>2121279</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>04h 06min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121324</v>
+        <v>2121325</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>01h 40min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121313</v>
+        <v>2121293</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>44min</t>
+          <t>03h 35min</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121314</v>
+        <v>2121319</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>01h 01min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121326</v>
+        <v>2121282</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121322</v>
+        <v>2121296</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>02h 08min</t>
+          <t>03h 14min</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121316</v>
+        <v>2121314</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>01h 25min</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121284</v>
+        <v>2121298</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>03h 20min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121281</v>
+        <v>2121323</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121317</v>
+        <v>2121295</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>02h 11min</t>
+          <t>03h 29min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121328</v>
+        <v>2121333</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -2742,30 +2742,74 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>01h 43min</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B37" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
-      <c r="J37" s="4" t="inlineStr"/>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr"/>
+        <v>2121313</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>WHITE MARTINS</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>RES: Emitir CTe 408</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Julio Henrique Labhardt Junior</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:40:48</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 03:24:37</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:40:48</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>48min</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr"/>
@@ -2781,7 +2825,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="inlineStr"/>
@@ -2794,70 +2838,26 @@
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Responsável: OXANA ANDRELI DA SILVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>2121285</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>SPAL/FEMSA</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 00:08:42</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:22:13</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 00:08:42</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>02h 47min</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121276</v>
+        <v>2121312</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>04h 01min</t>
+          <t>02h 31min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121297</v>
+        <v>2121302</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>03h 20min</t>
+          <t>02h 11min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121305</v>
+        <v>2121276</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>04h 05min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121294</v>
+        <v>2121310</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>02h 31min</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121301</v>
+        <v>2121307</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3132,17 +3132,17 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 58min</t>
+          <t>01h 57min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121307</v>
+        <v>2121294</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>01h 53min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121291</v>
+        <v>2121301</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 27min</t>
+          <t>03h 02min</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>31min</t>
+          <t>35min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121302</v>
+        <v>2121283</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 07min</t>
+          <t>03h 24min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121277</v>
+        <v>2121287</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>03h 13min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121303</v>
+        <v>2121277</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 45min</t>
+          <t>03h 17min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121310</v>
+        <v>2121291</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 27min</t>
+          <t>02h 31min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121312</v>
+        <v>2121297</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>02h 27min</t>
+          <t>03h 23min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121287</v>
+        <v>2121300</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121283</v>
+        <v>2121303</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>03h 20min</t>
+          <t>02h 49min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121292</v>
+        <v>2121305</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 47min</t>
+          <t>02h 02min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121300</v>
+        <v>2121292</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,25 +3877,69 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>02h 50min</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="4" t="inlineStr"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B59" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr"/>
+        <v>2121285</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>SPAL/FEMSA</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>cte_prd_saidas@kof.com.mx</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:08:42</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:22:13</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:08:42</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>02h 50min</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="4" t="inlineStr"/>
@@ -3932,7 +3976,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="4" t="inlineStr"/>
       <c r="B62" s="4" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
       <c r="D62" s="4" t="inlineStr"/>
@@ -3948,7 +3992,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="4" t="inlineStr"/>
       <c r="B63" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr"/>
@@ -3964,7 +4008,7 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="4" t="inlineStr"/>
       <c r="B64" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
       <c r="D64" s="4" t="inlineStr"/>
@@ -3976,6 +4020,22 @@
       <c r="J64" s="4" t="inlineStr"/>
       <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3988,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4050,118 +4110,6 @@
       <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Alterado há</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2121330</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SPAL/FEMSA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>27/03/2026 03:10:47</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>27/03/2026 03:10:47</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 57 Min</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>18min</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2121332</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SPAL/FEMSA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27/03/2026 03:44:42</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>27/03/2026 03:44:42</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 23 Min</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>18min</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4264,7 +4212,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -4309,7 +4257,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 39 Min</t>
+          <t xml:space="preserve"> 02 Hs 42 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4319,11 +4267,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01h 55min</t>
+          <t>01h 58min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4368,7 +4316,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 39 Min</t>
+          <t xml:space="preserve"> 03 Hs 42 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4378,11 +4326,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>01h 02min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -4392,42 +4340,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121280</v>
+        <v>2121290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 07 Min</t>
+          <t xml:space="preserve"> 03 Hs 40 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4437,11 +4385,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02h 14min</t>
+          <t>03h 01min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -4451,42 +4399,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121304</v>
+        <v>2121280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 47 Min</t>
+          <t xml:space="preserve"> 04 Hs 10 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4496,11 +4444,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40min</t>
+          <t>02h 18min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -4510,11 +4458,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121290</v>
+        <v>2121304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4524,28 +4472,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 37 Min</t>
+          <t xml:space="preserve"> 02 Hs 50 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4555,11 +4503,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>43min</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -4578,7 +4526,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -4597,7 +4545,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -4616,16 +4564,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Responsável: JEAN LUCAS FERREIRA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -4637,13 +4583,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4656,13 +4602,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4675,83 +4621,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="n">
-        <v>7</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4823,16 +4693,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19m 30s</t>
+          <t>19m 41s</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>offline</t>
         </is>
       </c>
     </row>
@@ -4945,23 +4815,23 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" t="n">
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33m 55s</t>
+          <t>0m 0s</t>
         </is>
       </c>
     </row>
@@ -5006,7 +4876,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -5042,10 +4912,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -5111,7 +4981,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121286</v>
+        <v>2121317</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>04h 03min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121317</v>
+        <v>2121314</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>01h 28min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121289</v>
+        <v>2121324</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>03h 44min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121315</v>
+        <v>2121293</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>03h 38min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121329</v>
+        <v>2121313</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>01h 01min</t>
+          <t>52min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121332</v>
+        <v>2121286</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>04h 07min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121311</v>
+        <v>2121321</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>01h 05min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121326</v>
+        <v>2121311</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121321</v>
+        <v>2121319</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>01h 01min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121299</v>
+        <v>2121330</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>03h 14min</t>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>03h 44min</t>
+          <t>03h 47min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121281</v>
+        <v>2121278</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121318</v>
+        <v>2121281</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121328</v>
+        <v>2121282</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>06min</t>
+          <t>03h 47min</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121327</v>
+        <v>2121325</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>01h 06min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121324</v>
+        <v>2121295</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>03h 33min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121320</v>
+        <v>2121318</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121330</v>
+        <v>2121315</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>04min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121316</v>
+        <v>2121299</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>03h 17min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121278</v>
+        <v>2121316</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121279</v>
+        <v>2121323</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121325</v>
+        <v>2121296</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>03h 17min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121293</v>
+        <v>2121326</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>03h 35min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121319</v>
+        <v>2121320</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121331</v>
+        <v>2121298</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>01h 01min</t>
+          <t>03h 24min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121282</v>
+        <v>2121279</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>03h 44min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121296</v>
+        <v>2121327</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>03h 14min</t>
+          <t>01h 09min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121314</v>
+        <v>2121289</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 25min</t>
+          <t>03h 47min</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121298</v>
+        <v>2121328</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>03h 20min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121323</v>
+        <v>2121329</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>01h 05min</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121295</v>
+        <v>2121331</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>03h 29min</t>
+          <t>01h 05min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121333</v>
+        <v>2121332</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>27min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2121309</v>
+        <v>2121333</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>30min</t>
         </is>
       </c>
     </row>
@@ -2753,11 +2753,11 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121313</v>
+        <v>2121309</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2767,27 +2767,27 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>48min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121312</v>
+        <v>2121276</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>02h 31min</t>
+          <t>04h 08min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121302</v>
+        <v>2121294</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>02h 11min</t>
+          <t>02h 54min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121276</v>
+        <v>2121277</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>04h 05min</t>
+          <t>03h 20min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121310</v>
+        <v>2121297</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>02h 31min</t>
+          <t>03h 27min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121307</v>
+        <v>2121303</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>01h 57min</t>
+          <t>02h 53min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121294</v>
+        <v>2121310</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>02h 34min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121301</v>
+        <v>2121283</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>03h 02min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121308</v>
+        <v>2121300</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>03h 05min</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121283</v>
+        <v>2121292</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -3372,17 +3372,17 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>03h 24min</t>
+          <t>02h 54min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121287</v>
+        <v>2121307</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>02h 13min</t>
+          <t>02h 01min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121277</v>
+        <v>2121287</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>03h 17min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 31min</t>
+          <t>02h 35min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121297</v>
+        <v>2121301</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>03h 23min</t>
+          <t>03h 05min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121300</v>
+        <v>2121302</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>03h 01min</t>
+          <t>02h 15min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121303</v>
+        <v>2121285</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>02h 49min</t>
+          <t>02h 54min</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 02min</t>
+          <t>02h 06min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121292</v>
+        <v>2121308</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -3888,11 +3888,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2121285</v>
+        <v>2121312</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3902,27 +3902,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>02h 50min</t>
+          <t>02h 34min</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4110,6 +4110,62 @@
       <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Alterado há</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2121334</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WHITE MARTINS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RES: Emitir CTE frota 524</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Julio Henrique Labhardt Junior</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>27/03/2026 04:14:42</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>27/03/2026 04:14:43</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 00 Min</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00min</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4268,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -4257,7 +4313,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 42 Min</t>
+          <t xml:space="preserve"> 02 Hs 46 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4267,11 +4323,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>02h 02min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4281,7 +4337,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121288</v>
+        <v>2121280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4290,12 +4346,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4305,18 +4361,18 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 42 Min</t>
+          <t xml:space="preserve"> 04 Hs 14 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4326,11 +4382,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01h 02min</t>
+          <t>02h 21min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -4340,11 +4396,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121290</v>
+        <v>2121288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4354,28 +4410,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 40 Min</t>
+          <t xml:space="preserve"> 03 Hs 46 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4385,11 +4441,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>03h 01min</t>
+          <t>01h 06min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4399,42 +4455,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121280</v>
+        <v>2121304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 10 Min</t>
+          <t xml:space="preserve"> 02 Hs 54 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4444,11 +4500,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 18min</t>
+          <t>47min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -4458,11 +4514,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121304</v>
+        <v>2121290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4472,28 +4528,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 50 Min</t>
+          <t xml:space="preserve"> 03 Hs 44 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4503,17 +4559,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>43min</t>
+          <t>03h 04min</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4526,13 +4582,13 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4545,13 +4601,13 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -4564,13 +4620,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4583,13 +4639,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4602,13 +4658,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4621,7 +4677,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4821,13 +4877,13 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121330</v>
+        <v>2121321</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>11min</t>
+          <t>01h 12min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121315</v>
+        <v>2121314</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>02h 23min</t>
+          <t>01h 36min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121298</v>
+        <v>2121309</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>03h 27min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121284</v>
+        <v>2121322</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>02h 23min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121289</v>
+        <v>2121316</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121318</v>
+        <v>2121279</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>04h 17min</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121326</v>
+        <v>2121325</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121286</v>
+        <v>2121295</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>04h 10min</t>
+          <t>03h 40min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121328</v>
+        <v>2121289</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121331</v>
+        <v>2121313</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>01h 08min</t>
+          <t>59min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121321</v>
+        <v>2121326</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 08min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121329</v>
+        <v>2121318</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>01h 08min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121324</v>
+        <v>2121315</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121319</v>
+        <v>2121298</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>03h 31min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121327</v>
+        <v>2121284</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>01h 13min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121278</v>
+        <v>2121311</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121281</v>
+        <v>2121296</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>03h 25min</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121320</v>
+        <v>2121329</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>01h 12min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121279</v>
+        <v>2121328</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>17min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121332</v>
+        <v>2121327</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>01h 17min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121333</v>
+        <v>2121278</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>34min</t>
+          <t>04h 17min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121309</v>
+        <v>2121323</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121311</v>
+        <v>2121324</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>01h 54min</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121322</v>
+        <v>2121293</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>02h 19min</t>
+          <t>03h 46min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121323</v>
+        <v>2121332</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 51min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121325</v>
+        <v>2121320</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -2357,17 +2357,17 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 50min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121293</v>
+        <v>2121331</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>03h 42min</t>
+          <t>01h 12min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121295</v>
+        <v>2121281</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>03h 37min</t>
+          <t>04h 17min</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121296</v>
+        <v>2121286</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>03h 21min</t>
+          <t>04h 14min</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121314</v>
+        <v>2121319</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>01h 32min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121299</v>
+        <v>2121330</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>03h 21min</t>
+          <t>15min</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2121316</v>
+        <v>2121299</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>03h 25min</t>
         </is>
       </c>
     </row>
@@ -2753,11 +2753,11 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121313</v>
+        <v>2121333</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2767,27 +2767,27 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>55min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -2868,11 +2868,11 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121307</v>
+        <v>2121285</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2882,27 +2882,27 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>02h 04min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>02h 24min</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121277</v>
+        <v>2121297</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>03h 24min</t>
+          <t>03h 34min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121283</v>
+        <v>2121303</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>03h 31min</t>
+          <t>03h 00min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121305</v>
+        <v>2121308</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>46min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121302</v>
+        <v>2121310</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 18min</t>
+          <t>02h 42min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121294</v>
+        <v>2121312</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>02h 42min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121300</v>
+        <v>2121294</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>03h 08min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121310</v>
+        <v>2121292</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 38min</t>
+          <t>03h 01min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121276</v>
+        <v>2121300</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>04h 12min</t>
+          <t>03h 12min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121292</v>
+        <v>2121305</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 57min</t>
+          <t>02h 13min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121291</v>
+        <v>2121302</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 38min</t>
+          <t>02h 22min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121297</v>
+        <v>2121307</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>03h 31min</t>
+          <t>02h 08min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121301</v>
+        <v>2121276</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>03h 09min</t>
+          <t>04h 16min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121303</v>
+        <v>2121277</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>02h 56min</t>
+          <t>03h 27min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121312</v>
+        <v>2121291</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 38min</t>
+          <t>02h 42min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121285</v>
+        <v>2121301</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>02h 58min</t>
+          <t>03h 13min</t>
         </is>
       </c>
     </row>
@@ -3888,11 +3888,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2121308</v>
+        <v>2121283</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3902,27 +3902,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>42min</t>
+          <t>03h 35min</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 03 Min</t>
+          <t xml:space="preserve"> 00 Hs 07 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>03min</t>
+          <t>07min</t>
         </is>
       </c>
     </row>
@@ -4278,42 +4278,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121280</v>
+        <v>2121290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 17 Min</t>
+          <t xml:space="preserve"> 03 Hs 51 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02h 25min</t>
+          <t>03h 12min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 49 Min</t>
+          <t xml:space="preserve"> 03 Hs 53 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01h 09min</t>
+          <t>01h 13min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4396,42 +4396,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121304</v>
+        <v>2121280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 57 Min</t>
+          <t xml:space="preserve"> 04 Hs 21 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50min</t>
+          <t>02h 29min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4455,11 +4455,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121290</v>
+        <v>2121306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4469,28 +4469,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 47 Min</t>
+          <t xml:space="preserve"> 02 Hs 53 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>03h 08min</t>
+          <t>02h 09min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4514,11 +4514,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121306</v>
+        <v>2121304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4528,28 +4528,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 49 Min</t>
+          <t xml:space="preserve"> 03 Hs 01 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>54min</t>
         </is>
       </c>
       <c r="M7" t="n">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121321</v>
+        <v>2121328</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>01h 12min</t>
+          <t>21min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121314</v>
+        <v>2121315</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 36min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121309</v>
+        <v>2121321</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>01h 16min</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>02h 23min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121316</v>
+        <v>2121329</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>01h 16min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121279</v>
+        <v>2121330</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>18min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121282</v>
+        <v>2121299</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 55min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121325</v>
+        <v>2121316</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121295</v>
+        <v>2121279</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>03h 40min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121289</v>
+        <v>2121324</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>03h 55min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121313</v>
+        <v>2121289</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>59min</t>
+          <t>03h 58min</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121326</v>
+        <v>2121333</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>41min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121318</v>
+        <v>2121331</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>01h 16min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121315</v>
+        <v>2121282</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>03h 58min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121298</v>
+        <v>2121325</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>03h 31min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121284</v>
+        <v>2121309</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>03h 55min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121311</v>
+        <v>2121286</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>04h 18min</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121296</v>
+        <v>2121320</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>03h 25min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121317</v>
+        <v>2121314</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>01h 39min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121329</v>
+        <v>2121284</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>01h 12min</t>
+          <t>03h 58min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121328</v>
+        <v>2121281</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>17min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121327</v>
+        <v>2121323</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>01h 17min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121278</v>
+        <v>2121317</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121323</v>
+        <v>2121319</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2117,17 +2117,17 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121324</v>
+        <v>2121298</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>03h 35min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121293</v>
+        <v>2121278</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>03h 46min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121332</v>
+        <v>2121326</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121320</v>
+        <v>2121318</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121331</v>
+        <v>2121327</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>01h 12min</t>
+          <t>01h 20min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121281</v>
+        <v>2121295</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>03h 44min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121286</v>
+        <v>2121313</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04h 14min</t>
+          <t>01h 02min</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121319</v>
+        <v>2121296</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>03h 28min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121330</v>
+        <v>2121311</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>15min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2121299</v>
+        <v>2121293</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>03h 25min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -2753,11 +2753,11 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121333</v>
+        <v>2121332</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2767,27 +2767,27 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>38min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>2121285</v>
+        <v>2121292</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>03h 01min</t>
+          <t>03h 05min</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2928,11 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2121287</v>
+        <v>2121291</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>02h 24min</t>
+          <t>02h 46min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121297</v>
+        <v>2121285</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>03h 34min</t>
+          <t>03h 05min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121303</v>
+        <v>2121287</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>02h 27min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121308</v>
+        <v>2121305</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>46min</t>
+          <t>02h 17min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121310</v>
+        <v>2121283</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 42min</t>
+          <t>03h 39min</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121312</v>
+        <v>2121276</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3252,17 +3252,17 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>02h 42min</t>
+          <t>04h 19min</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>03h 01min</t>
+          <t>03h 05min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121292</v>
+        <v>2121300</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>03h 01min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121300</v>
+        <v>2121308</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>03h 12min</t>
+          <t>49min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121305</v>
+        <v>2121310</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 13min</t>
+          <t>02h 45min</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121302</v>
+        <v>2121301</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 22min</t>
+          <t>03h 16min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121307</v>
+        <v>2121303</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>02h 08min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121276</v>
+        <v>2121302</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>04h 16min</t>
+          <t>02h 26min</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121277</v>
+        <v>2121297</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3732,17 +3732,17 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>03h 27min</t>
+          <t>03h 38min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121291</v>
+        <v>2121277</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 42min</t>
+          <t>03h 31min</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121301</v>
+        <v>2121307</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3852,17 +3852,17 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>03h 13min</t>
+          <t>02h 12min</t>
         </is>
       </c>
     </row>
@@ -3888,11 +3888,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2121283</v>
+        <v>2121312</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3902,27 +3902,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>03h 35min</t>
+          <t>02h 45min</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 07 Min</t>
+          <t xml:space="preserve"> 00 Hs 11 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4165,7 +4165,119 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07min</t>
+          <t>11min</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2121336</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>XML Femsa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27/03/2026 04:22:42</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>27/03/2026 04:22:42</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 03 Min</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>03min</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2121335</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HEINEKEN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motor de Emissão - nstech</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>27/03/2026 04:22:40</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>27/03/2026 04:22:40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 00 Hs 03 Min</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Pendente de Atendimento</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>03min</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4380,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -4278,42 +4390,42 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121290</v>
+        <v>2121280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 51 Min</t>
+          <t xml:space="preserve"> 04 Hs 25 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4323,11 +4435,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>03h 12min</t>
+          <t>02h 32min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -4337,11 +4449,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121288</v>
+        <v>2121306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4351,28 +4463,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 53 Min</t>
+          <t xml:space="preserve"> 02 Hs 57 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4382,11 +4494,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01h 13min</t>
+          <t>02h 13min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -4396,42 +4508,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121280</v>
+        <v>2121304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 21 Min</t>
+          <t xml:space="preserve"> 03 Hs 05 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4441,11 +4553,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02h 29min</t>
+          <t>58min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -4455,11 +4567,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121306</v>
+        <v>2121288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4469,28 +4581,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 02 Hs 53 Min</t>
+          <t xml:space="preserve"> 03 Hs 57 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4500,11 +4612,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 09min</t>
+          <t>01h 17min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -4514,11 +4626,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121304</v>
+        <v>2121290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4528,28 +4640,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 01 Min</t>
+          <t xml:space="preserve"> 03 Hs 55 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4559,17 +4671,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>54min</t>
+          <t>03h 15min</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4582,13 +4694,13 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4601,13 +4713,13 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -4620,13 +4732,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4639,13 +4751,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4658,13 +4770,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4677,7 +4789,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4877,17 +4989,17 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0m 0s</t>
+          <t>8m 0s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121319</v>
+        <v>2121329</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>01h 23min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121314</v>
+        <v>2121299</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>01h 43min</t>
+          <t>03h 36min</t>
         </is>
       </c>
     </row>
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121293</v>
+        <v>2121319</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>03h 53min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121282</v>
+        <v>2121327</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>01h 28min</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121309</v>
+        <v>2121324</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121329</v>
+        <v>2121332</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>01h 19min</t>
+          <t>24min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121299</v>
+        <v>2121316</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>03h 32min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121327</v>
+        <v>2121284</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>01h 24min</t>
+          <t>04h 06min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121278</v>
+        <v>2121282</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>04h 06min</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121279</v>
+        <v>2121336</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 04:32:50</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>02min</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121311</v>
+        <v>2121309</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121317</v>
+        <v>2121322</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>02h 34min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121320</v>
+        <v>2121314</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>01h 47min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121328</v>
+        <v>2121278</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>04h 28min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121330</v>
+        <v>2121293</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>22min</t>
+          <t>03h 57min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121295</v>
+        <v>2121311</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>03h 47min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121286</v>
+        <v>2121317</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>04h 21min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121318</v>
+        <v>2121330</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>26min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121322</v>
+        <v>2121334</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTE frota 524</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 04:14:42</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 04:33:28</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 04:14:43</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>02h 30min</t>
+          <t>01min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121315</v>
+        <v>2121323</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 34min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121324</v>
+        <v>2121295</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>03h 51min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121325</v>
+        <v>2121318</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121313</v>
+        <v>2121298</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>01h 06min</t>
+          <t>03h 42min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121326</v>
+        <v>2121333</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>49min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121321</v>
+        <v>2121313</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 19min</t>
+          <t>01h 10min</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121331</v>
+        <v>2121286</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>01h 19min</t>
+          <t>04h 25min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121298</v>
+        <v>2121321</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>03h 38min</t>
+          <t>01h 23min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121316</v>
+        <v>2121328</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>28min</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121289</v>
+        <v>2121315</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2417,17 +2417,17 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121296</v>
+        <v>2121331</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>03h 32min</t>
+          <t>01h 23min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121284</v>
+        <v>2121281</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>04h 28min</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121281</v>
+        <v>2121296</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>04h 24min</t>
+          <t>03h 36min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121323</v>
+        <v>2121326</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>02h 01min</t>
+          <t>02h 05min</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2121332</v>
+        <v>2121320</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>20min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121333</v>
+        <v>2121279</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,46 +2802,134 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>45min</t>
+          <t>04h 28min</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="4" t="inlineStr"/>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B38" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr"/>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr"/>
+        <v>2121325</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>XML Femsa</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 02:08:49</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 02:29:22</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 02:08:49</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>02h 05min</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B39" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
+        <v>2121289</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>SPAL JUNDIAÍ</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>XML Femsa</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:28:46</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:28:56</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:28:46</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>04h 06min</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
@@ -2854,130 +2942,42 @@
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Responsável: OXANA ANDRELI DA SILVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>2121294</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>SPAL/FEMSA</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 00:42:40</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:22:25</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 00:42:40</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>03h 08min</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>2121301</v>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>FILIAL MARILIA</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Ricardo Cardoso da Costa</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:06:42</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:10:59</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>27/03/2026 01:06:42</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>03h 20min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121303</v>
+        <v>2121305</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>03h 07min</t>
+          <t>02h 24min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121285</v>
+        <v>2121303</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>03h 09min</t>
+          <t>03h 11min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121312</v>
+        <v>2121307</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 49min</t>
+          <t>02h 19min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121291</v>
+        <v>2121283</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>02h 49min</t>
+          <t>03h 46min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121308</v>
+        <v>2121294</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>53min</t>
+          <t>03h 12min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121302</v>
+        <v>2121292</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>02h 29min</t>
+          <t>03h 12min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121283</v>
+        <v>2121302</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>03h 42min</t>
+          <t>02h 33min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121292</v>
+        <v>2121312</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>03h 08min</t>
+          <t>02h 53min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121276</v>
+        <v>2121277</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>04h 23min</t>
+          <t>03h 38min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121287</v>
+        <v>2121297</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>02h 31min</t>
+          <t>03h 45min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121310</v>
+        <v>2121308</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>02h 49min</t>
+          <t>57min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121307</v>
+        <v>2121310</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 15min</t>
+          <t>02h 53min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121277</v>
+        <v>2121285</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>03h 35min</t>
+          <t>03h 12min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121305</v>
+        <v>2121287</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>02h 35min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121297</v>
+        <v>2121276</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>03h 42min</t>
+          <t>04h 27min</t>
         </is>
       </c>
     </row>
@@ -3888,90 +3888,178 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>2121291</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>RECKITT</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>RibeiroFiuza, Fernando</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:30:42</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:41:29</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 00:30:42</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>02h 53min</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
         <v>2121300</v>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>CCR</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>27/03/2026 01:04:42</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>27/03/2026 01:11:39</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>27/03/2026 01:04:42</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>03h 19min</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="4" t="inlineStr"/>
-      <c r="B60" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>03h 23min</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="4" t="inlineStr"/>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B61" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C61" s="4" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr"/>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr"/>
+        <v>2121301</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>FILIAL MARILIA</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Ricardo Cardoso da Costa</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:06:42</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:10:59</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>27/03/2026 01:06:42</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>03h 24min</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="4" t="inlineStr"/>
@@ -3992,7 +4080,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="4" t="inlineStr"/>
       <c r="B63" s="4" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr"/>
@@ -4008,7 +4096,7 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="4" t="inlineStr"/>
       <c r="B64" s="4" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
       <c r="D64" s="4" t="inlineStr"/>
@@ -4024,7 +4112,7 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="4" t="inlineStr"/>
       <c r="B65" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
       <c r="D65" s="4" t="inlineStr"/>
@@ -4036,6 +4124,38 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="4" t="inlineStr"/>
+      <c r="B66" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="4" t="inlineStr"/>
+      <c r="B67" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4048,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4155,7 +4275,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 14 Min</t>
+          <t xml:space="preserve"> 00 Hs 18 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4165,7 +4285,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14min</t>
+          <t>18min</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4331,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 06 Min</t>
+          <t xml:space="preserve"> 00 Hs 10 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4221,63 +4341,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>06min</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2121336</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SPAL JUNDIAÍ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>XML Femsa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>27/03/2026 04:22:42</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27/03/2026 04:22:42</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 06 Min</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Pendente de Atendimento</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>06min</t>
+          <t>10min</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4444,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -4390,7 +4454,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121280</v>
+        <v>2121288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4399,12 +4463,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4414,18 +4478,18 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 28 Min</t>
+          <t xml:space="preserve"> 04 Hs 04 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4435,11 +4499,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02h 36min</t>
+          <t>01h 24min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -4449,11 +4513,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121290</v>
+        <v>2121304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4463,28 +4527,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emitir CTe 408</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:40</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 58 Min</t>
+          <t xml:space="preserve"> 03 Hs 12 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4494,11 +4558,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>03h 19min</t>
+          <t>01h 05min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -4508,11 +4572,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2121306</v>
+        <v>2121290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4522,28 +4586,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>Emitir CTe 408</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:30:40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 00 Min</t>
+          <t xml:space="preserve"> 04 Hs 02 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4553,11 +4617,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>03h 22min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -4567,11 +4631,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121304</v>
+        <v>2121306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4581,28 +4645,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 08 Min</t>
+          <t xml:space="preserve"> 03 Hs 04 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4612,11 +4676,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01h 01min</t>
+          <t>02h 20min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -4626,7 +4690,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121288</v>
+        <v>2121280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -4635,12 +4699,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4650,18 +4714,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 00 Min</t>
+          <t xml:space="preserve"> 04 Hs 32 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4671,17 +4735,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01h 20min</t>
+          <t>02h 39min</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4694,13 +4758,13 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4713,13 +4777,13 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -4732,13 +4796,13 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4751,13 +4815,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4770,13 +4834,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4789,7 +4853,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4861,11 +4925,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19m 41s</t>
+          <t>19m 24s</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4983,23 +5047,23 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" t="n">
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4m 0s</t>
+          <t>7m 58s</t>
         </is>
       </c>
     </row>
@@ -5041,10 +5105,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -5158,7 +5222,9 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121329</v>
+        <v>2121286</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>01h 23min</t>
+          <t>04h 29min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121299</v>
+        <v>2121311</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>03h 36min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121319</v>
+        <v>2121318</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121327</v>
+        <v>2121321</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>01h 28min</t>
+          <t>01h 27min</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121324</v>
+        <v>2121314</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>01h 50min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121332</v>
+        <v>2121327</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>24min</t>
+          <t>01h 31min</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121316</v>
+        <v>2121284</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121284</v>
+        <v>2121278</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>04h 31min</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121282</v>
+        <v>2121279</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>04h 31min</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121336</v>
+        <v>2121317</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:22:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:32:50</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:22:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>02min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121309</v>
+        <v>2121281</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>04h 31min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121322</v>
+        <v>2121323</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>02h 34min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121314</v>
+        <v>2121331</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>01h 47min</t>
+          <t>01h 26min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121278</v>
+        <v>2121299</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>04h 28min</t>
+          <t>03h 39min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121293</v>
+        <v>2121334</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTE frota 524</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 04:14:42</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 04:33:28</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 04:14:43</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>03h 57min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121311</v>
+        <v>2121325</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121317</v>
+        <v>2121295</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>03h 55min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121330</v>
+        <v>2121333</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>26min</t>
+          <t>52min</t>
         </is>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121334</v>
+        <v>2121336</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTE frota 524</t>
+          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:14:42</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:33:28</t>
+          <t>27/03/2026 04:32:50</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:14:43</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>01min</t>
+          <t>05min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121323</v>
+        <v>2121322</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121295</v>
+        <v>2121315</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>03h 51min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121318</v>
+        <v>2121298</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>03h 46min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121298</v>
+        <v>2121316</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>03h 42min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121333</v>
+        <v>2121282</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>49min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121313</v>
+        <v>2121324</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>01h 10min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121286</v>
+        <v>2121289</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>04h 25min</t>
+          <t>04h 09min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121321</v>
+        <v>2121309</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 23min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121328</v>
+        <v>2121326</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>28min</t>
+          <t>02h 09min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121315</v>
+        <v>2121328</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>32min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121331</v>
+        <v>2121329</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>01h 23min</t>
+          <t>01h 27min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121281</v>
+        <v>2121332</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04h 28min</t>
+          <t>27min</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>03h 36min</t>
+          <t>03h 39min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121326</v>
+        <v>2121319</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>02h 37min</t>
+          <t>02h 41min</t>
         </is>
       </c>
     </row>
@@ -2753,11 +2753,11 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121279</v>
+        <v>2121330</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2767,27 +2767,27 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>04h 28min</t>
+          <t>29min</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2121325</v>
+        <v>2121293</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2837,17 +2837,17 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>02h 05min</t>
+          <t>04h 00min</t>
         </is>
       </c>
     </row>
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121289</v>
+        <v>2121313</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2887,27 +2887,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>04h 06min</t>
+          <t>01h 13min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121305</v>
+        <v>2121291</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 24min</t>
+          <t>02h 57min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121303</v>
+        <v>2121301</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>03h 11min</t>
+          <t>03h 27min</t>
         </is>
       </c>
     </row>
@@ -3108,11 +3108,11 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121307</v>
+        <v>2121277</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>02h 19min</t>
+          <t>03h 42min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121283</v>
+        <v>2121307</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>03h 46min</t>
+          <t>02h 23min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121294</v>
+        <v>2121276</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>03h 12min</t>
+          <t>04h 30min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121292</v>
+        <v>2121297</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>03h 12min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121302</v>
+        <v>2121303</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 33min</t>
+          <t>03h 15min</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121312</v>
+        <v>2121310</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>02h 53min</t>
+          <t>02h 56min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121277</v>
+        <v>2121285</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>03h 38min</t>
+          <t>03h 16min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121297</v>
+        <v>2121287</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>03h 45min</t>
+          <t>02h 38min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121308</v>
+        <v>2121292</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>57min</t>
+          <t>03h 16min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121310</v>
+        <v>2121300</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>02h 53min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121285</v>
+        <v>2121312</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>03h 12min</t>
+          <t>02h 56min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121287</v>
+        <v>2121302</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 35min</t>
+          <t>02h 37min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121276</v>
+        <v>2121305</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>04h 27min</t>
+          <t>02h 28min</t>
         </is>
       </c>
     </row>
@@ -3888,11 +3888,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2121291</v>
+        <v>2121294</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3902,27 +3902,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>02h 53min</t>
+          <t>03h 16min</t>
         </is>
       </c>
     </row>
@@ -3948,11 +3948,11 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2121300</v>
+        <v>2121283</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3962,27 +3962,27 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>03h 23min</t>
+          <t>03h 50min</t>
         </is>
       </c>
     </row>
@@ -4008,11 +4008,11 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2121301</v>
+        <v>2121308</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4022,27 +4022,27 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>03h 24min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2121334</v>
+        <v>2121335</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4254,94 +4254,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RES: Emitir CTE frota 524</t>
+          <t>CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026 04:14:42</t>
+          <t>27/03/2026 04:22:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27/03/2026 04:14:43</t>
+          <t>27/03/2026 04:22:40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 18 Min</t>
+          <t xml:space="preserve"> 00 Hs 14 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pendente de Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18min</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2121335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HEINEKEN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Motor de Emissão - nstech</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>27/03/2026 04:22:40</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>27/03/2026 04:22:40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 00 Hs 10 Min</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Pendente de Atendimento</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>10min</t>
+          <t>02min</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4444,7 +4388,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -4454,11 +4398,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121288</v>
+        <v>2121306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4468,28 +4412,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 04 Min</t>
+          <t xml:space="preserve"> 03 Hs 08 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4499,11 +4443,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01h 24min</t>
+          <t>02h 24min</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4513,42 +4457,42 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121304</v>
+        <v>2121280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 12 Min</t>
+          <t xml:space="preserve"> 04 Hs 36 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4558,11 +4502,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01h 05min</t>
+          <t>02h 43min</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -4607,7 +4551,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 02 Min</t>
+          <t xml:space="preserve"> 04 Hs 06 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4617,11 +4561,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>03h 26min</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4631,11 +4575,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121306</v>
+        <v>2121288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4645,28 +4589,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 04 Min</t>
+          <t xml:space="preserve"> 04 Hs 08 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4676,11 +4620,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 20min</t>
+          <t>01h 28min</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -4690,42 +4634,42 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121280</v>
+        <v>2121304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 32 Min</t>
+          <t xml:space="preserve"> 03 Hs 16 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4735,17 +4679,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02h 39min</t>
+          <t>01h 09min</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -4758,13 +4702,13 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4777,13 +4721,13 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -4796,14 +4740,16 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>7</v>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Responsável: OXANA ANDRELI DA SILVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -4815,13 +4761,13 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -4834,13 +4780,13 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4853,7 +4799,83 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4954,7 +4976,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>offline</t>
+          <t>online</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5075,17 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7m 58s</t>
+          <t>0m 0s</t>
         </is>
       </c>
     </row>

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121298</v>
+        <v>2121327</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>03h 49min</t>
+          <t>01h 39min</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121324</v>
+        <v>2121278</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>04h 39min</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121296</v>
+        <v>2121279</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -847,27 +847,27 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>03h 43min</t>
+          <t>04h 39min</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2121329</v>
+        <v>2121334</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTE frota 524</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 04:14:42</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 04:33:28</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 04:14:43</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>01h 30min</t>
+          <t>12min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121331</v>
+        <v>2121323</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>01h 30min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121334</v>
+        <v>2121289</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTE frota 524</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:14:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:33:28</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:14:43</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>08min</t>
+          <t>04h 17min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121279</v>
+        <v>2121336</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 04:32:50</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>04h 35min</t>
+          <t>13min</t>
         </is>
       </c>
     </row>
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121295</v>
+        <v>2121311</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>03h 58min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121336</v>
+        <v>2121326</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:22:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:32:50</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:22:42</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>09min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121320</v>
+        <v>2121319</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121309</v>
+        <v>2121328</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>39min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121318</v>
+        <v>2121329</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>01h 34min</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1433,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121322</v>
+        <v>2121316</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 41min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121299</v>
+        <v>2121324</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>03h 43min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121284</v>
+        <v>2121281</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>04h 39min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121311</v>
+        <v>2121282</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>04h 17min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121321</v>
+        <v>2121295</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>01h 30min</t>
+          <t>04h 02min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121282</v>
+        <v>2121313</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>01h 21min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121286</v>
+        <v>2121296</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>04h 32min</t>
+          <t>03h 47min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121328</v>
+        <v>2121320</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121330</v>
+        <v>2121322</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>33min</t>
+          <t>02h 45min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121315</v>
+        <v>2121330</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>37min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121323</v>
+        <v>2121284</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>04h 17min</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121289</v>
+        <v>2121333</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>04h 13min</t>
+          <t>01h 00min</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121326</v>
+        <v>2121317</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121317</v>
+        <v>2121318</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121319</v>
+        <v>2121321</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>01h 34min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121314</v>
+        <v>2121331</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 54min</t>
+          <t>01h 34min</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121316</v>
+        <v>2121325</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2407,27 +2407,27 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121327</v>
+        <v>2121293</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>01h 35min</t>
+          <t>04h 08min</t>
         </is>
       </c>
     </row>
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121278</v>
+        <v>2121286</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2527,27 +2527,27 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04h 35min</t>
+          <t>04h 36min</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121281</v>
+        <v>2121314</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>04h 35min</t>
+          <t>01h 58min</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121325</v>
+        <v>2121315</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2657,17 +2657,17 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>02h 12min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2121293</v>
+        <v>2121298</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>04h 04min</t>
+          <t>03h 53min</t>
         </is>
       </c>
     </row>
@@ -2753,11 +2753,11 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121332</v>
+        <v>2121299</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2767,27 +2767,27 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>31min</t>
+          <t>03h 47min</t>
         </is>
       </c>
     </row>
@@ -2813,11 +2813,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2121333</v>
+        <v>2121332</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2827,27 +2827,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>56min</t>
+          <t>35min</t>
         </is>
       </c>
     </row>
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121313</v>
+        <v>2121309</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2887,27 +2887,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>01h 17min</t>
+          <t>02h 16min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121307</v>
+        <v>2121308</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>MANIFESTAR NF DJC1E58</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 03:37:42</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:34:40</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>02h 26min</t>
+          <t>01h 08min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121276</v>
+        <v>2121285</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>04h 34min</t>
+          <t>03h 23min</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121297</v>
+        <v>2121300</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>03h 53min</t>
+          <t>03h 34min</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121300</v>
+        <v>2121277</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>03h 30min</t>
+          <t>03h 49min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121283</v>
+        <v>2121291</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>03h 53min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121310</v>
+        <v>2121297</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:00</t>
+          <t>27/03/2026 00:49:11</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:44</t>
+          <t>27/03/2026 00:48:40</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>03h 56min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121312</v>
+        <v>2121307</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>02h 30min</t>
         </is>
       </c>
     </row>
@@ -3408,11 +3408,11 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121305</v>
+        <v>2121276</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>02h 31min</t>
+          <t>04h 38min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121287</v>
+        <v>2121312</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>02h 42min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121294</v>
+        <v>2121301</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>03h 19min</t>
+          <t>03h 35min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121292</v>
+        <v>2121303</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:19</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:40</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>03h 19min</t>
+          <t>03h 22min</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121285</v>
+        <v>2121283</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>03h 20min</t>
+          <t>03h 57min</t>
         </is>
       </c>
     </row>
@@ -3708,11 +3708,11 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121277</v>
+        <v>2121305</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>03h 46min</t>
+          <t>02h 35min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121291</v>
+        <v>2121302</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>03h 00min</t>
+          <t>02h 44min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121303</v>
+        <v>2121287</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>03h 18min</t>
+          <t>02h 46min</t>
         </is>
       </c>
     </row>
@@ -3888,11 +3888,11 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2121302</v>
+        <v>2121294</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3902,27 +3902,27 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 01:22:25</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 00:42:40</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>02h 40min</t>
+          <t>03h 23min</t>
         </is>
       </c>
     </row>
@@ -3948,11 +3948,11 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>2121308</v>
+        <v>2121292</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3962,27 +3962,27 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>01h 04min</t>
+          <t>03h 23min</t>
         </is>
       </c>
     </row>
@@ -4008,11 +4008,11 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>2121301</v>
+        <v>2121310</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4022,27 +4022,27 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>03h 31min</t>
+          <t>03h 04min</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 00 Hs 17 Min</t>
+          <t xml:space="preserve"> 00 Hs 21 Min</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05min</t>
+          <t>09min</t>
         </is>
       </c>
     </row>
@@ -4398,11 +4398,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2121288</v>
+        <v>2121306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4412,28 +4412,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:42</t>
+          <t>27/03/2026 01:28:40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 11 Min</t>
+          <t xml:space="preserve"> 03 Hs 15 Min</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01h 31min</t>
+          <t>02h 31min</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -4457,11 +4457,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2121306</v>
+        <v>2121288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4471,28 +4471,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:28:40</t>
+          <t>27/03/2026 00:28:42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 11 Min</t>
+          <t xml:space="preserve"> 04 Hs 15 Min</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>02h 27min</t>
+          <t>01h 35min</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 09 Min</t>
+          <t xml:space="preserve"> 04 Hs 13 Min</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>03h 30min</t>
+          <t>03h 33min</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -4575,42 +4575,42 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2121280</v>
+        <v>2121304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>MASTERCARGO - MATRIZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Heron Pedro dos Santos Rodrigues</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:55</t>
+          <t>27/03/2026 01:20:44</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 04 Hs 39 Min</t>
+          <t xml:space="preserve"> 03 Hs 23 Min</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02h 47min</t>
+          <t>01h 16min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -4634,42 +4634,42 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2121304</v>
+        <v>2121280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MASTERCARGO - MATRIZ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FILIAIS</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RES: Emissão KN x ML Nunes - Carlos Muniz SEB0C89 // APQ5957 - 815494037 </t>
+          <t>CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heron Pedro dos Santos Rodrigues</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:44</t>
+          <t>27/03/2026 00:00:55</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 03 Hs 19 Min</t>
+          <t xml:space="preserve"> 04 Hs 43 Min</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01h 12min</t>
+          <t>02h 50min</t>
         </is>
       </c>
       <c r="M7" t="n">

--- a/dados-atendimentos.xlsx
+++ b/dados-atendimentos.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,11 +713,11 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2121327</v>
+        <v>2121319</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -727,27 +727,27 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>RE: Emissão do CT-e manual- "RITMO</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Correia, Guilherme Valerio</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:06:47</t>
+          <t>27/03/2026 01:57:33</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:28:43</t>
+          <t>27/03/2026 01:56:43</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>01h 39min</t>
+          <t>02h 51min</t>
         </is>
       </c>
     </row>
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2121278</v>
+        <v>2121321</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:54</t>
+          <t>27/03/2026 03:11:31</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:52</t>
+          <t>27/03/2026 02:00:42</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>01h 38min</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2121279</v>
+        <v>2121315</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:56</t>
+          <t>27/03/2026 01:57:14</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:54</t>
+          <t>27/03/2026 01:52:44</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>12min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2121323</v>
+        <v>2121293</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -967,27 +967,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:41</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:18</t>
+          <t>27/03/2026 00:37:45</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:42</t>
+          <t>27/03/2026 00:36:42</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>04h 11min</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2121289</v>
+        <v>2121333</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:56</t>
+          <t>27/03/2026 03:45:47</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:46</t>
+          <t>27/03/2026 03:44:45</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>01h 03min</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2121336</v>
+        <v>2121286</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:22:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:32:50</t>
+          <t>27/03/2026 00:09:20</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:22:42</t>
+          <t>27/03/2026 00:08:44</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>13min</t>
+          <t>04h 40min</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2121311</v>
+        <v>2121316</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1147,27 +1147,27 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:29</t>
+          <t>27/03/2026 01:57:20</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:45</t>
+          <t>27/03/2026 01:54:40</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2121326</v>
+        <v>2121279</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1207,27 +1207,27 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RES: Status das garantias Ritmo 27/03</t>
+          <t>ENC: MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Douglas Romagna Santos</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:24</t>
+          <t>27/03/2026 00:06:56</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:40</t>
+          <t>27/03/2026 00:00:54</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2121319</v>
+        <v>2121324</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:33</t>
+          <t>27/03/2026 02:29:20</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:43</t>
+          <t>27/03/2026 02:08:48</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2121328</v>
+        <v>2121336</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1327,27 +1327,27 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:06:22</t>
+          <t>27/03/2026 04:32:50</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:40</t>
+          <t>27/03/2026 04:22:42</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>39min</t>
+          <t>16min</t>
         </is>
       </c>
     </row>
@@ -1373,11 +1373,11 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2121329</v>
+        <v>2121309</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1387,27 +1387,27 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:33</t>
+          <t>27/03/2026 02:29:27</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:46</t>
+          <t>27/03/2026 01:40:42</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2121316</v>
+        <v>2121311</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -1447,27 +1447,27 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:20</t>
+          <t>27/03/2026 02:29:29</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:54:40</t>
+          <t>27/03/2026 01:40:45</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2121324</v>
+        <v>2121326</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1507,27 +1507,27 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RES: Status das garantias Ritmo 27/03</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Envio CTe/MDFe</t>
+          <t>Douglas Romagna Santos</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:20</t>
+          <t>27/03/2026 02:29:24</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:48</t>
+          <t>27/03/2026 02:10:40</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2121281</v>
+        <v>2121318</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>Resposta Automática</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte@multicte.com.br</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:06:58</t>
+          <t>27/03/2026 01:57:26</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:57</t>
+          <t>27/03/2026 01:56:42</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>04h 39min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -1613,11 +1613,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2121282</v>
+        <v>2121328</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Maria Beatriz Guedes de Brito</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:53</t>
+          <t>27/03/2026 04:06:22</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:58</t>
+          <t>27/03/2026 03:10:40</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>43min</t>
         </is>
       </c>
     </row>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2121295</v>
+        <v>2121298</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:43:18</t>
+          <t>27/03/2026 00:52:26</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:42</t>
+          <t>27/03/2026 00:50:41</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>04h 02min</t>
+          <t>03h 57min</t>
         </is>
       </c>
     </row>
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2121313</v>
+        <v>2121327</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>WHITE MARTINS</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1747,27 +1747,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>RES: Emitir CTe 408</t>
+          <t>RE: Emissão do CT-e manual- "RITMO</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Julio Henrique Labhardt Junior</t>
+          <t>Correia, Guilherme Valerio</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:24:37</t>
+          <t>27/03/2026 03:06:47</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:48</t>
+          <t>27/03/2026 02:28:43</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>01h 21min</t>
+          <t>01h 42min</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2121296</v>
+        <v>2121317</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1807,27 +1807,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Transporte sem CT-e - RITMO.</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>de Oliveira, Lucas Chaves</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:50</t>
+          <t>27/03/2026 01:57:23</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:44:42</t>
+          <t>27/03/2026 01:56:40</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>03h 47min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2121320</v>
+        <v>2121323</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1867,27 +1867,27 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Envio CTe/MDFe</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:08:41</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:29</t>
+          <t>27/03/2026 02:29:18</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:44</t>
+          <t>27/03/2026 02:08:42</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -1913,11 +1913,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2121322</v>
+        <v>2121330</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:05</t>
+          <t>27/03/2026 04:08:48</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:44</t>
+          <t>27/03/2026 03:10:47</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>02h 45min</t>
+          <t>40min</t>
         </is>
       </c>
     </row>
@@ -1973,11 +1973,11 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2121330</v>
+        <v>2121325</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:08:48</t>
+          <t>27/03/2026 02:29:22</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:47</t>
+          <t>27/03/2026 02:08:49</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>37min</t>
+          <t>02h 20min</t>
         </is>
       </c>
     </row>
@@ -2033,11 +2033,11 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2121284</v>
+        <v>2121295</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>RES: MANIFESTAR NF AWV6A28</t>
+          <t>ENC: CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:28:45</t>
+          <t>27/03/2026 00:43:18</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:04:42</t>
+          <t>27/03/2026 00:42:42</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>04h 17min</t>
+          <t>04h 06min</t>
         </is>
       </c>
     </row>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2121333</v>
+        <v>2121313</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>WHITE MARTINS</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2107,27 +2107,27 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Emitir CTe 408</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Julio Henrique Labhardt Junior</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:45:47</t>
+          <t>27/03/2026 03:24:37</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:45</t>
+          <t>27/03/2026 01:40:48</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>01h 00min</t>
+          <t>01h 24min</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>2121317</v>
+        <v>2121299</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -2167,27 +2167,27 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>ENC: Expiração Certificado Digital - RITMO LOGISTICA S/A</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:23</t>
+          <t>27/03/2026 00:58:57</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:40</t>
+          <t>27/03/2026 00:56:42</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>03h 50min</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2121318</v>
+        <v>2121278</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -2227,27 +2227,27 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Resposta Automática</t>
+          <t>MDFe 334 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>cte@multicte.com.br</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:26</t>
+          <t>27/03/2026 00:06:54</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:56:42</t>
+          <t>27/03/2026 00:00:52</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2273,11 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>2121321</v>
+        <v>2121281</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:31</t>
+          <t>27/03/2026 00:06:58</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:00:42</t>
+          <t>27/03/2026 00:00:57</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>04h 42min</t>
         </is>
       </c>
     </row>
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>2121331</v>
+        <v>2121282</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2347,27 +2347,27 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: CTe 437 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Maria Beatriz Guedes de Brito</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:11:35</t>
+          <t>27/03/2026 00:28:53</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:10:48</t>
+          <t>27/03/2026 00:00:58</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>01h 34min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>2121325</v>
+        <v>2121320</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:22</t>
+          <t>27/03/2026 01:57:29</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:08:49</t>
+          <t>27/03/2026 01:56:44</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>02h 52min</t>
         </is>
       </c>
     </row>
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2121293</v>
+        <v>2121314</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2467,27 +2467,27 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:37:45</t>
+          <t>27/03/2026 02:47:46</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:36:42</t>
+          <t>27/03/2026 01:52:40</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>04h 08min</t>
+          <t>02h 01min</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2121286</v>
+        <v>2121331</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ENC: CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.079 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:09:20</t>
+          <t>27/03/2026 03:11:35</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:44</t>
+          <t>27/03/2026 03:10:48</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>04h 36min</t>
+          <t>01h 37min</t>
         </is>
       </c>
     </row>
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>2121314</v>
+        <v>2121284</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2587,27 +2587,27 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>RES: MANIFESTAR NF AWV6A28</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:47:46</t>
+          <t>27/03/2026 00:28:45</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:40</t>
+          <t>27/03/2026 00:04:42</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>01h 58min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>2121315</v>
+        <v>2121332</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2647,27 +2647,27 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44742 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:57:14</t>
+          <t>27/03/2026 04:10:45</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:52:44</t>
+          <t>27/03/2026 03:44:42</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>02h 48min</t>
+          <t>38min</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2121298</v>
+        <v>2121296</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>ENC: Transporte sem CT-e - RITMO.</t>
+          <t>Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>de Oliveira, Lucas Chaves</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:52:26</t>
+          <t>27/03/2026 00:58:50</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:50:41</t>
+          <t>27/03/2026 00:44:42</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>03h 53min</t>
+          <t>03h 50min</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>2121299</v>
+        <v>2121322</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
@@ -2767,27 +2767,27 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>ENC: CT-e: 000.048.077 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:58:57</t>
+          <t>27/03/2026 02:01:05</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:42</t>
+          <t>27/03/2026 02:00:44</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>03h 47min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -2813,11 +2813,11 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>2121332</v>
+        <v>2121329</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2827,27 +2827,27 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.080 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CT-e: 000.048.078 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 04:10:45</t>
+          <t>27/03/2026 03:11:33</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:44:42</t>
+          <t>27/03/2026 03:10:46</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>35min</t>
+          <t>01h 37min</t>
         </is>
       </c>
     </row>
@@ -2873,11 +2873,11 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>2121309</v>
+        <v>2121289</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2887,27 +2887,27 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 2530 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Motor de Emissão - nstech</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:29:27</t>
+          <t>27/03/2026 00:28:56</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:42</t>
+          <t>27/03/2026 00:28:46</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>02h 16min</t>
+          <t>04h 20min</t>
         </is>
       </c>
     </row>
@@ -2988,11 +2988,11 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>2121308</v>
+        <v>2121307</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF DJC1E58</t>
+          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 03:37:42</t>
+          <t>27/03/2026 02:15:26</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:34:40</t>
+          <t>27/03/2026 01:32:42</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>01h 08min</t>
+          <t>02h 34min</t>
         </is>
       </c>
     </row>
@@ -3048,11 +3048,11 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>2121285</v>
+        <v>2121287</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>FILIAL MOGI</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3062,27 +3062,27 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
+          <t>MANIFESTAR NF - OEP9E65</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>Jonas Antonio Torres Garcia</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:13</t>
+          <t>27/03/2026 01:59:40</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:08:42</t>
+          <t>27/03/2026 00:18:40</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>03h 23min</t>
+          <t>02h 49min</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2121300</v>
+        <v>2121277</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
@@ -3122,27 +3122,27 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: Solicitação de CT-e - TBW5I40</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Supervisão 02 RasterGR</t>
+          <t>Renata Pereira de Lima</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:11:39</t>
+          <t>27/03/2026 00:56:09</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:04:42</t>
+          <t>27/03/2026 00:00:49</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>03h 34min</t>
+          <t>03h 53min</t>
         </is>
       </c>
     </row>
@@ -3168,11 +3168,11 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>2121277</v>
+        <v>2121305</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3182,27 +3182,27 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>RES: Solicitação de CT-e - TBW5I40</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:56:09</t>
+          <t>27/03/2026 02:10:27</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:49</t>
+          <t>27/03/2026 01:26:40</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>03h 49min</t>
+          <t>02h 39min</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2121291</v>
+        <v>2121310</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>RECKITT</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3242,27 +3242,27 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
+          <t>ENC: CTe 44740 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>RibeiroFiuza, Fernando</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:41:29</t>
+          <t>27/03/2026 01:42:00</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:30:42</t>
+          <t>27/03/2026 01:40:44</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>03h 04min</t>
+          <t>03h 07min</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>2121297</v>
+        <v>2121276</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>CCR</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3302,27 +3302,27 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>RES: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
+          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Renata Pereira de Lima</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:49:11</t>
+          <t>27/03/2026 00:07:57</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:40</t>
+          <t>27/03/2026 00:00:43</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>03h 56min</t>
+          <t>04h 41min</t>
         </is>
       </c>
     </row>
@@ -3348,11 +3348,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2121307</v>
+        <v>2121300</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>CCR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - MFO0A99</t>
+          <t>Re: CT-e: 000.048.070 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Supervisão 02 RasterGR</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:15:26</t>
+          <t>27/03/2026 01:11:39</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:32:42</t>
+          <t>27/03/2026 01:04:42</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>02h 30min</t>
+          <t>03h 37min</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>2121276</v>
+        <v>2121303</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
@@ -3422,27 +3422,27 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 442 Série 88 Emitido - RITMO LOGISTICA SA</t>
+          <t>RE: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>Feitosa de Santana, Sabrina</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:07:57</t>
+          <t>27/03/2026 01:23:29</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:00:43</t>
+          <t>27/03/2026 01:20:40</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>04h 38min</t>
+          <t>03h 26min</t>
         </is>
       </c>
     </row>
@@ -3468,11 +3468,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2121312</v>
+        <v>2121283</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3482,27 +3482,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>XML Femsa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:42:05</t>
+          <t>27/03/2026 00:48:23</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:40:47</t>
+          <t>27/03/2026 00:02:40</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>03h 04min</t>
+          <t>04h 01min</t>
         </is>
       </c>
     </row>
@@ -3528,11 +3528,11 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2121301</v>
+        <v>2121292</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>SPAL/FEMSA</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>RES: Transporte sem CT-e - RITMO.</t>
+          <t>CT-e: 000.048.075 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>cte_prd_saidas@kof.com.mx</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:10:59</t>
+          <t>27/03/2026 01:22:19</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:06:42</t>
+          <t>27/03/2026 00:36:40</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>03h 35min</t>
+          <t>03h 27min</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3588,11 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>2121303</v>
+        <v>2121302</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SPAL JUNDIAÍ</t>
+          <t>FILIAL MARILIA</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3602,27 +3602,27 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>RE: Transporte sem CT-e - RITMO.</t>
+          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Feitosa de Santana, Sabrina</t>
+          <t>Ricardo Cardoso da Costa</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:23:29</t>
+          <t>27/03/2026 02:01:22</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:20:40</t>
+          <t>27/03/2026 01:12:40</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>03h 22min</t>
+          <t>02h 48min</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2121283</v>
+        <v>2121291</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>SPAL/FEMSA</t>
+          <t>RECKITT</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.073 / 007 - RITMO LOGISTICA S/A</t>
+          <t>RES: [EXTERNAL] RES: INFORMAÇÕES PARA EMISSÃO DE CTE</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>cte_prd_saidas@kof.com.mx</t>
+          <t>RibeiroFiuza, Fernando</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:48:23</t>
+          <t>27/03/2026 01:41:29</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:02:40</t>
+          <t>27/03/2026 00:30:42</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>03h 57min</t>
+          <t>03h 08min</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2121305</v>
+        <v>2121301</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>RES: Transporte sem CT-e - RITMO.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3732,17 +3732,17 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:10:27</t>
+          <t>27/03/2026 01:10:59</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:26:40</t>
+          <t>27/03/2026 01:06:42</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>02h 35min</t>
+          <t>03h 38min</t>
         </is>
       </c>
     </row>
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>2121302</v>
+        <v>2121335</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MARILIA</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3782,27 +3782,27 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>EMISSÃO DE CONTRATO - EFW7H61</t>
+          <t>CTe 44743 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Ricardo Cardoso da Costa</t>
+          <t>Motor de Emissão - nstech</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 04:22:40</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 02:01:22</t>
+          <t>27/03/2026 04:47:10</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:12:40</t>
+          <t>27/03/2026 04:22:40</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>02h 44min</t>
+          <t>02min</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>2121287</v>
+        <v>2121312</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>FILIAL MOGI</t>
+          <t>SPAL JUNDIAÍ</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>MANIFESTAR NF - OEP9E65</t>
+          <t>ENC: CTe 44741 Série 52 Emitido - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Jonas Antonio Torres Garcia</t>
+          <t>XML Femsa</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:59:40</t>
+          <t>27/03/2026 01:42:05</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:18:40</t>
+          <t>27/03/2026 01:40:47</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>02h 46min</t>
+          <t>03h 07min</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>2121294</v>
+        <v>2121285</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>CT-e: 000.048.076 / 007 - RITMO LOGISTICA S/A</t>
+          <t>CT-e: 000.048.074 / 007 - RITMO LOGISTICA S/A</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/2026 00:08:42</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 01:22:25</t>
+          <t>27/03/2026 01:22:13</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>27/03/2026 00:42:40</t>
+          <t>27/03/20